--- a/Archivos/Archivos_origen/Planeación contenido blog PaniPlay 2025.xlsx
+++ b/Archivos/Archivos_origen/Planeación contenido blog PaniPlay 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/jhor_caro_virtualsoft_tech/Documents/Documentos/GitHub/Planeaci-n_SEO/Archivos/Archivos_origen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="11_1EA87AF73562F5927A472218417A2D1B2C2F09A9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB7113F0-08F8-4CE7-B58D-160923ADD450}"/>
+  <xr:revisionPtr revIDLastSave="321" documentId="11_1EA87AF73562F5927A472218417A2D1B2C2F09A9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A83DE49-A63E-4378-9105-F9661C4A03E6}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enero" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2265" uniqueCount="942">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2083" uniqueCount="937">
   <si>
     <t>m</t>
   </si>
@@ -3966,22 +3966,7 @@
     <t>Manuela</t>
   </si>
   <si>
-    <t>15 min</t>
-  </si>
-  <si>
     <t>1 hora</t>
-  </si>
-  <si>
-    <t>30 min</t>
-  </si>
-  <si>
-    <t>2 hora</t>
-  </si>
-  <si>
-    <t>45 min</t>
-  </si>
-  <si>
-    <t>90 min</t>
   </si>
   <si>
     <t>Responsable de publicacion</t>
@@ -4652,7 +4637,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5078,6 +5063,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5093,6 +5085,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5308,10 +5304,12 @@
     <col min="8" max="8" width="19.36328125" customWidth="1"/>
     <col min="9" max="9" width="34.453125" customWidth="1"/>
     <col min="10" max="10" width="23.90625" customWidth="1"/>
+    <col min="13" max="13" width="12.6328125" style="159"/>
     <col min="14" max="14" width="25.90625" customWidth="1"/>
     <col min="15" max="15" width="22.7265625" customWidth="1"/>
     <col min="16" max="16" width="19.90625" customWidth="1"/>
-    <col min="17" max="19" width="14.36328125" customWidth="1"/>
+    <col min="17" max="18" width="14.36328125" customWidth="1"/>
+    <col min="19" max="19" width="14.36328125" style="159" customWidth="1"/>
     <col min="20" max="20" width="13.7265625" customWidth="1"/>
     <col min="21" max="21" width="25.453125" customWidth="1"/>
   </cols>
@@ -5353,7 +5351,7 @@
       <c r="L1" s="156" t="s">
         <v>931</v>
       </c>
-      <c r="M1" s="156" t="s">
+      <c r="M1" s="157" t="s">
         <v>932</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -5369,10 +5367,10 @@
         <v>13</v>
       </c>
       <c r="R1" s="156" t="s">
-        <v>940</v>
-      </c>
-      <c r="S1" s="156" t="s">
-        <v>941</v>
+        <v>935</v>
+      </c>
+      <c r="S1" s="157" t="s">
+        <v>936</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>14</v>
@@ -5432,8 +5430,8 @@
       <c r="L2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M2" s="15" t="s">
-        <v>934</v>
+      <c r="M2" s="158">
+        <v>15</v>
       </c>
       <c r="N2" s="8" t="s">
         <v>24</v>
@@ -5450,8 +5448,8 @@
       <c r="R2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S2" s="15" t="s">
-        <v>934</v>
+      <c r="S2" s="158">
+        <v>15</v>
       </c>
       <c r="T2" s="10" t="s">
         <v>28</v>
@@ -5495,8 +5493,8 @@
       <c r="L3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M3" s="15" t="s">
-        <v>934</v>
+      <c r="M3" s="158">
+        <v>15</v>
       </c>
       <c r="N3" s="13" t="s">
         <v>38</v>
@@ -5511,8 +5509,8 @@
       <c r="R3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S3" s="15" t="s">
-        <v>934</v>
+      <c r="S3" s="158">
+        <v>15</v>
       </c>
       <c r="T3" s="9" t="s">
         <v>40</v>
@@ -5556,8 +5554,8 @@
       <c r="L4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M4" s="15" t="s">
-        <v>935</v>
+      <c r="M4" s="158">
+        <v>60</v>
       </c>
       <c r="N4" s="8" t="s">
         <v>47</v>
@@ -5574,15 +5572,15 @@
       <c r="R4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S4" s="15" t="s">
-        <v>935</v>
+      <c r="S4" s="158">
+        <v>60</v>
       </c>
       <c r="T4" s="9" t="s">
         <v>50</v>
       </c>
       <c r="U4" s="3"/>
     </row>
-    <row r="5" spans="1:35" ht="75">
+    <row r="5" spans="1:35" ht="62.5">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
@@ -5619,8 +5617,8 @@
       <c r="L5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M5" s="15" t="s">
-        <v>936</v>
+      <c r="M5" s="158">
+        <v>30</v>
       </c>
       <c r="N5" s="16" t="s">
         <v>56</v>
@@ -5637,8 +5635,8 @@
       <c r="R5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S5" s="15" t="s">
-        <v>936</v>
+      <c r="S5" s="158">
+        <v>30</v>
       </c>
       <c r="T5" s="10" t="s">
         <v>58</v>
@@ -5682,8 +5680,8 @@
       <c r="L6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M6" s="15" t="s">
-        <v>934</v>
+      <c r="M6" s="158">
+        <v>15</v>
       </c>
       <c r="N6" s="21" t="s">
         <v>66</v>
@@ -5700,8 +5698,8 @@
       <c r="R6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S6" s="15" t="s">
-        <v>934</v>
+      <c r="S6" s="158">
+        <v>15</v>
       </c>
       <c r="T6" s="10" t="s">
         <v>70</v>
@@ -5759,8 +5757,8 @@
       <c r="L7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M7" s="15" t="s">
-        <v>937</v>
+      <c r="M7" s="158">
+        <v>120</v>
       </c>
       <c r="N7" s="16" t="s">
         <v>77</v>
@@ -5777,8 +5775,8 @@
       <c r="R7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S7" s="15" t="s">
-        <v>937</v>
+      <c r="S7" s="158">
+        <v>120</v>
       </c>
       <c r="T7" s="10" t="s">
         <v>81</v>
@@ -5834,8 +5832,8 @@
       <c r="L8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M8" s="15" t="s">
-        <v>936</v>
+      <c r="M8" s="158">
+        <v>30</v>
       </c>
       <c r="N8" s="13" t="s">
         <v>87</v>
@@ -5852,8 +5850,8 @@
       <c r="R8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S8" s="15" t="s">
-        <v>936</v>
+      <c r="S8" s="158">
+        <v>30</v>
       </c>
       <c r="T8" s="9" t="s">
         <v>91</v>
@@ -5897,8 +5895,8 @@
       <c r="L9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M9" s="15" t="s">
-        <v>938</v>
+      <c r="M9" s="158">
+        <v>45</v>
       </c>
       <c r="N9" s="26" t="s">
         <v>98</v>
@@ -5915,8 +5913,8 @@
       <c r="R9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S9" s="15" t="s">
-        <v>938</v>
+      <c r="S9" s="158">
+        <v>45</v>
       </c>
       <c r="T9" s="25" t="s">
         <v>102</v>
@@ -5960,8 +5958,8 @@
       <c r="L10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M10" s="15" t="s">
-        <v>935</v>
+      <c r="M10" s="158">
+        <v>60</v>
       </c>
       <c r="N10" s="28" t="s">
         <v>109</v>
@@ -5976,8 +5974,8 @@
       <c r="R10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S10" s="15" t="s">
-        <v>935</v>
+      <c r="S10" s="158">
+        <v>60</v>
       </c>
       <c r="T10" s="9" t="s">
         <v>112</v>
@@ -6035,8 +6033,8 @@
       <c r="L11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M11" s="15" t="s">
-        <v>935</v>
+      <c r="M11" s="158">
+        <v>60</v>
       </c>
       <c r="N11" s="30" t="s">
         <v>118</v>
@@ -6051,8 +6049,8 @@
       <c r="R11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S11" s="15" t="s">
-        <v>935</v>
+      <c r="S11" s="158">
+        <v>60</v>
       </c>
       <c r="T11" s="10" t="s">
         <v>121</v>
@@ -6063,57 +6061,57 @@
       <c r="I12" s="31"/>
       <c r="J12" s="31"/>
       <c r="L12" s="7"/>
-      <c r="M12" s="15"/>
+      <c r="M12" s="158"/>
       <c r="R12" s="7"/>
-      <c r="S12" s="15"/>
+      <c r="S12" s="158"/>
     </row>
     <row r="13" spans="1:35">
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="L13" s="7"/>
-      <c r="M13" s="15"/>
+      <c r="M13" s="158"/>
       <c r="R13" s="7"/>
-      <c r="S13" s="15"/>
+      <c r="S13" s="158"/>
     </row>
     <row r="14" spans="1:35">
       <c r="I14" s="31"/>
       <c r="J14" s="31"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="15"/>
+      <c r="M14" s="158"/>
       <c r="R14" s="7"/>
-      <c r="S14" s="15"/>
+      <c r="S14" s="158"/>
     </row>
     <row r="15" spans="1:35">
       <c r="I15" s="31"/>
       <c r="J15" s="31"/>
       <c r="L15" s="7"/>
-      <c r="M15" s="15"/>
+      <c r="M15" s="158"/>
       <c r="R15" s="7"/>
-      <c r="S15" s="15"/>
+      <c r="S15" s="158"/>
     </row>
     <row r="16" spans="1:35">
       <c r="I16" s="31"/>
       <c r="J16" s="31"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="15"/>
+      <c r="M16" s="158"/>
       <c r="R16" s="7"/>
-      <c r="S16" s="15"/>
+      <c r="S16" s="158"/>
     </row>
     <row r="17" spans="9:19">
       <c r="I17" s="31"/>
       <c r="J17" s="31"/>
       <c r="L17" s="7"/>
-      <c r="M17" s="15"/>
+      <c r="M17" s="158"/>
       <c r="R17" s="7"/>
-      <c r="S17" s="15"/>
+      <c r="S17" s="158"/>
     </row>
     <row r="18" spans="9:19">
       <c r="I18" s="31"/>
       <c r="J18" s="31"/>
       <c r="L18" s="7"/>
-      <c r="M18" s="15"/>
+      <c r="M18" s="158"/>
       <c r="R18" s="7"/>
-      <c r="S18" s="15"/>
+      <c r="S18" s="158"/>
     </row>
     <row r="19" spans="9:19">
       <c r="I19" s="31"/>
@@ -15378,7 +15376,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="37.5">
+    <row r="56" spans="1:4" ht="25">
       <c r="A56" s="123">
         <v>45825</v>
       </c>
@@ -15490,7 +15488,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="37.5">
+    <row r="64" spans="1:4" ht="25">
       <c r="A64" s="123">
         <v>45848</v>
       </c>
@@ -21254,10 +21252,12 @@
     <col min="8" max="8" width="19.36328125" customWidth="1"/>
     <col min="9" max="9" width="34.453125" customWidth="1"/>
     <col min="10" max="10" width="23.90625" customWidth="1"/>
+    <col min="13" max="13" width="12.6328125" style="159"/>
     <col min="14" max="14" width="25.90625" customWidth="1"/>
     <col min="15" max="15" width="22.7265625" customWidth="1"/>
     <col min="16" max="16" width="19.90625" customWidth="1"/>
-    <col min="17" max="19" width="14.36328125" customWidth="1"/>
+    <col min="17" max="18" width="14.36328125" customWidth="1"/>
+    <col min="19" max="19" width="14.36328125" style="159" customWidth="1"/>
     <col min="20" max="20" width="13.7265625" customWidth="1"/>
     <col min="21" max="21" width="25.453125" customWidth="1"/>
   </cols>
@@ -21299,7 +21299,7 @@
       <c r="L1" s="156" t="s">
         <v>931</v>
       </c>
-      <c r="M1" s="156" t="s">
+      <c r="M1" s="157" t="s">
         <v>932</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -21315,10 +21315,10 @@
         <v>13</v>
       </c>
       <c r="R1" s="156" t="s">
-        <v>940</v>
-      </c>
-      <c r="S1" s="156" t="s">
-        <v>941</v>
+        <v>935</v>
+      </c>
+      <c r="S1" s="157" t="s">
+        <v>936</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>14</v>
@@ -21378,8 +21378,8 @@
       <c r="L2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M2" s="15" t="s">
-        <v>934</v>
+      <c r="M2" s="158">
+        <v>15</v>
       </c>
       <c r="N2" s="8" t="s">
         <v>129</v>
@@ -21396,8 +21396,8 @@
       <c r="R2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S2" s="15" t="s">
-        <v>934</v>
+      <c r="S2" s="158">
+        <v>15</v>
       </c>
       <c r="T2" s="10" t="s">
         <v>133</v>
@@ -21441,8 +21441,8 @@
       <c r="L3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M3" s="15" t="s">
-        <v>934</v>
+      <c r="M3" s="158">
+        <v>15</v>
       </c>
       <c r="N3" s="13" t="s">
         <v>140</v>
@@ -21457,8 +21457,8 @@
       <c r="R3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S3" s="15" t="s">
-        <v>934</v>
+      <c r="S3" s="158">
+        <v>15</v>
       </c>
       <c r="T3" s="9" t="s">
         <v>143</v>
@@ -21502,8 +21502,8 @@
       <c r="L4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M4" s="15" t="s">
-        <v>935</v>
+      <c r="M4" s="158">
+        <v>60</v>
       </c>
       <c r="N4" s="28" t="s">
         <v>149</v>
@@ -21520,8 +21520,8 @@
       <c r="R4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S4" s="15" t="s">
-        <v>935</v>
+      <c r="S4" s="158">
+        <v>60</v>
       </c>
       <c r="T4" s="9" t="s">
         <v>153</v>
@@ -21579,8 +21579,8 @@
       <c r="L5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M5" s="15" t="s">
-        <v>936</v>
+      <c r="M5" s="158">
+        <v>30</v>
       </c>
       <c r="N5" s="8" t="s">
         <v>160</v>
@@ -21597,8 +21597,8 @@
       <c r="R5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S5" s="15" t="s">
-        <v>936</v>
+      <c r="S5" s="158">
+        <v>30</v>
       </c>
       <c r="T5" s="9" t="s">
         <v>164</v>
@@ -21642,8 +21642,8 @@
       <c r="L6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M6" s="15" t="s">
-        <v>934</v>
+      <c r="M6" s="158">
+        <v>15</v>
       </c>
       <c r="N6" s="26" t="s">
         <v>170</v>
@@ -21658,8 +21658,8 @@
       <c r="R6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S6" s="15" t="s">
-        <v>934</v>
+      <c r="S6" s="158">
+        <v>15</v>
       </c>
       <c r="T6" s="25" t="s">
         <v>173</v>
@@ -21703,8 +21703,8 @@
       <c r="L7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M7" s="15" t="s">
-        <v>937</v>
+      <c r="M7" s="158">
+        <v>120</v>
       </c>
       <c r="N7" s="16" t="s">
         <v>181</v>
@@ -21719,8 +21719,8 @@
       <c r="R7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S7" s="15" t="s">
-        <v>937</v>
+      <c r="S7" s="158">
+        <v>120</v>
       </c>
       <c r="T7" s="10" t="s">
         <v>183</v>
@@ -21778,8 +21778,8 @@
       <c r="L8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M8" s="15" t="s">
-        <v>936</v>
+      <c r="M8" s="158">
+        <v>30</v>
       </c>
       <c r="N8" s="16" t="s">
         <v>192</v>
@@ -21796,8 +21796,8 @@
       <c r="R8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S8" s="15" t="s">
-        <v>936</v>
+      <c r="S8" s="158">
+        <v>30</v>
       </c>
       <c r="T8" s="10" t="s">
         <v>196</v>
@@ -21839,8 +21839,8 @@
       <c r="L9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M9" s="15" t="s">
-        <v>938</v>
+      <c r="M9" s="158">
+        <v>45</v>
       </c>
       <c r="N9" s="13" t="s">
         <v>198</v>
@@ -21857,8 +21857,8 @@
       <c r="R9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S9" s="15" t="s">
-        <v>938</v>
+      <c r="S9" s="158">
+        <v>45</v>
       </c>
       <c r="T9" s="9" t="s">
         <v>201</v>
@@ -21902,8 +21902,8 @@
       <c r="L10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M10" s="15" t="s">
-        <v>935</v>
+      <c r="M10" s="158">
+        <v>60</v>
       </c>
       <c r="N10" s="21" t="s">
         <v>208</v>
@@ -21918,8 +21918,8 @@
       <c r="R10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S10" s="15" t="s">
-        <v>935</v>
+      <c r="S10" s="158">
+        <v>60</v>
       </c>
       <c r="T10" s="10" t="s">
         <v>211</v>
@@ -21977,8 +21977,8 @@
       <c r="L11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M11" s="15" t="s">
-        <v>935</v>
+      <c r="M11" s="158">
+        <v>60</v>
       </c>
       <c r="N11" s="34" t="s">
         <v>219</v>
@@ -21993,8 +21993,8 @@
       <c r="R11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S11" s="15" t="s">
-        <v>935</v>
+      <c r="S11" s="158">
+        <v>60</v>
       </c>
       <c r="T11" s="10" t="s">
         <v>221</v>
@@ -22005,57 +22005,57 @@
       <c r="I12" s="31"/>
       <c r="J12" s="31"/>
       <c r="L12" s="7"/>
-      <c r="M12" s="15"/>
+      <c r="M12" s="158"/>
       <c r="R12" s="7"/>
-      <c r="S12" s="15"/>
+      <c r="S12" s="158"/>
     </row>
     <row r="13" spans="1:35">
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="L13" s="7"/>
-      <c r="M13" s="15"/>
+      <c r="M13" s="158"/>
       <c r="R13" s="7"/>
-      <c r="S13" s="15"/>
+      <c r="S13" s="158"/>
     </row>
     <row r="14" spans="1:35">
       <c r="I14" s="31"/>
       <c r="J14" s="31"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="15"/>
+      <c r="M14" s="158"/>
       <c r="R14" s="7"/>
-      <c r="S14" s="15"/>
+      <c r="S14" s="158"/>
     </row>
     <row r="15" spans="1:35">
       <c r="I15" s="31"/>
       <c r="J15" s="31"/>
       <c r="L15" s="7"/>
-      <c r="M15" s="15"/>
+      <c r="M15" s="158"/>
       <c r="R15" s="7"/>
-      <c r="S15" s="15"/>
+      <c r="S15" s="158"/>
     </row>
     <row r="16" spans="1:35">
       <c r="I16" s="31"/>
       <c r="J16" s="31"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="15"/>
+      <c r="M16" s="158"/>
       <c r="R16" s="7"/>
-      <c r="S16" s="15"/>
+      <c r="S16" s="158"/>
     </row>
     <row r="17" spans="9:19">
       <c r="I17" s="31"/>
       <c r="J17" s="31"/>
       <c r="L17" s="7"/>
-      <c r="M17" s="15"/>
+      <c r="M17" s="158"/>
       <c r="R17" s="7"/>
-      <c r="S17" s="15"/>
+      <c r="S17" s="158"/>
     </row>
     <row r="18" spans="9:19">
       <c r="I18" s="31"/>
       <c r="J18" s="31"/>
       <c r="L18" s="7"/>
-      <c r="M18" s="15"/>
+      <c r="M18" s="158"/>
       <c r="R18" s="7"/>
-      <c r="S18" s="15"/>
+      <c r="S18" s="158"/>
     </row>
     <row r="19" spans="9:19">
       <c r="I19" s="31"/>
@@ -26035,10 +26035,12 @@
     <col min="8" max="8" width="19.36328125" customWidth="1"/>
     <col min="9" max="9" width="34.453125" customWidth="1"/>
     <col min="10" max="10" width="23.90625" customWidth="1"/>
+    <col min="13" max="13" width="12.6328125" style="159"/>
     <col min="14" max="14" width="25.90625" customWidth="1"/>
     <col min="15" max="15" width="22.7265625" customWidth="1"/>
     <col min="16" max="16" width="19.90625" customWidth="1"/>
-    <col min="17" max="19" width="14.36328125" customWidth="1"/>
+    <col min="17" max="18" width="14.36328125" customWidth="1"/>
+    <col min="19" max="19" width="14.36328125" style="159" customWidth="1"/>
     <col min="20" max="20" width="16.36328125" customWidth="1"/>
     <col min="21" max="21" width="25.453125" customWidth="1"/>
   </cols>
@@ -26080,7 +26082,7 @@
       <c r="L1" s="156" t="s">
         <v>931</v>
       </c>
-      <c r="M1" s="156" t="s">
+      <c r="M1" s="157" t="s">
         <v>932</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -26096,10 +26098,10 @@
         <v>13</v>
       </c>
       <c r="R1" s="156" t="s">
-        <v>940</v>
-      </c>
-      <c r="S1" s="156" t="s">
-        <v>941</v>
+        <v>935</v>
+      </c>
+      <c r="S1" s="157" t="s">
+        <v>936</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>14</v>
@@ -26157,8 +26159,8 @@
       <c r="L2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M2" s="15" t="s">
-        <v>934</v>
+      <c r="M2" s="158">
+        <v>15</v>
       </c>
       <c r="N2" s="28" t="s">
         <v>227</v>
@@ -26175,8 +26177,8 @@
       <c r="R2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S2" s="15" t="s">
-        <v>934</v>
+      <c r="S2" s="158">
+        <v>15</v>
       </c>
       <c r="T2" s="9" t="s">
         <v>230</v>
@@ -26234,8 +26236,8 @@
       <c r="L3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M3" s="15" t="s">
-        <v>934</v>
+      <c r="M3" s="158">
+        <v>15</v>
       </c>
       <c r="N3" s="8" t="s">
         <v>236</v>
@@ -26250,8 +26252,8 @@
       <c r="R3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S3" s="15" t="s">
-        <v>934</v>
+      <c r="S3" s="158">
+        <v>15</v>
       </c>
       <c r="T3" s="9" t="s">
         <v>239</v>
@@ -26292,8 +26294,8 @@
       <c r="L4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M4" s="15" t="s">
-        <v>935</v>
+      <c r="M4" s="158">
+        <v>60</v>
       </c>
       <c r="N4" s="8" t="s">
         <v>244</v>
@@ -26310,8 +26312,8 @@
       <c r="R4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S4" s="15" t="s">
-        <v>935</v>
+      <c r="S4" s="158">
+        <v>60</v>
       </c>
       <c r="T4" s="10" t="s">
         <v>247</v>
@@ -26355,8 +26357,8 @@
       <c r="L5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M5" s="15" t="s">
-        <v>936</v>
+      <c r="M5" s="158">
+        <v>30</v>
       </c>
       <c r="N5" s="16" t="s">
         <v>252</v>
@@ -26373,8 +26375,8 @@
       <c r="R5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S5" s="15" t="s">
-        <v>936</v>
+      <c r="S5" s="158">
+        <v>30</v>
       </c>
       <c r="T5" s="10" t="s">
         <v>256</v>
@@ -26430,8 +26432,8 @@
       <c r="L6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M6" s="15" t="s">
-        <v>934</v>
+      <c r="M6" s="158">
+        <v>15</v>
       </c>
       <c r="N6" s="13" t="s">
         <v>261</v>
@@ -26446,8 +26448,8 @@
       <c r="R6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S6" s="15" t="s">
-        <v>934</v>
+      <c r="S6" s="158">
+        <v>15</v>
       </c>
       <c r="T6" s="9" t="s">
         <v>264</v>
@@ -26489,8 +26491,8 @@
       <c r="L7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M7" s="15" t="s">
-        <v>937</v>
+      <c r="M7" s="158">
+        <v>120</v>
       </c>
       <c r="N7" s="16" t="s">
         <v>270</v>
@@ -26507,8 +26509,8 @@
       <c r="R7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S7" s="15" t="s">
-        <v>937</v>
+      <c r="S7" s="158">
+        <v>120</v>
       </c>
       <c r="T7" s="10" t="s">
         <v>274</v>
@@ -26550,8 +26552,8 @@
       <c r="L8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M8" s="15" t="s">
-        <v>936</v>
+      <c r="M8" s="158">
+        <v>30</v>
       </c>
       <c r="N8" s="13" t="s">
         <v>280</v>
@@ -26564,8 +26566,8 @@
       <c r="R8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S8" s="15" t="s">
-        <v>936</v>
+      <c r="S8" s="158">
+        <v>30</v>
       </c>
       <c r="T8" s="9" t="s">
         <v>282</v>
@@ -26609,8 +26611,8 @@
       <c r="L9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M9" s="15" t="s">
-        <v>938</v>
+      <c r="M9" s="158">
+        <v>45</v>
       </c>
       <c r="N9" s="26" t="s">
         <v>286</v>
@@ -26623,8 +26625,8 @@
       <c r="R9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S9" s="15" t="s">
-        <v>938</v>
+      <c r="S9" s="158">
+        <v>45</v>
       </c>
       <c r="T9" s="37" t="s">
         <v>288</v>
@@ -26664,8 +26666,8 @@
       <c r="L10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M10" s="15" t="s">
-        <v>935</v>
+      <c r="M10" s="158">
+        <v>60</v>
       </c>
       <c r="N10" s="21" t="s">
         <v>293</v>
@@ -26680,8 +26682,8 @@
       <c r="R10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S10" s="15" t="s">
-        <v>935</v>
+      <c r="S10" s="158">
+        <v>60</v>
       </c>
       <c r="T10" s="10" t="s">
         <v>296</v>
@@ -26735,8 +26737,8 @@
       <c r="L11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M11" s="15" t="s">
-        <v>935</v>
+      <c r="M11" s="158">
+        <v>60</v>
       </c>
       <c r="N11" s="30" t="s">
         <v>301</v>
@@ -26751,8 +26753,8 @@
       <c r="R11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S11" s="15" t="s">
-        <v>935</v>
+      <c r="S11" s="158">
+        <v>60</v>
       </c>
       <c r="T11" s="10" t="s">
         <v>304</v>
@@ -26763,57 +26765,57 @@
       <c r="I12" s="31"/>
       <c r="J12" s="31"/>
       <c r="L12" s="7"/>
-      <c r="M12" s="15"/>
+      <c r="M12" s="158"/>
       <c r="R12" s="7"/>
-      <c r="S12" s="15"/>
+      <c r="S12" s="158"/>
     </row>
     <row r="13" spans="1:35">
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="L13" s="7"/>
-      <c r="M13" s="15"/>
+      <c r="M13" s="158"/>
       <c r="R13" s="7"/>
-      <c r="S13" s="15"/>
+      <c r="S13" s="158"/>
     </row>
     <row r="14" spans="1:35">
       <c r="I14" s="31"/>
       <c r="J14" s="31"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="15"/>
+      <c r="M14" s="158"/>
       <c r="R14" s="7"/>
-      <c r="S14" s="15"/>
+      <c r="S14" s="158"/>
     </row>
     <row r="15" spans="1:35">
       <c r="I15" s="31"/>
       <c r="J15" s="31"/>
       <c r="L15" s="7"/>
-      <c r="M15" s="15"/>
+      <c r="M15" s="158"/>
       <c r="R15" s="7"/>
-      <c r="S15" s="15"/>
+      <c r="S15" s="158"/>
     </row>
     <row r="16" spans="1:35">
       <c r="I16" s="31"/>
       <c r="J16" s="31"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="15"/>
+      <c r="M16" s="158"/>
       <c r="R16" s="7"/>
-      <c r="S16" s="15"/>
+      <c r="S16" s="158"/>
     </row>
     <row r="17" spans="9:19">
       <c r="I17" s="31"/>
       <c r="J17" s="31"/>
       <c r="L17" s="7"/>
-      <c r="M17" s="15"/>
+      <c r="M17" s="158"/>
       <c r="R17" s="7"/>
-      <c r="S17" s="15"/>
+      <c r="S17" s="158"/>
     </row>
     <row r="18" spans="9:19">
       <c r="I18" s="31"/>
       <c r="J18" s="31"/>
       <c r="L18" s="7"/>
-      <c r="M18" s="15"/>
+      <c r="M18" s="158"/>
       <c r="R18" s="7"/>
-      <c r="S18" s="15"/>
+      <c r="S18" s="158"/>
     </row>
     <row r="19" spans="9:19">
       <c r="I19" s="31"/>
@@ -30798,10 +30800,12 @@
     <col min="14" max="14" width="25.90625" customWidth="1"/>
     <col min="15" max="15" width="22.7265625" customWidth="1"/>
     <col min="16" max="16" width="19.90625" customWidth="1"/>
-    <col min="17" max="19" width="14.36328125" customWidth="1"/>
+    <col min="17" max="18" width="14.36328125" customWidth="1"/>
+    <col min="19" max="19" width="14.36328125" style="159" customWidth="1"/>
     <col min="20" max="20" width="16.36328125" customWidth="1"/>
     <col min="21" max="21" width="25.453125" customWidth="1"/>
-    <col min="22" max="23" width="14.36328125" customWidth="1"/>
+    <col min="22" max="22" width="14.36328125" customWidth="1"/>
+    <col min="23" max="23" width="14.36328125" style="159" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="39">
@@ -30856,8 +30860,12 @@
       <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
+      <c r="R1" s="156" t="s">
+        <v>935</v>
+      </c>
+      <c r="S1" s="157" t="s">
+        <v>936</v>
+      </c>
       <c r="T1" s="1" t="s">
         <v>14</v>
       </c>
@@ -30865,10 +30873,10 @@
         <v>15</v>
       </c>
       <c r="V1" s="156" t="s">
-        <v>940</v>
-      </c>
-      <c r="W1" s="156" t="s">
-        <v>941</v>
+        <v>935</v>
+      </c>
+      <c r="W1" s="157" t="s">
+        <v>936</v>
       </c>
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
@@ -30920,8 +30928,8 @@
       <c r="L2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M2" s="15" t="s">
-        <v>934</v>
+      <c r="M2" s="5">
+        <v>15</v>
       </c>
       <c r="N2" s="30" t="s">
         <v>310</v>
@@ -30935,8 +30943,12 @@
       <c r="Q2" s="7">
         <v>45752</v>
       </c>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
+      <c r="R2" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="S2" s="158">
+        <v>15</v>
+      </c>
       <c r="T2" s="10" t="s">
         <v>314</v>
       </c>
@@ -30944,8 +30956,8 @@
       <c r="V2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="W2" s="15" t="s">
-        <v>934</v>
+      <c r="W2" s="158">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="63.5">
@@ -30985,8 +30997,8 @@
       <c r="L3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M3" s="15" t="s">
-        <v>934</v>
+      <c r="M3" s="5">
+        <v>15</v>
       </c>
       <c r="N3" s="30" t="s">
         <v>319</v>
@@ -31000,8 +31012,12 @@
       <c r="Q3" s="7">
         <v>45752</v>
       </c>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
+      <c r="R3" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="S3" s="158">
+        <v>15</v>
+      </c>
       <c r="T3" s="10" t="s">
         <v>322</v>
       </c>
@@ -31009,8 +31025,8 @@
       <c r="V3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="W3" s="15" t="s">
-        <v>934</v>
+      <c r="W3" s="158">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:35" ht="62.5">
@@ -31050,8 +31066,8 @@
       <c r="L4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M4" s="15" t="s">
-        <v>935</v>
+      <c r="M4" s="5">
+        <v>60</v>
       </c>
       <c r="N4" s="13" t="s">
         <v>324</v>
@@ -31063,8 +31079,12 @@
       <c r="Q4" s="7">
         <v>45756</v>
       </c>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
+      <c r="R4" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="S4" s="158">
+        <v>60</v>
+      </c>
       <c r="T4" s="9" t="s">
         <v>330</v>
       </c>
@@ -31072,8 +31092,8 @@
       <c r="V4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="W4" s="15" t="s">
-        <v>935</v>
+      <c r="W4" s="158">
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:35" ht="75">
@@ -31113,8 +31133,8 @@
       <c r="L5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M5" s="15" t="s">
-        <v>936</v>
+      <c r="M5" s="5">
+        <v>30</v>
       </c>
       <c r="N5" s="16" t="s">
         <v>336</v>
@@ -31128,8 +31148,12 @@
       <c r="Q5" s="7">
         <v>45761</v>
       </c>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
+      <c r="R5" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="S5" s="158">
+        <v>30</v>
+      </c>
       <c r="T5" s="10" t="s">
         <v>339</v>
       </c>
@@ -31137,8 +31161,8 @@
       <c r="V5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="W5" s="15" t="s">
-        <v>936</v>
+      <c r="W5" s="158">
+        <v>30</v>
       </c>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
@@ -31190,8 +31214,8 @@
       <c r="L6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M6" s="15" t="s">
-        <v>934</v>
+      <c r="M6" s="5">
+        <v>15</v>
       </c>
       <c r="N6" s="28" t="s">
         <v>342</v>
@@ -31205,8 +31229,12 @@
       <c r="Q6" s="7">
         <v>45761</v>
       </c>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
+      <c r="R6" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="S6" s="158">
+        <v>15</v>
+      </c>
       <c r="T6" s="9" t="s">
         <v>345</v>
       </c>
@@ -31214,8 +31242,8 @@
       <c r="V6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="W6" s="15" t="s">
-        <v>934</v>
+      <c r="W6" s="158">
+        <v>15</v>
       </c>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
@@ -31267,8 +31295,8 @@
       <c r="L7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M7" s="15" t="s">
-        <v>937</v>
+      <c r="M7" s="5">
+        <v>120</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>351</v>
@@ -31280,8 +31308,12 @@
       <c r="Q7" s="7">
         <v>45762</v>
       </c>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
+      <c r="R7" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="S7" s="158">
+        <v>120</v>
+      </c>
       <c r="T7" s="9" t="s">
         <v>354</v>
       </c>
@@ -31289,8 +31321,8 @@
       <c r="V7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="W7" s="15" t="s">
-        <v>937</v>
+      <c r="W7" s="158">
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:35" ht="75">
@@ -31330,8 +31362,8 @@
       <c r="L8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M8" s="15" t="s">
-        <v>936</v>
+      <c r="M8" s="5">
+        <v>30</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>360</v>
@@ -31343,8 +31375,12 @@
       <c r="Q8" s="7">
         <v>45768</v>
       </c>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
+      <c r="R8" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="S8" s="158">
+        <v>30</v>
+      </c>
       <c r="T8" s="10" t="s">
         <v>363</v>
       </c>
@@ -31352,8 +31388,8 @@
       <c r="V8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="W8" s="15" t="s">
-        <v>936</v>
+      <c r="W8" s="158">
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:35" ht="100">
@@ -31393,8 +31429,8 @@
       <c r="L9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M9" s="15" t="s">
-        <v>938</v>
+      <c r="M9" s="5">
+        <v>45</v>
       </c>
       <c r="N9" s="21" t="s">
         <v>370</v>
@@ -31408,8 +31444,12 @@
       <c r="Q9" s="7">
         <v>45769</v>
       </c>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
+      <c r="R9" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="S9" s="158">
+        <v>45</v>
+      </c>
       <c r="T9" s="10" t="s">
         <v>374</v>
       </c>
@@ -31417,8 +31457,8 @@
       <c r="V9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="W9" s="15" t="s">
-        <v>938</v>
+      <c r="W9" s="158">
+        <v>45</v>
       </c>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
@@ -31470,8 +31510,8 @@
       <c r="L10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M10" s="15" t="s">
-        <v>935</v>
+      <c r="M10" s="5" t="s">
+        <v>934</v>
       </c>
       <c r="N10" s="8" t="s">
         <v>381</v>
@@ -31483,8 +31523,12 @@
       <c r="Q10" s="12">
         <v>45772</v>
       </c>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
+      <c r="R10" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="S10" s="158">
+        <v>60</v>
+      </c>
       <c r="T10" s="9" t="s">
         <v>383</v>
       </c>
@@ -31492,8 +31536,8 @@
       <c r="V10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="W10" s="15" t="s">
-        <v>935</v>
+      <c r="W10" s="158">
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:35" ht="124">
@@ -31533,8 +31577,8 @@
       <c r="L11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M11" s="15" t="s">
-        <v>935</v>
+      <c r="M11" s="5" t="s">
+        <v>934</v>
       </c>
       <c r="N11" s="26" t="s">
         <v>390</v>
@@ -31546,8 +31590,12 @@
       <c r="Q11" s="7">
         <v>45777</v>
       </c>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
+      <c r="R11" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="S11" s="158">
+        <v>60</v>
+      </c>
       <c r="T11" s="37" t="s">
         <v>393</v>
       </c>
@@ -31555,65 +31603,79 @@
       <c r="V11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="W11" s="15" t="s">
-        <v>935</v>
+      <c r="W11" s="158">
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:35">
       <c r="I12" s="31"/>
       <c r="J12" s="31"/>
       <c r="L12" s="7"/>
-      <c r="M12" s="15"/>
+      <c r="M12" s="5"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="158"/>
       <c r="V12" s="7"/>
-      <c r="W12" s="15"/>
+      <c r="W12" s="158"/>
     </row>
     <row r="13" spans="1:35">
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="L13" s="7"/>
-      <c r="M13" s="15"/>
+      <c r="M13" s="5"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="158"/>
       <c r="V13" s="7"/>
-      <c r="W13" s="15"/>
+      <c r="W13" s="158"/>
     </row>
     <row r="14" spans="1:35">
       <c r="I14" s="31"/>
       <c r="J14" s="31"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="15"/>
+      <c r="M14" s="5"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="158"/>
       <c r="V14" s="7"/>
-      <c r="W14" s="15"/>
+      <c r="W14" s="158"/>
     </row>
     <row r="15" spans="1:35">
       <c r="I15" s="31"/>
       <c r="J15" s="31"/>
       <c r="L15" s="7"/>
-      <c r="M15" s="15"/>
+      <c r="M15" s="5"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="158"/>
       <c r="V15" s="7"/>
-      <c r="W15" s="15"/>
+      <c r="W15" s="158"/>
     </row>
     <row r="16" spans="1:35">
       <c r="I16" s="31"/>
       <c r="J16" s="31"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="15"/>
+      <c r="M16" s="5"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="158"/>
       <c r="V16" s="7"/>
-      <c r="W16" s="15"/>
+      <c r="W16" s="158"/>
     </row>
     <row r="17" spans="9:23">
       <c r="I17" s="31"/>
       <c r="J17" s="31"/>
       <c r="L17" s="7"/>
-      <c r="M17" s="15"/>
+      <c r="M17" s="5"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="158"/>
       <c r="V17" s="7"/>
-      <c r="W17" s="15"/>
+      <c r="W17" s="158"/>
     </row>
     <row r="18" spans="9:23">
       <c r="I18" s="31"/>
       <c r="J18" s="31"/>
       <c r="L18" s="7"/>
-      <c r="M18" s="15"/>
+      <c r="M18" s="5"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="158"/>
       <c r="V18" s="7"/>
-      <c r="W18" s="15"/>
+      <c r="W18" s="158"/>
     </row>
     <row r="19" spans="9:23">
       <c r="I19" s="31"/>
@@ -35597,10 +35659,12 @@
     <col min="8" max="8" width="19.36328125" customWidth="1"/>
     <col min="9" max="9" width="26.6328125" customWidth="1"/>
     <col min="10" max="10" width="23.90625" customWidth="1"/>
+    <col min="13" max="13" width="12.6328125" style="159"/>
     <col min="14" max="14" width="25.90625" customWidth="1"/>
     <col min="15" max="15" width="22.7265625" customWidth="1"/>
     <col min="16" max="16" width="19.90625" customWidth="1"/>
-    <col min="17" max="19" width="14.36328125" customWidth="1"/>
+    <col min="17" max="18" width="14.36328125" customWidth="1"/>
+    <col min="19" max="19" width="14.36328125" style="159" customWidth="1"/>
     <col min="20" max="20" width="16.36328125" customWidth="1"/>
     <col min="21" max="21" width="25.453125" customWidth="1"/>
   </cols>
@@ -35642,7 +35706,7 @@
       <c r="L1" s="156" t="s">
         <v>931</v>
       </c>
-      <c r="M1" s="156" t="s">
+      <c r="M1" s="157" t="s">
         <v>932</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -35658,10 +35722,10 @@
         <v>13</v>
       </c>
       <c r="R1" s="156" t="s">
-        <v>940</v>
-      </c>
-      <c r="S1" s="156" t="s">
-        <v>941</v>
+        <v>935</v>
+      </c>
+      <c r="S1" s="157" t="s">
+        <v>936</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>14</v>
@@ -35721,8 +35785,8 @@
       <c r="L2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M2" s="15" t="s">
-        <v>934</v>
+      <c r="M2" s="158">
+        <v>15</v>
       </c>
       <c r="N2" s="30" t="s">
         <v>397</v>
@@ -35737,15 +35801,15 @@
       <c r="R2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S2" s="15" t="s">
-        <v>934</v>
+      <c r="S2" s="158">
+        <v>15</v>
       </c>
       <c r="T2" s="10" t="s">
         <v>400</v>
       </c>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:35" ht="139.5">
+    <row r="3" spans="1:35" ht="124">
       <c r="A3" s="22" t="s">
         <v>59</v>
       </c>
@@ -35782,8 +35846,8 @@
       <c r="L3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M3" s="15" t="s">
-        <v>934</v>
+      <c r="M3" s="158">
+        <v>15</v>
       </c>
       <c r="N3" s="30" t="s">
         <v>406</v>
@@ -35798,8 +35862,8 @@
       <c r="R3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S3" s="15" t="s">
-        <v>934</v>
+      <c r="S3" s="158">
+        <v>15</v>
       </c>
       <c r="T3" s="10" t="s">
         <v>409</v>
@@ -35843,8 +35907,8 @@
       <c r="L4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M4" s="15" t="s">
-        <v>935</v>
+      <c r="M4" s="158">
+        <v>60</v>
       </c>
       <c r="N4" s="8" t="s">
         <v>415</v>
@@ -35859,8 +35923,8 @@
       <c r="R4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S4" s="15" t="s">
-        <v>935</v>
+      <c r="S4" s="158">
+        <v>60</v>
       </c>
       <c r="T4" s="10" t="s">
         <v>418</v>
@@ -35904,8 +35968,8 @@
       <c r="L5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M5" s="15" t="s">
-        <v>936</v>
+      <c r="M5" s="158">
+        <v>30</v>
       </c>
       <c r="N5" s="21" t="s">
         <v>425</v>
@@ -35922,8 +35986,8 @@
       <c r="R5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S5" s="15" t="s">
-        <v>936</v>
+      <c r="S5" s="158">
+        <v>30</v>
       </c>
       <c r="T5" s="10" t="s">
         <v>428</v>
@@ -35981,8 +36045,8 @@
       <c r="L6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M6" s="15" t="s">
-        <v>934</v>
+      <c r="M6" s="158">
+        <v>15</v>
       </c>
       <c r="N6" s="13" t="s">
         <v>434</v>
@@ -35999,8 +36063,8 @@
       <c r="R6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S6" s="15" t="s">
-        <v>934</v>
+      <c r="S6" s="158">
+        <v>15</v>
       </c>
       <c r="T6" s="9" t="s">
         <v>437</v>
@@ -36044,8 +36108,8 @@
       <c r="L7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M7" s="15" t="s">
-        <v>937</v>
+      <c r="M7" s="158">
+        <v>120</v>
       </c>
       <c r="N7" s="26" t="s">
         <v>444</v>
@@ -36062,8 +36126,8 @@
       <c r="R7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S7" s="15" t="s">
-        <v>937</v>
+      <c r="S7" s="158">
+        <v>120</v>
       </c>
       <c r="T7" s="37" t="s">
         <v>448</v>
@@ -36107,8 +36171,8 @@
       <c r="L8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M8" s="15" t="s">
-        <v>936</v>
+      <c r="M8" s="158">
+        <v>30</v>
       </c>
       <c r="N8" s="16" t="s">
         <v>454</v>
@@ -36123,8 +36187,8 @@
       <c r="R8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S8" s="15" t="s">
-        <v>936</v>
+      <c r="S8" s="158">
+        <v>30</v>
       </c>
       <c r="T8" s="10" t="s">
         <v>457</v>
@@ -36182,8 +36246,8 @@
       <c r="L9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M9" s="15" t="s">
-        <v>938</v>
+      <c r="M9" s="158">
+        <v>45</v>
       </c>
       <c r="N9" s="8" t="s">
         <v>463</v>
@@ -36200,8 +36264,8 @@
       <c r="R9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S9" s="15" t="s">
-        <v>938</v>
+      <c r="S9" s="158">
+        <v>45</v>
       </c>
       <c r="T9" s="9" t="s">
         <v>467</v>
@@ -36245,8 +36309,8 @@
       <c r="L10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M10" s="15" t="s">
-        <v>935</v>
+      <c r="M10" s="158">
+        <v>60</v>
       </c>
       <c r="N10" s="28" t="s">
         <v>472</v>
@@ -36261,8 +36325,8 @@
       <c r="R10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S10" s="15" t="s">
-        <v>935</v>
+      <c r="S10" s="158">
+        <v>60</v>
       </c>
       <c r="T10" s="9" t="s">
         <v>475</v>
@@ -36320,8 +36384,8 @@
       <c r="L11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M11" s="15" t="s">
-        <v>935</v>
+      <c r="M11" s="158">
+        <v>60</v>
       </c>
       <c r="N11" s="13" t="s">
         <v>479</v>
@@ -36336,8 +36400,8 @@
       <c r="R11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S11" s="15" t="s">
-        <v>935</v>
+      <c r="S11" s="158">
+        <v>60</v>
       </c>
       <c r="T11" s="9" t="s">
         <v>482</v>
@@ -36348,57 +36412,57 @@
       <c r="I12" s="31"/>
       <c r="J12" s="31"/>
       <c r="L12" s="7"/>
-      <c r="M12" s="15"/>
+      <c r="M12" s="158"/>
       <c r="R12" s="7"/>
-      <c r="S12" s="15"/>
+      <c r="S12" s="158"/>
     </row>
     <row r="13" spans="1:35">
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="L13" s="7"/>
-      <c r="M13" s="15"/>
+      <c r="M13" s="158"/>
       <c r="R13" s="7"/>
-      <c r="S13" s="15"/>
+      <c r="S13" s="158"/>
     </row>
     <row r="14" spans="1:35">
       <c r="I14" s="31"/>
       <c r="J14" s="31"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="15"/>
+      <c r="M14" s="158"/>
       <c r="R14" s="7"/>
-      <c r="S14" s="15"/>
+      <c r="S14" s="158"/>
     </row>
     <row r="15" spans="1:35">
       <c r="I15" s="31"/>
       <c r="J15" s="31"/>
       <c r="L15" s="7"/>
-      <c r="M15" s="15"/>
+      <c r="M15" s="158"/>
       <c r="R15" s="7"/>
-      <c r="S15" s="15"/>
+      <c r="S15" s="158"/>
     </row>
     <row r="16" spans="1:35">
       <c r="I16" s="31"/>
       <c r="J16" s="31"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="15"/>
+      <c r="M16" s="158"/>
       <c r="R16" s="7"/>
-      <c r="S16" s="15"/>
+      <c r="S16" s="158"/>
     </row>
     <row r="17" spans="9:19">
       <c r="I17" s="31"/>
       <c r="J17" s="31"/>
       <c r="L17" s="7"/>
-      <c r="M17" s="15"/>
+      <c r="M17" s="158"/>
       <c r="R17" s="7"/>
-      <c r="S17" s="15"/>
+      <c r="S17" s="158"/>
     </row>
     <row r="18" spans="9:19">
       <c r="I18" s="31"/>
       <c r="J18" s="31"/>
       <c r="L18" s="7"/>
-      <c r="M18" s="15"/>
+      <c r="M18" s="158"/>
       <c r="R18" s="7"/>
-      <c r="S18" s="15"/>
+      <c r="S18" s="158"/>
     </row>
     <row r="19" spans="9:19">
       <c r="I19" s="31"/>
@@ -40383,10 +40447,12 @@
     <col min="8" max="8" width="19.36328125" customWidth="1"/>
     <col min="9" max="9" width="26.6328125" customWidth="1"/>
     <col min="10" max="10" width="23.90625" customWidth="1"/>
+    <col min="13" max="13" width="12.6328125" style="159"/>
     <col min="14" max="14" width="25.90625" customWidth="1"/>
     <col min="15" max="15" width="22.7265625" customWidth="1"/>
     <col min="16" max="16" width="19.90625" customWidth="1"/>
-    <col min="17" max="19" width="14.36328125" customWidth="1"/>
+    <col min="17" max="18" width="14.36328125" customWidth="1"/>
+    <col min="19" max="19" width="14.36328125" style="159" customWidth="1"/>
     <col min="20" max="20" width="16.36328125" customWidth="1"/>
     <col min="21" max="21" width="25.453125" customWidth="1"/>
   </cols>
@@ -40428,7 +40494,7 @@
       <c r="L1" s="156" t="s">
         <v>931</v>
       </c>
-      <c r="M1" s="156" t="s">
+      <c r="M1" s="157" t="s">
         <v>932</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -40444,10 +40510,10 @@
         <v>13</v>
       </c>
       <c r="R1" s="156" t="s">
-        <v>940</v>
-      </c>
-      <c r="S1" s="156" t="s">
-        <v>941</v>
+        <v>935</v>
+      </c>
+      <c r="S1" s="157" t="s">
+        <v>936</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>14</v>
@@ -40507,8 +40573,8 @@
       <c r="L2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M2" s="15" t="s">
-        <v>934</v>
+      <c r="M2" s="158">
+        <v>15</v>
       </c>
       <c r="N2" s="30" t="s">
         <v>487</v>
@@ -40525,15 +40591,15 @@
       <c r="R2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S2" s="15" t="s">
-        <v>934</v>
+      <c r="S2" s="158">
+        <v>15</v>
       </c>
       <c r="T2" s="10" t="s">
         <v>491</v>
       </c>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:35" ht="108.5">
+    <row r="3" spans="1:35" ht="100">
       <c r="A3" s="22" t="s">
         <v>59</v>
       </c>
@@ -40570,8 +40636,8 @@
       <c r="L3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M3" s="15" t="s">
-        <v>934</v>
+      <c r="M3" s="158">
+        <v>15</v>
       </c>
       <c r="N3" s="30" t="s">
         <v>497</v>
@@ -40586,8 +40652,8 @@
       <c r="R3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S3" s="15" t="s">
-        <v>934</v>
+      <c r="S3" s="158">
+        <v>15</v>
       </c>
       <c r="T3" s="10" t="s">
         <v>500</v>
@@ -40631,8 +40697,8 @@
       <c r="L4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M4" s="15" t="s">
-        <v>935</v>
+      <c r="M4" s="158">
+        <v>60</v>
       </c>
       <c r="N4" s="8" t="s">
         <v>504</v>
@@ -40647,8 +40713,8 @@
       <c r="R4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S4" s="15" t="s">
-        <v>935</v>
+      <c r="S4" s="158">
+        <v>60</v>
       </c>
       <c r="T4" s="10" t="s">
         <v>507</v>
@@ -40692,8 +40758,8 @@
       <c r="L5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M5" s="15" t="s">
-        <v>936</v>
+      <c r="M5" s="158">
+        <v>30</v>
       </c>
       <c r="N5" s="21" t="s">
         <v>513</v>
@@ -40708,8 +40774,8 @@
       <c r="R5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S5" s="15" t="s">
-        <v>936</v>
+      <c r="S5" s="158">
+        <v>30</v>
       </c>
       <c r="T5" s="10" t="s">
         <v>516</v>
@@ -40767,8 +40833,8 @@
       <c r="L6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M6" s="15" t="s">
-        <v>934</v>
+      <c r="M6" s="158">
+        <v>15</v>
       </c>
       <c r="N6" s="28" t="s">
         <v>522</v>
@@ -40783,8 +40849,8 @@
       <c r="R6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S6" s="15" t="s">
-        <v>934</v>
+      <c r="S6" s="158">
+        <v>15</v>
       </c>
       <c r="T6" s="9" t="s">
         <v>525</v>
@@ -40842,8 +40908,8 @@
       <c r="L7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M7" s="15" t="s">
-        <v>937</v>
+      <c r="M7" s="158">
+        <v>120</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>531</v>
@@ -40858,8 +40924,8 @@
       <c r="R7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S7" s="15" t="s">
-        <v>937</v>
+      <c r="S7" s="158">
+        <v>120</v>
       </c>
       <c r="T7" s="9" t="s">
         <v>534</v>
@@ -40903,8 +40969,8 @@
       <c r="L8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M8" s="15" t="s">
-        <v>936</v>
+      <c r="M8" s="158">
+        <v>30</v>
       </c>
       <c r="N8" s="13" t="s">
         <v>539</v>
@@ -40919,8 +40985,8 @@
       <c r="R8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S8" s="15" t="s">
-        <v>936</v>
+      <c r="S8" s="158">
+        <v>30</v>
       </c>
       <c r="T8" s="9" t="s">
         <v>542</v>
@@ -40964,8 +41030,8 @@
       <c r="L9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M9" s="15" t="s">
-        <v>938</v>
+      <c r="M9" s="158">
+        <v>45</v>
       </c>
       <c r="N9" s="16" t="s">
         <v>548</v>
@@ -40980,8 +41046,8 @@
       <c r="R9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S9" s="15" t="s">
-        <v>938</v>
+      <c r="S9" s="158">
+        <v>45</v>
       </c>
       <c r="T9" s="10" t="s">
         <v>551</v>
@@ -41039,8 +41105,8 @@
       <c r="L10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M10" s="15" t="s">
-        <v>935</v>
+      <c r="M10" s="158">
+        <v>60</v>
       </c>
       <c r="N10" s="26" t="s">
         <v>555</v>
@@ -41055,8 +41121,8 @@
       <c r="R10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S10" s="15" t="s">
-        <v>935</v>
+      <c r="S10" s="158">
+        <v>60</v>
       </c>
       <c r="T10" s="36" t="s">
         <v>558</v>
@@ -41100,8 +41166,8 @@
       <c r="L11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M11" s="15" t="s">
-        <v>935</v>
+      <c r="M11" s="158">
+        <v>60</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="18"/>
@@ -41112,8 +41178,8 @@
       <c r="R11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S11" s="15" t="s">
-        <v>935</v>
+      <c r="S11" s="158">
+        <v>60</v>
       </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
@@ -41122,57 +41188,57 @@
       <c r="I12" s="31"/>
       <c r="J12" s="31"/>
       <c r="L12" s="7"/>
-      <c r="M12" s="15"/>
+      <c r="M12" s="158"/>
       <c r="R12" s="7"/>
-      <c r="S12" s="15"/>
+      <c r="S12" s="158"/>
     </row>
     <row r="13" spans="1:35">
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="L13" s="7"/>
-      <c r="M13" s="15"/>
+      <c r="M13" s="158"/>
       <c r="R13" s="7"/>
-      <c r="S13" s="15"/>
+      <c r="S13" s="158"/>
     </row>
     <row r="14" spans="1:35">
       <c r="I14" s="31"/>
       <c r="J14" s="31"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="15"/>
+      <c r="M14" s="158"/>
       <c r="R14" s="7"/>
-      <c r="S14" s="15"/>
+      <c r="S14" s="158"/>
     </row>
     <row r="15" spans="1:35">
       <c r="I15" s="31"/>
       <c r="J15" s="31"/>
       <c r="L15" s="7"/>
-      <c r="M15" s="15"/>
+      <c r="M15" s="158"/>
       <c r="R15" s="7"/>
-      <c r="S15" s="15"/>
+      <c r="S15" s="158"/>
     </row>
     <row r="16" spans="1:35">
       <c r="I16" s="31"/>
       <c r="J16" s="31"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="15"/>
+      <c r="M16" s="158"/>
       <c r="R16" s="7"/>
-      <c r="S16" s="15"/>
+      <c r="S16" s="158"/>
     </row>
     <row r="17" spans="9:19">
       <c r="I17" s="31"/>
       <c r="J17" s="31"/>
       <c r="L17" s="7"/>
-      <c r="M17" s="15"/>
+      <c r="M17" s="158"/>
       <c r="R17" s="7"/>
-      <c r="S17" s="15"/>
+      <c r="S17" s="158"/>
     </row>
     <row r="18" spans="9:19">
       <c r="I18" s="31"/>
       <c r="J18" s="31"/>
       <c r="L18" s="7"/>
-      <c r="M18" s="15"/>
+      <c r="M18" s="158"/>
       <c r="R18" s="7"/>
-      <c r="S18" s="15"/>
+      <c r="S18" s="158"/>
     </row>
     <row r="19" spans="9:19">
       <c r="I19" s="31"/>
@@ -45153,10 +45219,12 @@
     <col min="8" max="8" width="19.36328125" customWidth="1"/>
     <col min="9" max="9" width="26.6328125" customWidth="1"/>
     <col min="10" max="10" width="23.90625" customWidth="1"/>
+    <col min="13" max="13" width="12.6328125" style="159"/>
     <col min="14" max="14" width="25.90625" customWidth="1"/>
     <col min="15" max="15" width="22.7265625" customWidth="1"/>
     <col min="16" max="16" width="19.90625" customWidth="1"/>
-    <col min="17" max="19" width="14.36328125" customWidth="1"/>
+    <col min="17" max="18" width="14.36328125" customWidth="1"/>
+    <col min="19" max="19" width="14.36328125" style="159" customWidth="1"/>
     <col min="20" max="20" width="16.36328125" customWidth="1"/>
     <col min="21" max="21" width="25.453125" customWidth="1"/>
   </cols>
@@ -45198,7 +45266,7 @@
       <c r="L1" s="156" t="s">
         <v>931</v>
       </c>
-      <c r="M1" s="156" t="s">
+      <c r="M1" s="157" t="s">
         <v>932</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -45214,10 +45282,10 @@
         <v>13</v>
       </c>
       <c r="R1" s="156" t="s">
-        <v>940</v>
-      </c>
-      <c r="S1" s="156" t="s">
-        <v>941</v>
+        <v>935</v>
+      </c>
+      <c r="S1" s="157" t="s">
+        <v>936</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>14</v>
@@ -45277,8 +45345,8 @@
       <c r="L2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M2" s="15" t="s">
-        <v>934</v>
+      <c r="M2" s="158">
+        <v>15</v>
       </c>
       <c r="N2" s="8" t="s">
         <v>566</v>
@@ -45292,8 +45360,8 @@
       <c r="R2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S2" s="15" t="s">
-        <v>934</v>
+      <c r="S2" s="158">
+        <v>15</v>
       </c>
       <c r="T2" s="10" t="s">
         <v>569</v>
@@ -45337,8 +45405,8 @@
       <c r="L3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M3" s="15" t="s">
-        <v>934</v>
+      <c r="M3" s="158">
+        <v>15</v>
       </c>
       <c r="N3" s="30" t="s">
         <v>575</v>
@@ -45353,8 +45421,8 @@
       <c r="R3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S3" s="15" t="s">
-        <v>934</v>
+      <c r="S3" s="158">
+        <v>15</v>
       </c>
       <c r="T3" s="10" t="s">
         <v>578</v>
@@ -45398,8 +45466,8 @@
       <c r="L4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M4" s="15" t="s">
-        <v>935</v>
+      <c r="M4" s="158">
+        <v>60</v>
       </c>
       <c r="N4" s="8" t="s">
         <v>582</v>
@@ -45414,8 +45482,8 @@
       <c r="R4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S4" s="15" t="s">
-        <v>935</v>
+      <c r="S4" s="158">
+        <v>60</v>
       </c>
       <c r="T4" s="10" t="s">
         <v>585</v>
@@ -45459,8 +45527,8 @@
       <c r="L5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M5" s="15" t="s">
-        <v>936</v>
+      <c r="M5" s="158">
+        <v>30</v>
       </c>
       <c r="N5" s="8" t="s">
         <v>592</v>
@@ -45475,8 +45543,8 @@
       <c r="R5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S5" s="15" t="s">
-        <v>936</v>
+      <c r="S5" s="158">
+        <v>30</v>
       </c>
       <c r="T5" s="9" t="s">
         <v>595</v>
@@ -45520,8 +45588,8 @@
       <c r="L6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M6" s="15" t="s">
-        <v>934</v>
+      <c r="M6" s="158">
+        <v>15</v>
       </c>
       <c r="N6" s="21" t="s">
         <v>598</v>
@@ -45536,8 +45604,8 @@
       <c r="R6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S6" s="15" t="s">
-        <v>934</v>
+      <c r="S6" s="158">
+        <v>15</v>
       </c>
       <c r="T6" s="10" t="s">
         <v>601</v>
@@ -45595,8 +45663,8 @@
       <c r="L7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M7" s="15" t="s">
-        <v>937</v>
+      <c r="M7" s="158">
+        <v>120</v>
       </c>
       <c r="N7" s="50" t="s">
         <v>607</v>
@@ -45611,8 +45679,8 @@
       <c r="R7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S7" s="15" t="s">
-        <v>937</v>
+      <c r="S7" s="158">
+        <v>120</v>
       </c>
       <c r="T7" s="9" t="s">
         <v>610</v>
@@ -45670,8 +45738,8 @@
       <c r="L8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M8" s="15" t="s">
-        <v>936</v>
+      <c r="M8" s="158">
+        <v>30</v>
       </c>
       <c r="N8" s="50" t="s">
         <v>616</v>
@@ -45686,8 +45754,8 @@
       <c r="R8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S8" s="15" t="s">
-        <v>936</v>
+      <c r="S8" s="158">
+        <v>30</v>
       </c>
       <c r="T8" s="9" t="s">
         <v>619</v>
@@ -45731,8 +45799,8 @@
       <c r="L9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M9" s="15" t="s">
-        <v>938</v>
+      <c r="M9" s="158">
+        <v>45</v>
       </c>
       <c r="N9" s="51" t="s">
         <v>628</v>
@@ -45745,8 +45813,8 @@
       <c r="R9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S9" s="15" t="s">
-        <v>938</v>
+      <c r="S9" s="158">
+        <v>45</v>
       </c>
       <c r="T9" s="37" t="s">
         <v>629</v>
@@ -45790,8 +45858,8 @@
       <c r="L10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M10" s="15" t="s">
-        <v>935</v>
+      <c r="M10" s="158">
+        <v>60</v>
       </c>
       <c r="N10" s="22"/>
       <c r="O10" s="18" t="s">
@@ -45804,8 +45872,8 @@
       <c r="R10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S10" s="15" t="s">
-        <v>935</v>
+      <c r="S10" s="158">
+        <v>60</v>
       </c>
       <c r="T10" s="9" t="s">
         <v>638</v>
@@ -45849,8 +45917,8 @@
       <c r="L11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="M11" s="15" t="s">
-        <v>935</v>
+      <c r="M11" s="158">
+        <v>60</v>
       </c>
       <c r="N11" s="52" t="s">
         <v>646</v>
@@ -45865,8 +45933,8 @@
       <c r="R11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="S11" s="15" t="s">
-        <v>935</v>
+      <c r="S11" s="158">
+        <v>60</v>
       </c>
       <c r="T11" s="10" t="s">
         <v>647</v>
@@ -45891,57 +45959,57 @@
       <c r="I12" s="31"/>
       <c r="J12" s="31"/>
       <c r="L12" s="7"/>
-      <c r="M12" s="15"/>
+      <c r="M12" s="158"/>
       <c r="R12" s="7"/>
-      <c r="S12" s="15"/>
+      <c r="S12" s="158"/>
     </row>
     <row r="13" spans="1:35">
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
       <c r="L13" s="7"/>
-      <c r="M13" s="15"/>
+      <c r="M13" s="158"/>
       <c r="R13" s="7"/>
-      <c r="S13" s="15"/>
+      <c r="S13" s="158"/>
     </row>
     <row r="14" spans="1:35">
       <c r="I14" s="31"/>
       <c r="J14" s="31"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="15"/>
+      <c r="M14" s="158"/>
       <c r="R14" s="7"/>
-      <c r="S14" s="15"/>
+      <c r="S14" s="158"/>
     </row>
     <row r="15" spans="1:35">
       <c r="I15" s="31"/>
       <c r="J15" s="31"/>
       <c r="L15" s="7"/>
-      <c r="M15" s="15"/>
+      <c r="M15" s="158"/>
       <c r="R15" s="7"/>
-      <c r="S15" s="15"/>
+      <c r="S15" s="158"/>
     </row>
     <row r="16" spans="1:35">
       <c r="I16" s="31"/>
       <c r="J16" s="31"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="15"/>
+      <c r="M16" s="158"/>
       <c r="R16" s="7"/>
-      <c r="S16" s="15"/>
+      <c r="S16" s="158"/>
     </row>
     <row r="17" spans="9:19">
       <c r="I17" s="31"/>
       <c r="J17" s="31"/>
       <c r="L17" s="7"/>
-      <c r="M17" s="15"/>
+      <c r="M17" s="158"/>
       <c r="R17" s="7"/>
-      <c r="S17" s="15"/>
+      <c r="S17" s="158"/>
     </row>
     <row r="18" spans="9:19">
       <c r="I18" s="31"/>
       <c r="J18" s="31"/>
       <c r="L18" s="7"/>
-      <c r="M18" s="15"/>
+      <c r="M18" s="158"/>
       <c r="R18" s="7"/>
-      <c r="S18" s="15"/>
+      <c r="S18" s="158"/>
     </row>
     <row r="19" spans="9:19">
       <c r="I19" s="31"/>
@@ -49923,10 +49991,12 @@
     <col min="9" max="9" width="22.7265625" customWidth="1"/>
     <col min="10" max="10" width="26.6328125" customWidth="1"/>
     <col min="11" max="11" width="23.90625" customWidth="1"/>
+    <col min="14" max="14" width="12.6328125" style="159"/>
     <col min="15" max="15" width="25.90625" customWidth="1"/>
     <col min="16" max="16" width="23.6328125" customWidth="1"/>
     <col min="17" max="17" width="19.90625" customWidth="1"/>
-    <col min="18" max="20" width="14.36328125" customWidth="1"/>
+    <col min="18" max="19" width="14.36328125" customWidth="1"/>
+    <col min="20" max="20" width="14.36328125" style="159" customWidth="1"/>
     <col min="21" max="22" width="25.453125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -49970,7 +50040,7 @@
       <c r="M1" s="156" t="s">
         <v>931</v>
       </c>
-      <c r="N1" s="156" t="s">
+      <c r="N1" s="157" t="s">
         <v>932</v>
       </c>
       <c r="O1" s="53" t="s">
@@ -49986,10 +50056,10 @@
         <v>13</v>
       </c>
       <c r="S1" s="156" t="s">
-        <v>940</v>
-      </c>
-      <c r="T1" s="156" t="s">
-        <v>941</v>
+        <v>935</v>
+      </c>
+      <c r="T1" s="157" t="s">
+        <v>936</v>
       </c>
       <c r="U1" s="53" t="s">
         <v>14</v>
@@ -50048,8 +50118,8 @@
       <c r="M2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N2" s="15" t="s">
-        <v>934</v>
+      <c r="N2" s="158">
+        <v>15</v>
       </c>
       <c r="O2" s="60" t="s">
         <v>658</v>
@@ -50064,8 +50134,8 @@
       <c r="S2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T2" s="15" t="s">
-        <v>934</v>
+      <c r="T2" s="158">
+        <v>15</v>
       </c>
       <c r="U2" s="63" t="s">
         <v>660</v>
@@ -50128,8 +50198,8 @@
       <c r="M3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N3" s="15" t="s">
-        <v>934</v>
+      <c r="N3" s="158">
+        <v>15</v>
       </c>
       <c r="O3" s="70" t="s">
         <v>662</v>
@@ -50144,8 +50214,8 @@
       <c r="S3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T3" s="15" t="s">
-        <v>934</v>
+      <c r="T3" s="158">
+        <v>15</v>
       </c>
       <c r="U3" s="72" t="s">
         <v>669</v>
@@ -50206,8 +50276,8 @@
       <c r="M4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N4" s="15" t="s">
-        <v>935</v>
+      <c r="N4" s="158">
+        <v>60</v>
       </c>
       <c r="O4" s="73" t="s">
         <v>676</v>
@@ -50222,8 +50292,8 @@
       <c r="S4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T4" s="15" t="s">
-        <v>935</v>
+      <c r="T4" s="158">
+        <v>60</v>
       </c>
       <c r="U4" s="75" t="s">
         <v>678</v>
@@ -50280,8 +50350,8 @@
       <c r="M5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N5" s="15" t="s">
-        <v>936</v>
+      <c r="N5" s="158">
+        <v>30</v>
       </c>
       <c r="O5" s="60" t="s">
         <v>686</v>
@@ -50296,8 +50366,8 @@
       <c r="S5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T5" s="15" t="s">
-        <v>936</v>
+      <c r="T5" s="158">
+        <v>30</v>
       </c>
       <c r="U5" s="63" t="s">
         <v>687</v>
@@ -50358,8 +50428,8 @@
       <c r="M6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N6" s="15" t="s">
-        <v>934</v>
+      <c r="N6" s="158">
+        <v>15</v>
       </c>
       <c r="O6" s="76" t="s">
         <v>695</v>
@@ -50374,8 +50444,8 @@
       <c r="S6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T6" s="15" t="s">
-        <v>934</v>
+      <c r="T6" s="158">
+        <v>15</v>
       </c>
       <c r="U6" s="72" t="s">
         <v>696</v>
@@ -50436,8 +50506,8 @@
       <c r="M7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N7" s="15" t="s">
-        <v>937</v>
+      <c r="N7" s="158">
+        <v>120</v>
       </c>
       <c r="O7" s="70" t="s">
         <v>703</v>
@@ -50452,8 +50522,8 @@
       <c r="S7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T7" s="15" t="s">
-        <v>937</v>
+      <c r="T7" s="158">
+        <v>120</v>
       </c>
       <c r="U7" s="72" t="s">
         <v>705</v>
@@ -50514,8 +50584,8 @@
       <c r="M8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N8" s="15" t="s">
-        <v>936</v>
+      <c r="N8" s="158">
+        <v>30</v>
       </c>
       <c r="O8" s="70" t="s">
         <v>713</v>
@@ -50530,8 +50600,8 @@
       <c r="S8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T8" s="15" t="s">
-        <v>936</v>
+      <c r="T8" s="158">
+        <v>30</v>
       </c>
       <c r="U8" s="75" t="s">
         <v>714</v>
@@ -50592,8 +50662,8 @@
       <c r="M9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N9" s="15" t="s">
-        <v>938</v>
+      <c r="N9" s="158">
+        <v>45</v>
       </c>
       <c r="O9" s="79" t="s">
         <v>720</v>
@@ -50608,8 +50678,8 @@
       <c r="S9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T9" s="15" t="s">
-        <v>938</v>
+      <c r="T9" s="158">
+        <v>45</v>
       </c>
       <c r="U9" s="72" t="s">
         <v>721</v>
@@ -50666,8 +50736,8 @@
       <c r="M10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N10" s="15" t="s">
-        <v>935</v>
+      <c r="N10" s="158">
+        <v>60</v>
       </c>
       <c r="O10" s="60" t="s">
         <v>728</v>
@@ -50682,8 +50752,8 @@
       <c r="S10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T10" s="15" t="s">
-        <v>935</v>
+      <c r="T10" s="158">
+        <v>60</v>
       </c>
       <c r="U10" s="63" t="s">
         <v>730</v>
@@ -50744,8 +50814,8 @@
       <c r="M11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N11" s="15" t="s">
-        <v>935</v>
+      <c r="N11" s="158">
+        <v>60</v>
       </c>
       <c r="O11" s="60" t="s">
         <v>736</v>
@@ -50760,8 +50830,8 @@
       <c r="S11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T11" s="15" t="s">
-        <v>935</v>
+      <c r="T11" s="158">
+        <v>60</v>
       </c>
       <c r="U11" s="75" t="s">
         <v>738</v>
@@ -50822,8 +50892,8 @@
       <c r="M12" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N12" s="15" t="s">
-        <v>936</v>
+      <c r="N12" s="158">
+        <v>30</v>
       </c>
       <c r="O12" s="60" t="s">
         <v>746</v>
@@ -50838,8 +50908,8 @@
       <c r="S12" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T12" s="15" t="s">
-        <v>936</v>
+      <c r="T12" s="158">
+        <v>30</v>
       </c>
       <c r="U12" s="75" t="s">
         <v>747</v>
@@ -50900,8 +50970,8 @@
       <c r="M13" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N13" s="15" t="s">
-        <v>935</v>
+      <c r="N13" s="158">
+        <v>60</v>
       </c>
       <c r="O13" s="84" t="s">
         <v>755</v>
@@ -50916,8 +50986,8 @@
       <c r="S13" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T13" s="15" t="s">
-        <v>935</v>
+      <c r="T13" s="158">
+        <v>60</v>
       </c>
       <c r="U13" s="72" t="s">
         <v>756</v>
@@ -50978,8 +51048,8 @@
       <c r="M14" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N14" s="15" t="s">
-        <v>939</v>
+      <c r="N14" s="158">
+        <v>90</v>
       </c>
       <c r="O14" s="86" t="s">
         <v>762</v>
@@ -50994,8 +51064,8 @@
       <c r="S14" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T14" s="15" t="s">
-        <v>939</v>
+      <c r="T14" s="158">
+        <v>90</v>
       </c>
       <c r="U14" s="88" t="s">
         <v>763</v>
@@ -51052,8 +51122,8 @@
       <c r="M15" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N15" s="15" t="s">
-        <v>936</v>
+      <c r="N15" s="158">
+        <v>30</v>
       </c>
       <c r="O15" s="60" t="s">
         <v>771</v>
@@ -51066,8 +51136,8 @@
       <c r="S15" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T15" s="15" t="s">
-        <v>936</v>
+      <c r="T15" s="158">
+        <v>30</v>
       </c>
       <c r="U15" s="63" t="s">
         <v>772</v>
@@ -51092,25 +51162,25 @@
       <c r="J16" s="31"/>
       <c r="K16" s="31"/>
       <c r="M16" s="7"/>
-      <c r="N16" s="15"/>
+      <c r="N16" s="158"/>
       <c r="S16" s="7"/>
-      <c r="T16" s="15"/>
+      <c r="T16" s="158"/>
     </row>
     <row r="17" spans="10:20">
       <c r="J17" s="31"/>
       <c r="K17" s="31"/>
       <c r="M17" s="7"/>
-      <c r="N17" s="15"/>
+      <c r="N17" s="158"/>
       <c r="S17" s="7"/>
-      <c r="T17" s="15"/>
+      <c r="T17" s="158"/>
     </row>
     <row r="18" spans="10:20">
       <c r="J18" s="31"/>
       <c r="K18" s="31"/>
       <c r="M18" s="7"/>
-      <c r="N18" s="15"/>
+      <c r="N18" s="158"/>
       <c r="S18" s="7"/>
-      <c r="T18" s="15"/>
+      <c r="T18" s="158"/>
     </row>
     <row r="19" spans="10:20">
       <c r="J19" s="31"/>
@@ -55107,10 +55177,12 @@
     <col min="9" max="9" width="22.7265625" customWidth="1"/>
     <col min="10" max="10" width="26.6328125" customWidth="1"/>
     <col min="11" max="11" width="23.90625" customWidth="1"/>
+    <col min="14" max="14" width="12.6328125" style="159"/>
     <col min="15" max="15" width="25.90625" customWidth="1"/>
     <col min="16" max="16" width="23.6328125" customWidth="1"/>
     <col min="17" max="17" width="19.90625" customWidth="1"/>
-    <col min="18" max="20" width="14.36328125" customWidth="1"/>
+    <col min="18" max="19" width="14.36328125" customWidth="1"/>
+    <col min="20" max="20" width="14.36328125" style="159" customWidth="1"/>
     <col min="21" max="22" width="25.453125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -55154,7 +55226,7 @@
       <c r="M1" s="156" t="s">
         <v>931</v>
       </c>
-      <c r="N1" s="156" t="s">
+      <c r="N1" s="157" t="s">
         <v>932</v>
       </c>
       <c r="O1" s="1" t="s">
@@ -55170,10 +55242,10 @@
         <v>13</v>
       </c>
       <c r="S1" s="156" t="s">
-        <v>940</v>
-      </c>
-      <c r="T1" s="156" t="s">
-        <v>941</v>
+        <v>935</v>
+      </c>
+      <c r="T1" s="157" t="s">
+        <v>936</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>14</v>
@@ -55230,8 +55302,8 @@
       <c r="M2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N2" s="15" t="s">
-        <v>934</v>
+      <c r="N2" s="158">
+        <v>15</v>
       </c>
       <c r="O2" s="90" t="s">
         <v>780</v>
@@ -55246,8 +55318,8 @@
       <c r="S2" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T2" s="15" t="s">
-        <v>934</v>
+      <c r="T2" s="158">
+        <v>30</v>
       </c>
       <c r="U2" s="63"/>
       <c r="V2" s="92"/>
@@ -55304,8 +55376,8 @@
       <c r="M3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N3" s="15" t="s">
-        <v>934</v>
+      <c r="N3" s="158">
+        <v>15</v>
       </c>
       <c r="O3" s="95" t="s">
         <v>789</v>
@@ -55320,8 +55392,8 @@
       <c r="S3" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T3" s="15" t="s">
-        <v>934</v>
+      <c r="T3" s="158">
+        <v>15</v>
       </c>
       <c r="U3" s="97" t="s">
         <v>790</v>
@@ -55380,8 +55452,8 @@
       <c r="M4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N4" s="15" t="s">
-        <v>935</v>
+      <c r="N4" s="158">
+        <v>60</v>
       </c>
       <c r="O4" s="98" t="s">
         <v>798</v>
@@ -55396,8 +55468,8 @@
       <c r="S4" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T4" s="15" t="s">
-        <v>935</v>
+      <c r="T4" s="158">
+        <v>60</v>
       </c>
       <c r="U4" s="58"/>
       <c r="V4" s="69"/>
@@ -55450,8 +55522,8 @@
       <c r="M5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N5" s="15" t="s">
-        <v>936</v>
+      <c r="N5" s="158">
+        <v>30</v>
       </c>
       <c r="O5" s="104"/>
       <c r="P5" s="104"/>
@@ -55462,8 +55534,8 @@
       <c r="S5" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T5" s="15" t="s">
-        <v>936</v>
+      <c r="T5" s="158">
+        <v>30</v>
       </c>
       <c r="U5" s="105"/>
       <c r="V5" s="100"/>
@@ -55520,8 +55592,8 @@
       <c r="M6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N6" s="15" t="s">
-        <v>934</v>
+      <c r="N6" s="158">
+        <v>15</v>
       </c>
       <c r="O6" s="108"/>
       <c r="P6" s="102"/>
@@ -55532,8 +55604,8 @@
       <c r="S6" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T6" s="15" t="s">
-        <v>934</v>
+      <c r="T6" s="158">
+        <v>15</v>
       </c>
       <c r="U6" s="102"/>
       <c r="V6" s="108"/>
@@ -55586,8 +55658,8 @@
       <c r="M7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N7" s="15" t="s">
-        <v>937</v>
+      <c r="N7" s="158">
+        <v>120</v>
       </c>
       <c r="O7" s="104"/>
       <c r="P7" s="104"/>
@@ -55598,8 +55670,8 @@
       <c r="S7" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T7" s="15" t="s">
-        <v>937</v>
+      <c r="T7" s="158">
+        <v>120</v>
       </c>
       <c r="U7" s="105"/>
       <c r="V7" s="100"/>
@@ -55656,8 +55728,8 @@
       <c r="M8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N8" s="15" t="s">
-        <v>936</v>
+      <c r="N8" s="158">
+        <v>30</v>
       </c>
       <c r="O8" s="106"/>
       <c r="P8" s="110"/>
@@ -55668,8 +55740,8 @@
       <c r="S8" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T8" s="15" t="s">
-        <v>936</v>
+      <c r="T8" s="158">
+        <v>30</v>
       </c>
       <c r="U8" s="108"/>
       <c r="V8" s="108"/>
@@ -55722,8 +55794,8 @@
       <c r="M9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N9" s="15" t="s">
-        <v>938</v>
+      <c r="N9" s="158">
+        <v>45</v>
       </c>
       <c r="O9" s="18"/>
       <c r="P9" s="18"/>
@@ -55734,8 +55806,8 @@
       <c r="S9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T9" s="15" t="s">
-        <v>938</v>
+      <c r="T9" s="158">
+        <v>45</v>
       </c>
       <c r="U9" s="113"/>
       <c r="V9" s="33"/>
@@ -55792,8 +55864,8 @@
       <c r="M10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N10" s="15" t="s">
-        <v>935</v>
+      <c r="N10" s="158">
+        <v>60</v>
       </c>
       <c r="O10" s="19"/>
       <c r="P10" s="5"/>
@@ -55804,8 +55876,8 @@
       <c r="S10" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T10" s="15" t="s">
-        <v>935</v>
+      <c r="T10" s="158">
+        <v>60</v>
       </c>
       <c r="U10" s="6"/>
       <c r="V10" s="6"/>
@@ -55862,8 +55934,8 @@
       <c r="M11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N11" s="15" t="s">
-        <v>935</v>
+      <c r="N11" s="158">
+        <v>60</v>
       </c>
       <c r="O11" s="5"/>
       <c r="P11" s="19"/>
@@ -55874,8 +55946,8 @@
       <c r="S11" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T11" s="15" t="s">
-        <v>935</v>
+      <c r="T11" s="158">
+        <v>60</v>
       </c>
       <c r="U11" s="112"/>
       <c r="V11" s="6"/>
@@ -55932,8 +56004,8 @@
       <c r="M12" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N12" s="15" t="s">
-        <v>936</v>
+      <c r="N12" s="158">
+        <v>30</v>
       </c>
       <c r="O12" s="19"/>
       <c r="P12" s="19"/>
@@ -55944,8 +56016,8 @@
       <c r="S12" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T12" s="15" t="s">
-        <v>936</v>
+      <c r="T12" s="158">
+        <v>30</v>
       </c>
       <c r="U12" s="6"/>
       <c r="V12" s="6"/>
@@ -56002,8 +56074,8 @@
       <c r="M13" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N13" s="15" t="s">
-        <v>935</v>
+      <c r="N13" s="158">
+        <v>60</v>
       </c>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
@@ -56014,8 +56086,8 @@
       <c r="S13" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T13" s="15" t="s">
-        <v>935</v>
+      <c r="T13" s="158">
+        <v>60</v>
       </c>
       <c r="U13" s="112"/>
       <c r="V13" s="6"/>
@@ -56072,8 +56144,8 @@
       <c r="M14" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N14" s="15" t="s">
-        <v>939</v>
+      <c r="N14" s="158">
+        <v>90</v>
       </c>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
@@ -56084,8 +56156,8 @@
       <c r="S14" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T14" s="15" t="s">
-        <v>939</v>
+      <c r="T14" s="158">
+        <v>90</v>
       </c>
       <c r="U14" s="6"/>
       <c r="V14" s="6"/>
@@ -56142,8 +56214,8 @@
       <c r="M15" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="N15" s="15" t="s">
-        <v>936</v>
+      <c r="N15" s="158">
+        <v>30</v>
       </c>
       <c r="O15" s="19"/>
       <c r="P15" s="116"/>
@@ -56154,8 +56226,8 @@
       <c r="S15" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="T15" s="15" t="s">
-        <v>936</v>
+      <c r="T15" s="158">
+        <v>30</v>
       </c>
       <c r="U15" s="6"/>
       <c r="V15" s="6"/>
@@ -56178,25 +56250,25 @@
       <c r="J16" s="31"/>
       <c r="K16" s="31"/>
       <c r="M16" s="7"/>
-      <c r="N16" s="15"/>
+      <c r="N16" s="158"/>
       <c r="S16" s="7"/>
-      <c r="T16" s="15"/>
+      <c r="T16" s="158"/>
     </row>
     <row r="17" spans="10:20">
       <c r="J17" s="31"/>
       <c r="K17" s="31"/>
       <c r="M17" s="7"/>
-      <c r="N17" s="15"/>
+      <c r="N17" s="158"/>
       <c r="S17" s="7"/>
-      <c r="T17" s="15"/>
+      <c r="T17" s="158"/>
     </row>
     <row r="18" spans="10:20">
       <c r="J18" s="31"/>
       <c r="K18" s="31"/>
       <c r="M18" s="7"/>
-      <c r="N18" s="15"/>
+      <c r="N18" s="158"/>
       <c r="S18" s="7"/>
-      <c r="T18" s="15"/>
+      <c r="T18" s="158"/>
     </row>
     <row r="19" spans="10:20">
       <c r="J19" s="31"/>

--- a/Archivos/Archivos_origen/Planeación contenido blog PaniPlay 2025.xlsx
+++ b/Archivos/Archivos_origen/Planeación contenido blog PaniPlay 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/jhor_caro_virtualsoft_tech/Documents/Documentos/Proyectos QuotaMedia/SEO/Planeacion SEO/Archivos enviados para octubre (con columnas)/Planeacion SEO Octubre/Planeacion SEO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QuotaMedia\Downloads\planeacion octubre editada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="11_7E2B824F2643A7D08604C3799E9C499CC994E440" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCE60E19-35C2-4B65-AA96-33C5E66C7551}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC8A802-47D6-4CF4-8CC3-C4934903EC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Octubre" sheetId="10" r:id="rId1"/>
@@ -290,7 +290,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -374,7 +374,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -390,10 +395,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -598,27 +599,27 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AJ1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="14.26953125" customWidth="1"/>
-    <col min="5" max="5" width="29.1796875" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" customWidth="1"/>
+    <col min="5" max="5" width="29.21875" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" customWidth="1"/>
-    <col min="8" max="8" width="23.7265625" customWidth="1"/>
-    <col min="9" max="9" width="22.7265625" customWidth="1"/>
-    <col min="10" max="10" width="26.54296875" customWidth="1"/>
-    <col min="11" max="11" width="23.81640625" customWidth="1"/>
-    <col min="13" max="14" width="12.54296875" style="28"/>
-    <col min="15" max="15" width="25.81640625" customWidth="1"/>
-    <col min="16" max="16" width="23.54296875" customWidth="1"/>
-    <col min="17" max="17" width="19.81640625" customWidth="1"/>
-    <col min="18" max="18" width="14.453125" customWidth="1"/>
-    <col min="19" max="20" width="14.453125" style="28" customWidth="1"/>
-    <col min="21" max="22" width="25.453125" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" customWidth="1"/>
+    <col min="8" max="8" width="23.77734375" customWidth="1"/>
+    <col min="9" max="9" width="22.77734375" customWidth="1"/>
+    <col min="10" max="10" width="26.5546875" customWidth="1"/>
+    <col min="11" max="11" width="23.77734375" customWidth="1"/>
+    <col min="13" max="14" width="12.5546875" style="28"/>
+    <col min="15" max="15" width="25.77734375" customWidth="1"/>
+    <col min="16" max="16" width="23.5546875" customWidth="1"/>
+    <col min="17" max="17" width="19.77734375" customWidth="1"/>
+    <col min="18" max="18" width="14.44140625" customWidth="1"/>
+    <col min="19" max="20" width="14.44140625" style="28" customWidth="1"/>
+    <col min="21" max="22" width="25.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="39">
+    <row r="1" spans="1:36" ht="39.6">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -700,7 +701,7 @@
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
     </row>
-    <row r="2" spans="1:36" ht="26">
+    <row r="2" spans="1:36" ht="27">
       <c r="A2" s="7" t="s">
         <v>23</v>
       </c>
@@ -725,7 +726,7 @@
         <v>44</v>
       </c>
       <c r="N2" s="27">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
@@ -756,7 +757,7 @@
       <c r="AI2" s="7"/>
       <c r="AJ2" s="7"/>
     </row>
-    <row r="3" spans="1:36" ht="29">
+    <row r="3" spans="1:36" ht="28.8">
       <c r="A3" s="5" t="s">
         <v>25</v>
       </c>
@@ -785,7 +786,7 @@
         <v>44</v>
       </c>
       <c r="N3" s="27">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="O3" s="13"/>
       <c r="P3" s="13"/>
@@ -816,7 +817,7 @@
       <c r="AI3" s="7"/>
       <c r="AJ3" s="7"/>
     </row>
-    <row r="4" spans="1:36" ht="29">
+    <row r="4" spans="1:36" ht="28.8">
       <c r="A4" s="5" t="s">
         <v>25</v>
       </c>
@@ -857,7 +858,7 @@
         <v>44</v>
       </c>
       <c r="T4" s="27">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="U4" s="16"/>
       <c r="V4" s="3"/>
@@ -876,7 +877,7 @@
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
     </row>
-    <row r="5" spans="1:36" ht="14.5">
+    <row r="5" spans="1:36" ht="14.4">
       <c r="A5" s="7" t="s">
         <v>23</v>
       </c>
@@ -901,7 +902,7 @@
         <v>44</v>
       </c>
       <c r="N5" s="27">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
@@ -913,7 +914,7 @@
         <v>44</v>
       </c>
       <c r="T5" s="27">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="U5" s="11"/>
       <c r="V5" s="7"/>
@@ -932,7 +933,7 @@
       <c r="AI5" s="7"/>
       <c r="AJ5" s="7"/>
     </row>
-    <row r="6" spans="1:36" ht="26">
+    <row r="6" spans="1:36" ht="27">
       <c r="A6" s="7" t="s">
         <v>23</v>
       </c>
@@ -957,7 +958,7 @@
         <v>44</v>
       </c>
       <c r="N6" s="27">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
@@ -988,7 +989,7 @@
       <c r="AI6" s="7"/>
       <c r="AJ6" s="7"/>
     </row>
-    <row r="7" spans="1:36" ht="14.5">
+    <row r="7" spans="1:36" ht="14.4">
       <c r="A7" s="7" t="s">
         <v>23</v>
       </c>
@@ -1013,7 +1014,7 @@
         <v>44</v>
       </c>
       <c r="N7" s="27">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
@@ -1025,7 +1026,7 @@
         <v>44</v>
       </c>
       <c r="T7" s="27">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="U7" s="11"/>
       <c r="V7" s="7"/>
@@ -1044,7 +1045,7 @@
       <c r="AI7" s="7"/>
       <c r="AJ7" s="7"/>
     </row>
-    <row r="8" spans="1:36" ht="29">
+    <row r="8" spans="1:36" ht="28.8">
       <c r="A8" s="18" t="s">
         <v>25</v>
       </c>
@@ -1085,7 +1086,7 @@
         <v>44</v>
       </c>
       <c r="T8" s="27">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="U8" s="16"/>
       <c r="V8" s="13"/>
@@ -1133,7 +1134,7 @@
         <v>44</v>
       </c>
       <c r="N9" s="27">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="O9" s="18"/>
       <c r="P9" s="19"/>
@@ -1164,7 +1165,7 @@
       <c r="AI9" s="16"/>
       <c r="AJ9" s="16"/>
     </row>
-    <row r="10" spans="1:36" ht="43.5">
+    <row r="10" spans="1:36" ht="43.2">
       <c r="A10" s="18" t="s">
         <v>25</v>
       </c>
@@ -1193,7 +1194,7 @@
         <v>44</v>
       </c>
       <c r="N10" s="27">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="O10" s="18"/>
       <c r="P10" s="18"/>
@@ -1205,7 +1206,7 @@
         <v>44</v>
       </c>
       <c r="T10" s="27">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="U10" s="16"/>
       <c r="V10" s="13"/>
@@ -1224,7 +1225,7 @@
       <c r="AI10" s="13"/>
       <c r="AJ10" s="13"/>
     </row>
-    <row r="11" spans="1:36" ht="29">
+    <row r="11" spans="1:36" ht="28.8">
       <c r="A11" s="18" t="s">
         <v>25</v>
       </c>
@@ -1253,7 +1254,7 @@
         <v>44</v>
       </c>
       <c r="N11" s="27">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="O11" s="18"/>
       <c r="P11" s="19"/>
@@ -1284,7 +1285,7 @@
       <c r="AI11" s="13"/>
       <c r="AJ11" s="13"/>
     </row>
-    <row r="12" spans="1:36" ht="29">
+    <row r="12" spans="1:36" ht="28.8">
       <c r="A12" s="18" t="s">
         <v>25</v>
       </c>
@@ -1325,7 +1326,7 @@
         <v>44</v>
       </c>
       <c r="T12" s="27">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="U12" s="18"/>
       <c r="V12" s="13"/>
@@ -1344,7 +1345,7 @@
       <c r="AI12" s="13"/>
       <c r="AJ12" s="13"/>
     </row>
-    <row r="13" spans="1:36" ht="29">
+    <row r="13" spans="1:36" ht="28.8">
       <c r="A13" s="18" t="s">
         <v>25</v>
       </c>
@@ -1373,7 +1374,7 @@
         <v>44</v>
       </c>
       <c r="N13" s="27">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="O13" s="13"/>
       <c r="P13" s="16"/>
@@ -1404,7 +1405,7 @@
       <c r="AI13" s="16"/>
       <c r="AJ13" s="16"/>
     </row>
-    <row r="14" spans="1:36" ht="29">
+    <row r="14" spans="1:36" ht="28.8">
       <c r="A14" s="18" t="s">
         <v>25</v>
       </c>
@@ -1429,11 +1430,11 @@
       <c r="L14" s="15">
         <v>45952</v>
       </c>
-      <c r="M14" s="26" t="s">
+      <c r="M14" s="29" t="s">
         <v>44</v>
       </c>
       <c r="N14" s="29">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="O14" s="18"/>
       <c r="P14" s="18"/>
@@ -1441,11 +1442,11 @@
       <c r="R14" s="15">
         <v>45954</v>
       </c>
-      <c r="S14" s="26" t="s">
+      <c r="S14" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T14" s="29">
-        <v>15</v>
+      <c r="T14" s="30">
+        <v>30</v>
       </c>
       <c r="U14" s="18"/>
       <c r="V14" s="18"/>
@@ -1464,7 +1465,7 @@
       <c r="AI14" s="16"/>
       <c r="AJ14" s="16"/>
     </row>
-    <row r="15" spans="1:36" ht="29">
+    <row r="15" spans="1:36" ht="28.8">
       <c r="A15" s="18" t="s">
         <v>25</v>
       </c>
@@ -1489,11 +1490,11 @@
       <c r="L15" s="15">
         <v>45953</v>
       </c>
-      <c r="M15" s="26" t="s">
+      <c r="M15" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="N15" s="28">
-        <v>30</v>
+      <c r="N15" s="29">
+        <v>60</v>
       </c>
       <c r="O15" s="18"/>
       <c r="P15" s="24"/>
@@ -1501,10 +1502,10 @@
       <c r="R15" s="15">
         <v>45954</v>
       </c>
-      <c r="S15" s="26" t="s">
+      <c r="S15" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="T15" s="28">
+      <c r="T15" s="29">
         <v>30</v>
       </c>
       <c r="U15" s="14"/>
@@ -1524,3953 +1525,3953 @@
       <c r="AI15" s="16"/>
       <c r="AJ15" s="16"/>
     </row>
-    <row r="16" spans="1:36" ht="12.5">
+    <row r="16" spans="1:36" ht="13.2">
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="10:11" ht="12.5">
+    <row r="17" spans="10:11" ht="13.2">
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
     </row>
-    <row r="18" spans="10:11" ht="12.5">
+    <row r="18" spans="10:11" ht="13.2">
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="10:11" ht="12.5">
+    <row r="19" spans="10:11" ht="13.2">
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="10:11" ht="12.5">
+    <row r="20" spans="10:11" ht="13.2">
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
     </row>
-    <row r="21" spans="10:11" ht="12.5">
+    <row r="21" spans="10:11" ht="13.2">
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="10:11" ht="12.5">
+    <row r="22" spans="10:11" ht="13.2">
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="10:11" ht="12.5">
+    <row r="23" spans="10:11" ht="13.2">
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
     </row>
-    <row r="24" spans="10:11" ht="12.5">
+    <row r="24" spans="10:11" ht="13.2">
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="10:11" ht="12.5">
+    <row r="25" spans="10:11" ht="13.2">
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
     </row>
-    <row r="26" spans="10:11" ht="12.5">
+    <row r="26" spans="10:11" ht="13.2">
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="10:11" ht="12.5">
+    <row r="27" spans="10:11" ht="13.2">
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
     </row>
-    <row r="28" spans="10:11" ht="12.5">
+    <row r="28" spans="10:11" ht="13.2">
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="10:11" ht="12.5">
+    <row r="29" spans="10:11" ht="13.2">
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
     </row>
-    <row r="30" spans="10:11" ht="12.5">
+    <row r="30" spans="10:11" ht="13.2">
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
     </row>
-    <row r="31" spans="10:11" ht="12.5">
+    <row r="31" spans="10:11" ht="13.2">
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
     </row>
-    <row r="32" spans="10:11" ht="12.5">
+    <row r="32" spans="10:11" ht="13.2">
       <c r="J32" s="6"/>
       <c r="K32" s="6"/>
     </row>
-    <row r="33" spans="10:11" ht="12.5">
+    <row r="33" spans="10:11" ht="13.2">
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
     </row>
-    <row r="34" spans="10:11" ht="12.5">
+    <row r="34" spans="10:11" ht="13.2">
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
     </row>
-    <row r="35" spans="10:11" ht="12.5">
+    <row r="35" spans="10:11" ht="13.2">
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" spans="10:11" ht="12.5">
+    <row r="36" spans="10:11" ht="13.2">
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
     </row>
-    <row r="37" spans="10:11" ht="12.5">
+    <row r="37" spans="10:11" ht="13.2">
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="10:11" ht="12.5">
+    <row r="38" spans="10:11" ht="13.2">
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
     </row>
-    <row r="39" spans="10:11" ht="12.5">
+    <row r="39" spans="10:11" ht="13.2">
       <c r="J39" s="6"/>
       <c r="K39" s="6"/>
     </row>
-    <row r="40" spans="10:11" ht="12.5">
+    <row r="40" spans="10:11" ht="13.2">
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
     </row>
-    <row r="41" spans="10:11" ht="12.5">
+    <row r="41" spans="10:11" ht="13.2">
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
     </row>
-    <row r="42" spans="10:11" ht="12.5">
+    <row r="42" spans="10:11" ht="13.2">
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" spans="10:11" ht="12.5">
+    <row r="43" spans="10:11" ht="13.2">
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
     </row>
-    <row r="44" spans="10:11" ht="12.5">
+    <row r="44" spans="10:11" ht="13.2">
       <c r="J44" s="6"/>
       <c r="K44" s="6"/>
     </row>
-    <row r="45" spans="10:11" ht="12.5">
+    <row r="45" spans="10:11" ht="13.2">
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
     </row>
-    <row r="46" spans="10:11" ht="12.5">
+    <row r="46" spans="10:11" ht="13.2">
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
     </row>
-    <row r="47" spans="10:11" ht="12.5">
+    <row r="47" spans="10:11" ht="13.2">
       <c r="J47" s="6"/>
       <c r="K47" s="6"/>
     </row>
-    <row r="48" spans="10:11" ht="12.5">
+    <row r="48" spans="10:11" ht="13.2">
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
     </row>
-    <row r="49" spans="10:11" ht="12.5">
+    <row r="49" spans="10:11" ht="13.2">
       <c r="J49" s="6"/>
       <c r="K49" s="6"/>
     </row>
-    <row r="50" spans="10:11" ht="12.5">
+    <row r="50" spans="10:11" ht="13.2">
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
     </row>
-    <row r="51" spans="10:11" ht="12.5">
+    <row r="51" spans="10:11" ht="13.2">
       <c r="J51" s="6"/>
       <c r="K51" s="6"/>
     </row>
-    <row r="52" spans="10:11" ht="12.5">
+    <row r="52" spans="10:11" ht="13.2">
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
     </row>
-    <row r="53" spans="10:11" ht="12.5">
+    <row r="53" spans="10:11" ht="13.2">
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
     </row>
-    <row r="54" spans="10:11" ht="12.5">
+    <row r="54" spans="10:11" ht="13.2">
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" spans="10:11" ht="12.5">
+    <row r="55" spans="10:11" ht="13.2">
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" spans="10:11" ht="12.5">
+    <row r="56" spans="10:11" ht="13.2">
       <c r="J56" s="6"/>
       <c r="K56" s="6"/>
     </row>
-    <row r="57" spans="10:11" ht="12.5">
+    <row r="57" spans="10:11" ht="13.2">
       <c r="J57" s="6"/>
       <c r="K57" s="6"/>
     </row>
-    <row r="58" spans="10:11" ht="12.5">
+    <row r="58" spans="10:11" ht="13.2">
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
     </row>
-    <row r="59" spans="10:11" ht="12.5">
+    <row r="59" spans="10:11" ht="13.2">
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
     </row>
-    <row r="60" spans="10:11" ht="12.5">
+    <row r="60" spans="10:11" ht="13.2">
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
     </row>
-    <row r="61" spans="10:11" ht="12.5">
+    <row r="61" spans="10:11" ht="13.2">
       <c r="J61" s="6"/>
       <c r="K61" s="6"/>
     </row>
-    <row r="62" spans="10:11" ht="12.5">
+    <row r="62" spans="10:11" ht="13.2">
       <c r="J62" s="6"/>
       <c r="K62" s="6"/>
     </row>
-    <row r="63" spans="10:11" ht="12.5">
+    <row r="63" spans="10:11" ht="13.2">
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
     </row>
-    <row r="64" spans="10:11" ht="12.5">
+    <row r="64" spans="10:11" ht="13.2">
       <c r="J64" s="6"/>
       <c r="K64" s="6"/>
     </row>
-    <row r="65" spans="10:11" ht="12.5">
+    <row r="65" spans="10:11" ht="13.2">
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
     </row>
-    <row r="66" spans="10:11" ht="12.5">
+    <row r="66" spans="10:11" ht="13.2">
       <c r="J66" s="6"/>
       <c r="K66" s="6"/>
     </row>
-    <row r="67" spans="10:11" ht="12.5">
+    <row r="67" spans="10:11" ht="13.2">
       <c r="J67" s="6"/>
       <c r="K67" s="6"/>
     </row>
-    <row r="68" spans="10:11" ht="12.5">
+    <row r="68" spans="10:11" ht="13.2">
       <c r="J68" s="6"/>
       <c r="K68" s="6"/>
     </row>
-    <row r="69" spans="10:11" ht="12.5">
+    <row r="69" spans="10:11" ht="13.2">
       <c r="J69" s="6"/>
       <c r="K69" s="6"/>
     </row>
-    <row r="70" spans="10:11" ht="12.5">
+    <row r="70" spans="10:11" ht="13.2">
       <c r="J70" s="6"/>
       <c r="K70" s="6"/>
     </row>
-    <row r="71" spans="10:11" ht="12.5">
+    <row r="71" spans="10:11" ht="13.2">
       <c r="J71" s="6"/>
       <c r="K71" s="6"/>
     </row>
-    <row r="72" spans="10:11" ht="12.5">
+    <row r="72" spans="10:11" ht="13.2">
       <c r="J72" s="6"/>
       <c r="K72" s="6"/>
     </row>
-    <row r="73" spans="10:11" ht="12.5">
+    <row r="73" spans="10:11" ht="13.2">
       <c r="J73" s="6"/>
       <c r="K73" s="6"/>
     </row>
-    <row r="74" spans="10:11" ht="12.5">
+    <row r="74" spans="10:11" ht="13.2">
       <c r="J74" s="6"/>
       <c r="K74" s="6"/>
     </row>
-    <row r="75" spans="10:11" ht="12.5">
+    <row r="75" spans="10:11" ht="13.2">
       <c r="J75" s="6"/>
       <c r="K75" s="6"/>
     </row>
-    <row r="76" spans="10:11" ht="12.5">
+    <row r="76" spans="10:11" ht="13.2">
       <c r="J76" s="6"/>
       <c r="K76" s="6"/>
     </row>
-    <row r="77" spans="10:11" ht="12.5">
+    <row r="77" spans="10:11" ht="13.2">
       <c r="J77" s="6"/>
       <c r="K77" s="6"/>
     </row>
-    <row r="78" spans="10:11" ht="12.5">
+    <row r="78" spans="10:11" ht="13.2">
       <c r="J78" s="6"/>
       <c r="K78" s="6"/>
     </row>
-    <row r="79" spans="10:11" ht="12.5">
+    <row r="79" spans="10:11" ht="13.2">
       <c r="J79" s="6"/>
       <c r="K79" s="6"/>
     </row>
-    <row r="80" spans="10:11" ht="12.5">
+    <row r="80" spans="10:11" ht="13.2">
       <c r="J80" s="6"/>
       <c r="K80" s="6"/>
     </row>
-    <row r="81" spans="10:11" ht="12.5">
+    <row r="81" spans="10:11" ht="13.2">
       <c r="J81" s="6"/>
       <c r="K81" s="6"/>
     </row>
-    <row r="82" spans="10:11" ht="12.5">
+    <row r="82" spans="10:11" ht="13.2">
       <c r="J82" s="6"/>
       <c r="K82" s="6"/>
     </row>
-    <row r="83" spans="10:11" ht="12.5">
+    <row r="83" spans="10:11" ht="13.2">
       <c r="J83" s="6"/>
       <c r="K83" s="6"/>
     </row>
-    <row r="84" spans="10:11" ht="12.5">
+    <row r="84" spans="10:11" ht="13.2">
       <c r="J84" s="6"/>
       <c r="K84" s="6"/>
     </row>
-    <row r="85" spans="10:11" ht="12.5">
+    <row r="85" spans="10:11" ht="13.2">
       <c r="J85" s="6"/>
       <c r="K85" s="6"/>
     </row>
-    <row r="86" spans="10:11" ht="12.5">
+    <row r="86" spans="10:11" ht="13.2">
       <c r="J86" s="6"/>
       <c r="K86" s="6"/>
     </row>
-    <row r="87" spans="10:11" ht="12.5">
+    <row r="87" spans="10:11" ht="13.2">
       <c r="J87" s="6"/>
       <c r="K87" s="6"/>
     </row>
-    <row r="88" spans="10:11" ht="12.5">
+    <row r="88" spans="10:11" ht="13.2">
       <c r="J88" s="6"/>
       <c r="K88" s="6"/>
     </row>
-    <row r="89" spans="10:11" ht="12.5">
+    <row r="89" spans="10:11" ht="13.2">
       <c r="J89" s="6"/>
       <c r="K89" s="6"/>
     </row>
-    <row r="90" spans="10:11" ht="12.5">
+    <row r="90" spans="10:11" ht="13.2">
       <c r="J90" s="6"/>
       <c r="K90" s="6"/>
     </row>
-    <row r="91" spans="10:11" ht="12.5">
+    <row r="91" spans="10:11" ht="13.2">
       <c r="J91" s="6"/>
       <c r="K91" s="6"/>
     </row>
-    <row r="92" spans="10:11" ht="12.5">
+    <row r="92" spans="10:11" ht="13.2">
       <c r="J92" s="6"/>
       <c r="K92" s="6"/>
     </row>
-    <row r="93" spans="10:11" ht="12.5">
+    <row r="93" spans="10:11" ht="13.2">
       <c r="J93" s="6"/>
       <c r="K93" s="6"/>
     </row>
-    <row r="94" spans="10:11" ht="12.5">
+    <row r="94" spans="10:11" ht="13.2">
       <c r="J94" s="6"/>
       <c r="K94" s="6"/>
     </row>
-    <row r="95" spans="10:11" ht="12.5">
+    <row r="95" spans="10:11" ht="13.2">
       <c r="J95" s="6"/>
       <c r="K95" s="6"/>
     </row>
-    <row r="96" spans="10:11" ht="12.5">
+    <row r="96" spans="10:11" ht="13.2">
       <c r="J96" s="6"/>
       <c r="K96" s="6"/>
     </row>
-    <row r="97" spans="10:11" ht="12.5">
+    <row r="97" spans="10:11" ht="13.2">
       <c r="J97" s="6"/>
       <c r="K97" s="6"/>
     </row>
-    <row r="98" spans="10:11" ht="12.5">
+    <row r="98" spans="10:11" ht="13.2">
       <c r="J98" s="6"/>
       <c r="K98" s="6"/>
     </row>
-    <row r="99" spans="10:11" ht="12.5">
+    <row r="99" spans="10:11" ht="13.2">
       <c r="J99" s="6"/>
       <c r="K99" s="6"/>
     </row>
-    <row r="100" spans="10:11" ht="12.5">
+    <row r="100" spans="10:11" ht="13.2">
       <c r="J100" s="6"/>
       <c r="K100" s="6"/>
     </row>
-    <row r="101" spans="10:11" ht="12.5">
+    <row r="101" spans="10:11" ht="13.2">
       <c r="J101" s="6"/>
       <c r="K101" s="6"/>
     </row>
-    <row r="102" spans="10:11" ht="12.5">
+    <row r="102" spans="10:11" ht="13.2">
       <c r="J102" s="6"/>
       <c r="K102" s="6"/>
     </row>
-    <row r="103" spans="10:11" ht="12.5">
+    <row r="103" spans="10:11" ht="13.2">
       <c r="J103" s="6"/>
       <c r="K103" s="6"/>
     </row>
-    <row r="104" spans="10:11" ht="12.5">
+    <row r="104" spans="10:11" ht="13.2">
       <c r="J104" s="6"/>
       <c r="K104" s="6"/>
     </row>
-    <row r="105" spans="10:11" ht="12.5">
+    <row r="105" spans="10:11" ht="13.2">
       <c r="J105" s="6"/>
       <c r="K105" s="6"/>
     </row>
-    <row r="106" spans="10:11" ht="12.5">
+    <row r="106" spans="10:11" ht="13.2">
       <c r="J106" s="6"/>
       <c r="K106" s="6"/>
     </row>
-    <row r="107" spans="10:11" ht="12.5">
+    <row r="107" spans="10:11" ht="13.2">
       <c r="J107" s="6"/>
       <c r="K107" s="6"/>
     </row>
-    <row r="108" spans="10:11" ht="12.5">
+    <row r="108" spans="10:11" ht="13.2">
       <c r="J108" s="6"/>
       <c r="K108" s="6"/>
     </row>
-    <row r="109" spans="10:11" ht="12.5">
+    <row r="109" spans="10:11" ht="13.2">
       <c r="J109" s="6"/>
       <c r="K109" s="6"/>
     </row>
-    <row r="110" spans="10:11" ht="12.5">
+    <row r="110" spans="10:11" ht="13.2">
       <c r="J110" s="6"/>
       <c r="K110" s="6"/>
     </row>
-    <row r="111" spans="10:11" ht="12.5">
+    <row r="111" spans="10:11" ht="13.2">
       <c r="J111" s="6"/>
       <c r="K111" s="6"/>
     </row>
-    <row r="112" spans="10:11" ht="12.5">
+    <row r="112" spans="10:11" ht="13.2">
       <c r="J112" s="6"/>
       <c r="K112" s="6"/>
     </row>
-    <row r="113" spans="10:11" ht="12.5">
+    <row r="113" spans="10:11" ht="13.2">
       <c r="J113" s="6"/>
       <c r="K113" s="6"/>
     </row>
-    <row r="114" spans="10:11" ht="12.5">
+    <row r="114" spans="10:11" ht="13.2">
       <c r="J114" s="6"/>
       <c r="K114" s="6"/>
     </row>
-    <row r="115" spans="10:11" ht="12.5">
+    <row r="115" spans="10:11" ht="13.2">
       <c r="J115" s="6"/>
       <c r="K115" s="6"/>
     </row>
-    <row r="116" spans="10:11" ht="12.5">
+    <row r="116" spans="10:11" ht="13.2">
       <c r="J116" s="6"/>
       <c r="K116" s="6"/>
     </row>
-    <row r="117" spans="10:11" ht="12.5">
+    <row r="117" spans="10:11" ht="13.2">
       <c r="J117" s="6"/>
       <c r="K117" s="6"/>
     </row>
-    <row r="118" spans="10:11" ht="12.5">
+    <row r="118" spans="10:11" ht="13.2">
       <c r="J118" s="6"/>
       <c r="K118" s="6"/>
     </row>
-    <row r="119" spans="10:11" ht="12.5">
+    <row r="119" spans="10:11" ht="13.2">
       <c r="J119" s="6"/>
       <c r="K119" s="6"/>
     </row>
-    <row r="120" spans="10:11" ht="12.5">
+    <row r="120" spans="10:11" ht="13.2">
       <c r="J120" s="6"/>
       <c r="K120" s="6"/>
     </row>
-    <row r="121" spans="10:11" ht="12.5">
+    <row r="121" spans="10:11" ht="13.2">
       <c r="J121" s="6"/>
       <c r="K121" s="6"/>
     </row>
-    <row r="122" spans="10:11" ht="12.5">
+    <row r="122" spans="10:11" ht="13.2">
       <c r="J122" s="6"/>
       <c r="K122" s="6"/>
     </row>
-    <row r="123" spans="10:11" ht="12.5">
+    <row r="123" spans="10:11" ht="13.2">
       <c r="J123" s="6"/>
       <c r="K123" s="6"/>
     </row>
-    <row r="124" spans="10:11" ht="12.5">
+    <row r="124" spans="10:11" ht="13.2">
       <c r="J124" s="6"/>
       <c r="K124" s="6"/>
     </row>
-    <row r="125" spans="10:11" ht="12.5">
+    <row r="125" spans="10:11" ht="13.2">
       <c r="J125" s="6"/>
       <c r="K125" s="6"/>
     </row>
-    <row r="126" spans="10:11" ht="12.5">
+    <row r="126" spans="10:11" ht="13.2">
       <c r="J126" s="6"/>
       <c r="K126" s="6"/>
     </row>
-    <row r="127" spans="10:11" ht="12.5">
+    <row r="127" spans="10:11" ht="13.2">
       <c r="J127" s="6"/>
       <c r="K127" s="6"/>
     </row>
-    <row r="128" spans="10:11" ht="12.5">
+    <row r="128" spans="10:11" ht="13.2">
       <c r="J128" s="6"/>
       <c r="K128" s="6"/>
     </row>
-    <row r="129" spans="10:11" ht="12.5">
+    <row r="129" spans="10:11" ht="13.2">
       <c r="J129" s="6"/>
       <c r="K129" s="6"/>
     </row>
-    <row r="130" spans="10:11" ht="12.5">
+    <row r="130" spans="10:11" ht="13.2">
       <c r="J130" s="6"/>
       <c r="K130" s="6"/>
     </row>
-    <row r="131" spans="10:11" ht="12.5">
+    <row r="131" spans="10:11" ht="13.2">
       <c r="J131" s="6"/>
       <c r="K131" s="6"/>
     </row>
-    <row r="132" spans="10:11" ht="12.5">
+    <row r="132" spans="10:11" ht="13.2">
       <c r="J132" s="6"/>
       <c r="K132" s="6"/>
     </row>
-    <row r="133" spans="10:11" ht="12.5">
+    <row r="133" spans="10:11" ht="13.2">
       <c r="J133" s="6"/>
       <c r="K133" s="6"/>
     </row>
-    <row r="134" spans="10:11" ht="12.5">
+    <row r="134" spans="10:11" ht="13.2">
       <c r="J134" s="6"/>
       <c r="K134" s="6"/>
     </row>
-    <row r="135" spans="10:11" ht="12.5">
+    <row r="135" spans="10:11" ht="13.2">
       <c r="J135" s="6"/>
       <c r="K135" s="6"/>
     </row>
-    <row r="136" spans="10:11" ht="12.5">
+    <row r="136" spans="10:11" ht="13.2">
       <c r="J136" s="6"/>
       <c r="K136" s="6"/>
     </row>
-    <row r="137" spans="10:11" ht="12.5">
+    <row r="137" spans="10:11" ht="13.2">
       <c r="J137" s="6"/>
       <c r="K137" s="6"/>
     </row>
-    <row r="138" spans="10:11" ht="12.5">
+    <row r="138" spans="10:11" ht="13.2">
       <c r="J138" s="6"/>
       <c r="K138" s="6"/>
     </row>
-    <row r="139" spans="10:11" ht="12.5">
+    <row r="139" spans="10:11" ht="13.2">
       <c r="J139" s="6"/>
       <c r="K139" s="6"/>
     </row>
-    <row r="140" spans="10:11" ht="12.5">
+    <row r="140" spans="10:11" ht="13.2">
       <c r="J140" s="6"/>
       <c r="K140" s="6"/>
     </row>
-    <row r="141" spans="10:11" ht="12.5">
+    <row r="141" spans="10:11" ht="13.2">
       <c r="J141" s="6"/>
       <c r="K141" s="6"/>
     </row>
-    <row r="142" spans="10:11" ht="12.5">
+    <row r="142" spans="10:11" ht="13.2">
       <c r="J142" s="6"/>
       <c r="K142" s="6"/>
     </row>
-    <row r="143" spans="10:11" ht="12.5">
+    <row r="143" spans="10:11" ht="13.2">
       <c r="J143" s="6"/>
       <c r="K143" s="6"/>
     </row>
-    <row r="144" spans="10:11" ht="12.5">
+    <row r="144" spans="10:11" ht="13.2">
       <c r="J144" s="6"/>
       <c r="K144" s="6"/>
     </row>
-    <row r="145" spans="10:11" ht="12.5">
+    <row r="145" spans="10:11" ht="13.2">
       <c r="J145" s="6"/>
       <c r="K145" s="6"/>
     </row>
-    <row r="146" spans="10:11" ht="12.5">
+    <row r="146" spans="10:11" ht="13.2">
       <c r="J146" s="6"/>
       <c r="K146" s="6"/>
     </row>
-    <row r="147" spans="10:11" ht="12.5">
+    <row r="147" spans="10:11" ht="13.2">
       <c r="J147" s="6"/>
       <c r="K147" s="6"/>
     </row>
-    <row r="148" spans="10:11" ht="12.5">
+    <row r="148" spans="10:11" ht="13.2">
       <c r="J148" s="6"/>
       <c r="K148" s="6"/>
     </row>
-    <row r="149" spans="10:11" ht="12.5">
+    <row r="149" spans="10:11" ht="13.2">
       <c r="J149" s="6"/>
       <c r="K149" s="6"/>
     </row>
-    <row r="150" spans="10:11" ht="12.5">
+    <row r="150" spans="10:11" ht="13.2">
       <c r="J150" s="6"/>
       <c r="K150" s="6"/>
     </row>
-    <row r="151" spans="10:11" ht="12.5">
+    <row r="151" spans="10:11" ht="13.2">
       <c r="J151" s="6"/>
       <c r="K151" s="6"/>
     </row>
-    <row r="152" spans="10:11" ht="12.5">
+    <row r="152" spans="10:11" ht="13.2">
       <c r="J152" s="6"/>
       <c r="K152" s="6"/>
     </row>
-    <row r="153" spans="10:11" ht="12.5">
+    <row r="153" spans="10:11" ht="13.2">
       <c r="J153" s="6"/>
       <c r="K153" s="6"/>
     </row>
-    <row r="154" spans="10:11" ht="12.5">
+    <row r="154" spans="10:11" ht="13.2">
       <c r="J154" s="6"/>
       <c r="K154" s="6"/>
     </row>
-    <row r="155" spans="10:11" ht="12.5">
+    <row r="155" spans="10:11" ht="13.2">
       <c r="J155" s="6"/>
       <c r="K155" s="6"/>
     </row>
-    <row r="156" spans="10:11" ht="12.5">
+    <row r="156" spans="10:11" ht="13.2">
       <c r="J156" s="6"/>
       <c r="K156" s="6"/>
     </row>
-    <row r="157" spans="10:11" ht="12.5">
+    <row r="157" spans="10:11" ht="13.2">
       <c r="J157" s="6"/>
       <c r="K157" s="6"/>
     </row>
-    <row r="158" spans="10:11" ht="12.5">
+    <row r="158" spans="10:11" ht="13.2">
       <c r="J158" s="6"/>
       <c r="K158" s="6"/>
     </row>
-    <row r="159" spans="10:11" ht="12.5">
+    <row r="159" spans="10:11" ht="13.2">
       <c r="J159" s="6"/>
       <c r="K159" s="6"/>
     </row>
-    <row r="160" spans="10:11" ht="12.5">
+    <row r="160" spans="10:11" ht="13.2">
       <c r="J160" s="6"/>
       <c r="K160" s="6"/>
     </row>
-    <row r="161" spans="10:11" ht="12.5">
+    <row r="161" spans="10:11" ht="13.2">
       <c r="J161" s="6"/>
       <c r="K161" s="6"/>
     </row>
-    <row r="162" spans="10:11" ht="12.5">
+    <row r="162" spans="10:11" ht="13.2">
       <c r="J162" s="6"/>
       <c r="K162" s="6"/>
     </row>
-    <row r="163" spans="10:11" ht="12.5">
+    <row r="163" spans="10:11" ht="13.2">
       <c r="J163" s="6"/>
       <c r="K163" s="6"/>
     </row>
-    <row r="164" spans="10:11" ht="12.5">
+    <row r="164" spans="10:11" ht="13.2">
       <c r="J164" s="6"/>
       <c r="K164" s="6"/>
     </row>
-    <row r="165" spans="10:11" ht="12.5">
+    <row r="165" spans="10:11" ht="13.2">
       <c r="J165" s="6"/>
       <c r="K165" s="6"/>
     </row>
-    <row r="166" spans="10:11" ht="12.5">
+    <row r="166" spans="10:11" ht="13.2">
       <c r="J166" s="6"/>
       <c r="K166" s="6"/>
     </row>
-    <row r="167" spans="10:11" ht="12.5">
+    <row r="167" spans="10:11" ht="13.2">
       <c r="J167" s="6"/>
       <c r="K167" s="6"/>
     </row>
-    <row r="168" spans="10:11" ht="12.5">
+    <row r="168" spans="10:11" ht="13.2">
       <c r="J168" s="6"/>
       <c r="K168" s="6"/>
     </row>
-    <row r="169" spans="10:11" ht="12.5">
+    <row r="169" spans="10:11" ht="13.2">
       <c r="J169" s="6"/>
       <c r="K169" s="6"/>
     </row>
-    <row r="170" spans="10:11" ht="12.5">
+    <row r="170" spans="10:11" ht="13.2">
       <c r="J170" s="6"/>
       <c r="K170" s="6"/>
     </row>
-    <row r="171" spans="10:11" ht="12.5">
+    <row r="171" spans="10:11" ht="13.2">
       <c r="J171" s="6"/>
       <c r="K171" s="6"/>
     </row>
-    <row r="172" spans="10:11" ht="12.5">
+    <row r="172" spans="10:11" ht="13.2">
       <c r="J172" s="6"/>
       <c r="K172" s="6"/>
     </row>
-    <row r="173" spans="10:11" ht="12.5">
+    <row r="173" spans="10:11" ht="13.2">
       <c r="J173" s="6"/>
       <c r="K173" s="6"/>
     </row>
-    <row r="174" spans="10:11" ht="12.5">
+    <row r="174" spans="10:11" ht="13.2">
       <c r="J174" s="6"/>
       <c r="K174" s="6"/>
     </row>
-    <row r="175" spans="10:11" ht="12.5">
+    <row r="175" spans="10:11" ht="13.2">
       <c r="J175" s="6"/>
       <c r="K175" s="6"/>
     </row>
-    <row r="176" spans="10:11" ht="12.5">
+    <row r="176" spans="10:11" ht="13.2">
       <c r="J176" s="6"/>
       <c r="K176" s="6"/>
     </row>
-    <row r="177" spans="10:11" ht="12.5">
+    <row r="177" spans="10:11" ht="13.2">
       <c r="J177" s="6"/>
       <c r="K177" s="6"/>
     </row>
-    <row r="178" spans="10:11" ht="12.5">
+    <row r="178" spans="10:11" ht="13.2">
       <c r="J178" s="6"/>
       <c r="K178" s="6"/>
     </row>
-    <row r="179" spans="10:11" ht="12.5">
+    <row r="179" spans="10:11" ht="13.2">
       <c r="J179" s="6"/>
       <c r="K179" s="6"/>
     </row>
-    <row r="180" spans="10:11" ht="12.5">
+    <row r="180" spans="10:11" ht="13.2">
       <c r="J180" s="6"/>
       <c r="K180" s="6"/>
     </row>
-    <row r="181" spans="10:11" ht="12.5">
+    <row r="181" spans="10:11" ht="13.2">
       <c r="J181" s="6"/>
       <c r="K181" s="6"/>
     </row>
-    <row r="182" spans="10:11" ht="12.5">
+    <row r="182" spans="10:11" ht="13.2">
       <c r="J182" s="6"/>
       <c r="K182" s="6"/>
     </row>
-    <row r="183" spans="10:11" ht="12.5">
+    <row r="183" spans="10:11" ht="13.2">
       <c r="J183" s="6"/>
       <c r="K183" s="6"/>
     </row>
-    <row r="184" spans="10:11" ht="12.5">
+    <row r="184" spans="10:11" ht="13.2">
       <c r="J184" s="6"/>
       <c r="K184" s="6"/>
     </row>
-    <row r="185" spans="10:11" ht="12.5">
+    <row r="185" spans="10:11" ht="13.2">
       <c r="J185" s="6"/>
       <c r="K185" s="6"/>
     </row>
-    <row r="186" spans="10:11" ht="12.5">
+    <row r="186" spans="10:11" ht="13.2">
       <c r="J186" s="6"/>
       <c r="K186" s="6"/>
     </row>
-    <row r="187" spans="10:11" ht="12.5">
+    <row r="187" spans="10:11" ht="13.2">
       <c r="J187" s="6"/>
       <c r="K187" s="6"/>
     </row>
-    <row r="188" spans="10:11" ht="12.5">
+    <row r="188" spans="10:11" ht="13.2">
       <c r="J188" s="6"/>
       <c r="K188" s="6"/>
     </row>
-    <row r="189" spans="10:11" ht="12.5">
+    <row r="189" spans="10:11" ht="13.2">
       <c r="J189" s="6"/>
       <c r="K189" s="6"/>
     </row>
-    <row r="190" spans="10:11" ht="12.5">
+    <row r="190" spans="10:11" ht="13.2">
       <c r="J190" s="6"/>
       <c r="K190" s="6"/>
     </row>
-    <row r="191" spans="10:11" ht="12.5">
+    <row r="191" spans="10:11" ht="13.2">
       <c r="J191" s="6"/>
       <c r="K191" s="6"/>
     </row>
-    <row r="192" spans="10:11" ht="12.5">
+    <row r="192" spans="10:11" ht="13.2">
       <c r="J192" s="6"/>
       <c r="K192" s="6"/>
     </row>
-    <row r="193" spans="10:11" ht="12.5">
+    <row r="193" spans="10:11" ht="13.2">
       <c r="J193" s="6"/>
       <c r="K193" s="6"/>
     </row>
-    <row r="194" spans="10:11" ht="12.5">
+    <row r="194" spans="10:11" ht="13.2">
       <c r="J194" s="6"/>
       <c r="K194" s="6"/>
     </row>
-    <row r="195" spans="10:11" ht="12.5">
+    <row r="195" spans="10:11" ht="13.2">
       <c r="J195" s="6"/>
       <c r="K195" s="6"/>
     </row>
-    <row r="196" spans="10:11" ht="12.5">
+    <row r="196" spans="10:11" ht="13.2">
       <c r="J196" s="6"/>
       <c r="K196" s="6"/>
     </row>
-    <row r="197" spans="10:11" ht="12.5">
+    <row r="197" spans="10:11" ht="13.2">
       <c r="J197" s="6"/>
       <c r="K197" s="6"/>
     </row>
-    <row r="198" spans="10:11" ht="12.5">
+    <row r="198" spans="10:11" ht="13.2">
       <c r="J198" s="6"/>
       <c r="K198" s="6"/>
     </row>
-    <row r="199" spans="10:11" ht="12.5">
+    <row r="199" spans="10:11" ht="13.2">
       <c r="J199" s="6"/>
       <c r="K199" s="6"/>
     </row>
-    <row r="200" spans="10:11" ht="12.5">
+    <row r="200" spans="10:11" ht="13.2">
       <c r="J200" s="6"/>
       <c r="K200" s="6"/>
     </row>
-    <row r="201" spans="10:11" ht="12.5">
+    <row r="201" spans="10:11" ht="13.2">
       <c r="J201" s="6"/>
       <c r="K201" s="6"/>
     </row>
-    <row r="202" spans="10:11" ht="12.5">
+    <row r="202" spans="10:11" ht="13.2">
       <c r="J202" s="6"/>
       <c r="K202" s="6"/>
     </row>
-    <row r="203" spans="10:11" ht="12.5">
+    <row r="203" spans="10:11" ht="13.2">
       <c r="J203" s="6"/>
       <c r="K203" s="6"/>
     </row>
-    <row r="204" spans="10:11" ht="12.5">
+    <row r="204" spans="10:11" ht="13.2">
       <c r="J204" s="6"/>
       <c r="K204" s="6"/>
     </row>
-    <row r="205" spans="10:11" ht="12.5">
+    <row r="205" spans="10:11" ht="13.2">
       <c r="J205" s="6"/>
       <c r="K205" s="6"/>
     </row>
-    <row r="206" spans="10:11" ht="12.5">
+    <row r="206" spans="10:11" ht="13.2">
       <c r="J206" s="6"/>
       <c r="K206" s="6"/>
     </row>
-    <row r="207" spans="10:11" ht="12.5">
+    <row r="207" spans="10:11" ht="13.2">
       <c r="J207" s="6"/>
       <c r="K207" s="6"/>
     </row>
-    <row r="208" spans="10:11" ht="12.5">
+    <row r="208" spans="10:11" ht="13.2">
       <c r="J208" s="6"/>
       <c r="K208" s="6"/>
     </row>
-    <row r="209" spans="10:11" ht="12.5">
+    <row r="209" spans="10:11" ht="13.2">
       <c r="J209" s="6"/>
       <c r="K209" s="6"/>
     </row>
-    <row r="210" spans="10:11" ht="12.5">
+    <row r="210" spans="10:11" ht="13.2">
       <c r="J210" s="6"/>
       <c r="K210" s="6"/>
     </row>
-    <row r="211" spans="10:11" ht="12.5">
+    <row r="211" spans="10:11" ht="13.2">
       <c r="J211" s="6"/>
       <c r="K211" s="6"/>
     </row>
-    <row r="212" spans="10:11" ht="12.5">
+    <row r="212" spans="10:11" ht="13.2">
       <c r="J212" s="6"/>
       <c r="K212" s="6"/>
     </row>
-    <row r="213" spans="10:11" ht="12.5">
+    <row r="213" spans="10:11" ht="13.2">
       <c r="J213" s="6"/>
       <c r="K213" s="6"/>
     </row>
-    <row r="214" spans="10:11" ht="12.5">
+    <row r="214" spans="10:11" ht="13.2">
       <c r="J214" s="6"/>
       <c r="K214" s="6"/>
     </row>
-    <row r="215" spans="10:11" ht="12.5">
+    <row r="215" spans="10:11" ht="13.2">
       <c r="J215" s="6"/>
       <c r="K215" s="6"/>
     </row>
-    <row r="216" spans="10:11" ht="12.5">
+    <row r="216" spans="10:11" ht="13.2">
       <c r="J216" s="6"/>
       <c r="K216" s="6"/>
     </row>
-    <row r="217" spans="10:11" ht="12.5">
+    <row r="217" spans="10:11" ht="13.2">
       <c r="J217" s="6"/>
       <c r="K217" s="6"/>
     </row>
-    <row r="218" spans="10:11" ht="12.5">
+    <row r="218" spans="10:11" ht="13.2">
       <c r="J218" s="6"/>
       <c r="K218" s="6"/>
     </row>
-    <row r="219" spans="10:11" ht="12.5">
+    <row r="219" spans="10:11" ht="13.2">
       <c r="J219" s="6"/>
       <c r="K219" s="6"/>
     </row>
-    <row r="220" spans="10:11" ht="12.5">
+    <row r="220" spans="10:11" ht="13.2">
       <c r="J220" s="6"/>
       <c r="K220" s="6"/>
     </row>
-    <row r="221" spans="10:11" ht="12.5">
+    <row r="221" spans="10:11" ht="13.2">
       <c r="J221" s="6"/>
       <c r="K221" s="6"/>
     </row>
-    <row r="222" spans="10:11" ht="12.5">
+    <row r="222" spans="10:11" ht="13.2">
       <c r="J222" s="6"/>
       <c r="K222" s="6"/>
     </row>
-    <row r="223" spans="10:11" ht="12.5">
+    <row r="223" spans="10:11" ht="13.2">
       <c r="J223" s="6"/>
       <c r="K223" s="6"/>
     </row>
-    <row r="224" spans="10:11" ht="12.5">
+    <row r="224" spans="10:11" ht="13.2">
       <c r="J224" s="6"/>
       <c r="K224" s="6"/>
     </row>
-    <row r="225" spans="10:11" ht="12.5">
+    <row r="225" spans="10:11" ht="13.2">
       <c r="J225" s="6"/>
       <c r="K225" s="6"/>
     </row>
-    <row r="226" spans="10:11" ht="12.5">
+    <row r="226" spans="10:11" ht="13.2">
       <c r="J226" s="6"/>
       <c r="K226" s="6"/>
     </row>
-    <row r="227" spans="10:11" ht="12.5">
+    <row r="227" spans="10:11" ht="13.2">
       <c r="J227" s="6"/>
       <c r="K227" s="6"/>
     </row>
-    <row r="228" spans="10:11" ht="12.5">
+    <row r="228" spans="10:11" ht="13.2">
       <c r="J228" s="6"/>
       <c r="K228" s="6"/>
     </row>
-    <row r="229" spans="10:11" ht="12.5">
+    <row r="229" spans="10:11" ht="13.2">
       <c r="J229" s="6"/>
       <c r="K229" s="6"/>
     </row>
-    <row r="230" spans="10:11" ht="12.5">
+    <row r="230" spans="10:11" ht="13.2">
       <c r="J230" s="6"/>
       <c r="K230" s="6"/>
     </row>
-    <row r="231" spans="10:11" ht="12.5">
+    <row r="231" spans="10:11" ht="13.2">
       <c r="J231" s="6"/>
       <c r="K231" s="6"/>
     </row>
-    <row r="232" spans="10:11" ht="12.5">
+    <row r="232" spans="10:11" ht="13.2">
       <c r="J232" s="6"/>
       <c r="K232" s="6"/>
     </row>
-    <row r="233" spans="10:11" ht="12.5">
+    <row r="233" spans="10:11" ht="13.2">
       <c r="J233" s="6"/>
       <c r="K233" s="6"/>
     </row>
-    <row r="234" spans="10:11" ht="12.5">
+    <row r="234" spans="10:11" ht="13.2">
       <c r="J234" s="6"/>
       <c r="K234" s="6"/>
     </row>
-    <row r="235" spans="10:11" ht="12.5">
+    <row r="235" spans="10:11" ht="13.2">
       <c r="J235" s="6"/>
       <c r="K235" s="6"/>
     </row>
-    <row r="236" spans="10:11" ht="12.5">
+    <row r="236" spans="10:11" ht="13.2">
       <c r="J236" s="6"/>
       <c r="K236" s="6"/>
     </row>
-    <row r="237" spans="10:11" ht="12.5">
+    <row r="237" spans="10:11" ht="13.2">
       <c r="J237" s="6"/>
       <c r="K237" s="6"/>
     </row>
-    <row r="238" spans="10:11" ht="12.5">
+    <row r="238" spans="10:11" ht="13.2">
       <c r="J238" s="6"/>
       <c r="K238" s="6"/>
     </row>
-    <row r="239" spans="10:11" ht="12.5">
+    <row r="239" spans="10:11" ht="13.2">
       <c r="J239" s="6"/>
       <c r="K239" s="6"/>
     </row>
-    <row r="240" spans="10:11" ht="12.5">
+    <row r="240" spans="10:11" ht="13.2">
       <c r="J240" s="6"/>
       <c r="K240" s="6"/>
     </row>
-    <row r="241" spans="10:11" ht="12.5">
+    <row r="241" spans="10:11" ht="13.2">
       <c r="J241" s="6"/>
       <c r="K241" s="6"/>
     </row>
-    <row r="242" spans="10:11" ht="12.5">
+    <row r="242" spans="10:11" ht="13.2">
       <c r="J242" s="6"/>
       <c r="K242" s="6"/>
     </row>
-    <row r="243" spans="10:11" ht="12.5">
+    <row r="243" spans="10:11" ht="13.2">
       <c r="J243" s="6"/>
       <c r="K243" s="6"/>
     </row>
-    <row r="244" spans="10:11" ht="12.5">
+    <row r="244" spans="10:11" ht="13.2">
       <c r="J244" s="6"/>
       <c r="K244" s="6"/>
     </row>
-    <row r="245" spans="10:11" ht="12.5">
+    <row r="245" spans="10:11" ht="13.2">
       <c r="J245" s="6"/>
       <c r="K245" s="6"/>
     </row>
-    <row r="246" spans="10:11" ht="12.5">
+    <row r="246" spans="10:11" ht="13.2">
       <c r="J246" s="6"/>
       <c r="K246" s="6"/>
     </row>
-    <row r="247" spans="10:11" ht="12.5">
+    <row r="247" spans="10:11" ht="13.2">
       <c r="J247" s="6"/>
       <c r="K247" s="6"/>
     </row>
-    <row r="248" spans="10:11" ht="12.5">
+    <row r="248" spans="10:11" ht="13.2">
       <c r="J248" s="6"/>
       <c r="K248" s="6"/>
     </row>
-    <row r="249" spans="10:11" ht="12.5">
+    <row r="249" spans="10:11" ht="13.2">
       <c r="J249" s="6"/>
       <c r="K249" s="6"/>
     </row>
-    <row r="250" spans="10:11" ht="12.5">
+    <row r="250" spans="10:11" ht="13.2">
       <c r="J250" s="6"/>
       <c r="K250" s="6"/>
     </row>
-    <row r="251" spans="10:11" ht="12.5">
+    <row r="251" spans="10:11" ht="13.2">
       <c r="J251" s="6"/>
       <c r="K251" s="6"/>
     </row>
-    <row r="252" spans="10:11" ht="12.5">
+    <row r="252" spans="10:11" ht="13.2">
       <c r="J252" s="6"/>
       <c r="K252" s="6"/>
     </row>
-    <row r="253" spans="10:11" ht="12.5">
+    <row r="253" spans="10:11" ht="13.2">
       <c r="J253" s="6"/>
       <c r="K253" s="6"/>
     </row>
-    <row r="254" spans="10:11" ht="12.5">
+    <row r="254" spans="10:11" ht="13.2">
       <c r="J254" s="6"/>
       <c r="K254" s="6"/>
     </row>
-    <row r="255" spans="10:11" ht="12.5">
+    <row r="255" spans="10:11" ht="13.2">
       <c r="J255" s="6"/>
       <c r="K255" s="6"/>
     </row>
-    <row r="256" spans="10:11" ht="12.5">
+    <row r="256" spans="10:11" ht="13.2">
       <c r="J256" s="6"/>
       <c r="K256" s="6"/>
     </row>
-    <row r="257" spans="10:11" ht="12.5">
+    <row r="257" spans="10:11" ht="13.2">
       <c r="J257" s="6"/>
       <c r="K257" s="6"/>
     </row>
-    <row r="258" spans="10:11" ht="12.5">
+    <row r="258" spans="10:11" ht="13.2">
       <c r="J258" s="6"/>
       <c r="K258" s="6"/>
     </row>
-    <row r="259" spans="10:11" ht="12.5">
+    <row r="259" spans="10:11" ht="13.2">
       <c r="J259" s="6"/>
       <c r="K259" s="6"/>
     </row>
-    <row r="260" spans="10:11" ht="12.5">
+    <row r="260" spans="10:11" ht="13.2">
       <c r="J260" s="6"/>
       <c r="K260" s="6"/>
     </row>
-    <row r="261" spans="10:11" ht="12.5">
+    <row r="261" spans="10:11" ht="13.2">
       <c r="J261" s="6"/>
       <c r="K261" s="6"/>
     </row>
-    <row r="262" spans="10:11" ht="12.5">
+    <row r="262" spans="10:11" ht="13.2">
       <c r="J262" s="6"/>
       <c r="K262" s="6"/>
     </row>
-    <row r="263" spans="10:11" ht="12.5">
+    <row r="263" spans="10:11" ht="13.2">
       <c r="J263" s="6"/>
       <c r="K263" s="6"/>
     </row>
-    <row r="264" spans="10:11" ht="12.5">
+    <row r="264" spans="10:11" ht="13.2">
       <c r="J264" s="6"/>
       <c r="K264" s="6"/>
     </row>
-    <row r="265" spans="10:11" ht="12.5">
+    <row r="265" spans="10:11" ht="13.2">
       <c r="J265" s="6"/>
       <c r="K265" s="6"/>
     </row>
-    <row r="266" spans="10:11" ht="12.5">
+    <row r="266" spans="10:11" ht="13.2">
       <c r="J266" s="6"/>
       <c r="K266" s="6"/>
     </row>
-    <row r="267" spans="10:11" ht="12.5">
+    <row r="267" spans="10:11" ht="13.2">
       <c r="J267" s="6"/>
       <c r="K267" s="6"/>
     </row>
-    <row r="268" spans="10:11" ht="12.5">
+    <row r="268" spans="10:11" ht="13.2">
       <c r="J268" s="6"/>
       <c r="K268" s="6"/>
     </row>
-    <row r="269" spans="10:11" ht="12.5">
+    <row r="269" spans="10:11" ht="13.2">
       <c r="J269" s="6"/>
       <c r="K269" s="6"/>
     </row>
-    <row r="270" spans="10:11" ht="12.5">
+    <row r="270" spans="10:11" ht="13.2">
       <c r="J270" s="6"/>
       <c r="K270" s="6"/>
     </row>
-    <row r="271" spans="10:11" ht="12.5">
+    <row r="271" spans="10:11" ht="13.2">
       <c r="J271" s="6"/>
       <c r="K271" s="6"/>
     </row>
-    <row r="272" spans="10:11" ht="12.5">
+    <row r="272" spans="10:11" ht="13.2">
       <c r="J272" s="6"/>
       <c r="K272" s="6"/>
     </row>
-    <row r="273" spans="10:11" ht="12.5">
+    <row r="273" spans="10:11" ht="13.2">
       <c r="J273" s="6"/>
       <c r="K273" s="6"/>
     </row>
-    <row r="274" spans="10:11" ht="12.5">
+    <row r="274" spans="10:11" ht="13.2">
       <c r="J274" s="6"/>
       <c r="K274" s="6"/>
     </row>
-    <row r="275" spans="10:11" ht="12.5">
+    <row r="275" spans="10:11" ht="13.2">
       <c r="J275" s="6"/>
       <c r="K275" s="6"/>
     </row>
-    <row r="276" spans="10:11" ht="12.5">
+    <row r="276" spans="10:11" ht="13.2">
       <c r="J276" s="6"/>
       <c r="K276" s="6"/>
     </row>
-    <row r="277" spans="10:11" ht="12.5">
+    <row r="277" spans="10:11" ht="13.2">
       <c r="J277" s="6"/>
       <c r="K277" s="6"/>
     </row>
-    <row r="278" spans="10:11" ht="12.5">
+    <row r="278" spans="10:11" ht="13.2">
       <c r="J278" s="6"/>
       <c r="K278" s="6"/>
     </row>
-    <row r="279" spans="10:11" ht="12.5">
+    <row r="279" spans="10:11" ht="13.2">
       <c r="J279" s="6"/>
       <c r="K279" s="6"/>
     </row>
-    <row r="280" spans="10:11" ht="12.5">
+    <row r="280" spans="10:11" ht="13.2">
       <c r="J280" s="6"/>
       <c r="K280" s="6"/>
     </row>
-    <row r="281" spans="10:11" ht="12.5">
+    <row r="281" spans="10:11" ht="13.2">
       <c r="J281" s="6"/>
       <c r="K281" s="6"/>
     </row>
-    <row r="282" spans="10:11" ht="12.5">
+    <row r="282" spans="10:11" ht="13.2">
       <c r="J282" s="6"/>
       <c r="K282" s="6"/>
     </row>
-    <row r="283" spans="10:11" ht="12.5">
+    <row r="283" spans="10:11" ht="13.2">
       <c r="J283" s="6"/>
       <c r="K283" s="6"/>
     </row>
-    <row r="284" spans="10:11" ht="12.5">
+    <row r="284" spans="10:11" ht="13.2">
       <c r="J284" s="6"/>
       <c r="K284" s="6"/>
     </row>
-    <row r="285" spans="10:11" ht="12.5">
+    <row r="285" spans="10:11" ht="13.2">
       <c r="J285" s="6"/>
       <c r="K285" s="6"/>
     </row>
-    <row r="286" spans="10:11" ht="12.5">
+    <row r="286" spans="10:11" ht="13.2">
       <c r="J286" s="6"/>
       <c r="K286" s="6"/>
     </row>
-    <row r="287" spans="10:11" ht="12.5">
+    <row r="287" spans="10:11" ht="13.2">
       <c r="J287" s="6"/>
       <c r="K287" s="6"/>
     </row>
-    <row r="288" spans="10:11" ht="12.5">
+    <row r="288" spans="10:11" ht="13.2">
       <c r="J288" s="6"/>
       <c r="K288" s="6"/>
     </row>
-    <row r="289" spans="10:11" ht="12.5">
+    <row r="289" spans="10:11" ht="13.2">
       <c r="J289" s="6"/>
       <c r="K289" s="6"/>
     </row>
-    <row r="290" spans="10:11" ht="12.5">
+    <row r="290" spans="10:11" ht="13.2">
       <c r="J290" s="6"/>
       <c r="K290" s="6"/>
     </row>
-    <row r="291" spans="10:11" ht="12.5">
+    <row r="291" spans="10:11" ht="13.2">
       <c r="J291" s="6"/>
       <c r="K291" s="6"/>
     </row>
-    <row r="292" spans="10:11" ht="12.5">
+    <row r="292" spans="10:11" ht="13.2">
       <c r="J292" s="6"/>
       <c r="K292" s="6"/>
     </row>
-    <row r="293" spans="10:11" ht="12.5">
+    <row r="293" spans="10:11" ht="13.2">
       <c r="J293" s="6"/>
       <c r="K293" s="6"/>
     </row>
-    <row r="294" spans="10:11" ht="12.5">
+    <row r="294" spans="10:11" ht="13.2">
       <c r="J294" s="6"/>
       <c r="K294" s="6"/>
     </row>
-    <row r="295" spans="10:11" ht="12.5">
+    <row r="295" spans="10:11" ht="13.2">
       <c r="J295" s="6"/>
       <c r="K295" s="6"/>
     </row>
-    <row r="296" spans="10:11" ht="12.5">
+    <row r="296" spans="10:11" ht="13.2">
       <c r="J296" s="6"/>
       <c r="K296" s="6"/>
     </row>
-    <row r="297" spans="10:11" ht="12.5">
+    <row r="297" spans="10:11" ht="13.2">
       <c r="J297" s="6"/>
       <c r="K297" s="6"/>
     </row>
-    <row r="298" spans="10:11" ht="12.5">
+    <row r="298" spans="10:11" ht="13.2">
       <c r="J298" s="6"/>
       <c r="K298" s="6"/>
     </row>
-    <row r="299" spans="10:11" ht="12.5">
+    <row r="299" spans="10:11" ht="13.2">
       <c r="J299" s="6"/>
       <c r="K299" s="6"/>
     </row>
-    <row r="300" spans="10:11" ht="12.5">
+    <row r="300" spans="10:11" ht="13.2">
       <c r="J300" s="6"/>
       <c r="K300" s="6"/>
     </row>
-    <row r="301" spans="10:11" ht="12.5">
+    <row r="301" spans="10:11" ht="13.2">
       <c r="J301" s="6"/>
       <c r="K301" s="6"/>
     </row>
-    <row r="302" spans="10:11" ht="12.5">
+    <row r="302" spans="10:11" ht="13.2">
       <c r="J302" s="6"/>
       <c r="K302" s="6"/>
     </row>
-    <row r="303" spans="10:11" ht="12.5">
+    <row r="303" spans="10:11" ht="13.2">
       <c r="J303" s="6"/>
       <c r="K303" s="6"/>
     </row>
-    <row r="304" spans="10:11" ht="12.5">
+    <row r="304" spans="10:11" ht="13.2">
       <c r="J304" s="6"/>
       <c r="K304" s="6"/>
     </row>
-    <row r="305" spans="10:11" ht="12.5">
+    <row r="305" spans="10:11" ht="13.2">
       <c r="J305" s="6"/>
       <c r="K305" s="6"/>
     </row>
-    <row r="306" spans="10:11" ht="12.5">
+    <row r="306" spans="10:11" ht="13.2">
       <c r="J306" s="6"/>
       <c r="K306" s="6"/>
     </row>
-    <row r="307" spans="10:11" ht="12.5">
+    <row r="307" spans="10:11" ht="13.2">
       <c r="J307" s="6"/>
       <c r="K307" s="6"/>
     </row>
-    <row r="308" spans="10:11" ht="12.5">
+    <row r="308" spans="10:11" ht="13.2">
       <c r="J308" s="6"/>
       <c r="K308" s="6"/>
     </row>
-    <row r="309" spans="10:11" ht="12.5">
+    <row r="309" spans="10:11" ht="13.2">
       <c r="J309" s="6"/>
       <c r="K309" s="6"/>
     </row>
-    <row r="310" spans="10:11" ht="12.5">
+    <row r="310" spans="10:11" ht="13.2">
       <c r="J310" s="6"/>
       <c r="K310" s="6"/>
     </row>
-    <row r="311" spans="10:11" ht="12.5">
+    <row r="311" spans="10:11" ht="13.2">
       <c r="J311" s="6"/>
       <c r="K311" s="6"/>
     </row>
-    <row r="312" spans="10:11" ht="12.5">
+    <row r="312" spans="10:11" ht="13.2">
       <c r="J312" s="6"/>
       <c r="K312" s="6"/>
     </row>
-    <row r="313" spans="10:11" ht="12.5">
+    <row r="313" spans="10:11" ht="13.2">
       <c r="J313" s="6"/>
       <c r="K313" s="6"/>
     </row>
-    <row r="314" spans="10:11" ht="12.5">
+    <row r="314" spans="10:11" ht="13.2">
       <c r="J314" s="6"/>
       <c r="K314" s="6"/>
     </row>
-    <row r="315" spans="10:11" ht="12.5">
+    <row r="315" spans="10:11" ht="13.2">
       <c r="J315" s="6"/>
       <c r="K315" s="6"/>
     </row>
-    <row r="316" spans="10:11" ht="12.5">
+    <row r="316" spans="10:11" ht="13.2">
       <c r="J316" s="6"/>
       <c r="K316" s="6"/>
     </row>
-    <row r="317" spans="10:11" ht="12.5">
+    <row r="317" spans="10:11" ht="13.2">
       <c r="J317" s="6"/>
       <c r="K317" s="6"/>
     </row>
-    <row r="318" spans="10:11" ht="12.5">
+    <row r="318" spans="10:11" ht="13.2">
       <c r="J318" s="6"/>
       <c r="K318" s="6"/>
     </row>
-    <row r="319" spans="10:11" ht="12.5">
+    <row r="319" spans="10:11" ht="13.2">
       <c r="J319" s="6"/>
       <c r="K319" s="6"/>
     </row>
-    <row r="320" spans="10:11" ht="12.5">
+    <row r="320" spans="10:11" ht="13.2">
       <c r="J320" s="6"/>
       <c r="K320" s="6"/>
     </row>
-    <row r="321" spans="10:11" ht="12.5">
+    <row r="321" spans="10:11" ht="13.2">
       <c r="J321" s="6"/>
       <c r="K321" s="6"/>
     </row>
-    <row r="322" spans="10:11" ht="12.5">
+    <row r="322" spans="10:11" ht="13.2">
       <c r="J322" s="6"/>
       <c r="K322" s="6"/>
     </row>
-    <row r="323" spans="10:11" ht="12.5">
+    <row r="323" spans="10:11" ht="13.2">
       <c r="J323" s="6"/>
       <c r="K323" s="6"/>
     </row>
-    <row r="324" spans="10:11" ht="12.5">
+    <row r="324" spans="10:11" ht="13.2">
       <c r="J324" s="6"/>
       <c r="K324" s="6"/>
     </row>
-    <row r="325" spans="10:11" ht="12.5">
+    <row r="325" spans="10:11" ht="13.2">
       <c r="J325" s="6"/>
       <c r="K325" s="6"/>
     </row>
-    <row r="326" spans="10:11" ht="12.5">
+    <row r="326" spans="10:11" ht="13.2">
       <c r="J326" s="6"/>
       <c r="K326" s="6"/>
     </row>
-    <row r="327" spans="10:11" ht="12.5">
+    <row r="327" spans="10:11" ht="13.2">
       <c r="J327" s="6"/>
       <c r="K327" s="6"/>
     </row>
-    <row r="328" spans="10:11" ht="12.5">
+    <row r="328" spans="10:11" ht="13.2">
       <c r="J328" s="6"/>
       <c r="K328" s="6"/>
     </row>
-    <row r="329" spans="10:11" ht="12.5">
+    <row r="329" spans="10:11" ht="13.2">
       <c r="J329" s="6"/>
       <c r="K329" s="6"/>
     </row>
-    <row r="330" spans="10:11" ht="12.5">
+    <row r="330" spans="10:11" ht="13.2">
       <c r="J330" s="6"/>
       <c r="K330" s="6"/>
     </row>
-    <row r="331" spans="10:11" ht="12.5">
+    <row r="331" spans="10:11" ht="13.2">
       <c r="J331" s="6"/>
       <c r="K331" s="6"/>
     </row>
-    <row r="332" spans="10:11" ht="12.5">
+    <row r="332" spans="10:11" ht="13.2">
       <c r="J332" s="6"/>
       <c r="K332" s="6"/>
     </row>
-    <row r="333" spans="10:11" ht="12.5">
+    <row r="333" spans="10:11" ht="13.2">
       <c r="J333" s="6"/>
       <c r="K333" s="6"/>
     </row>
-    <row r="334" spans="10:11" ht="12.5">
+    <row r="334" spans="10:11" ht="13.2">
       <c r="J334" s="6"/>
       <c r="K334" s="6"/>
     </row>
-    <row r="335" spans="10:11" ht="12.5">
+    <row r="335" spans="10:11" ht="13.2">
       <c r="J335" s="6"/>
       <c r="K335" s="6"/>
     </row>
-    <row r="336" spans="10:11" ht="12.5">
+    <row r="336" spans="10:11" ht="13.2">
       <c r="J336" s="6"/>
       <c r="K336" s="6"/>
     </row>
-    <row r="337" spans="10:11" ht="12.5">
+    <row r="337" spans="10:11" ht="13.2">
       <c r="J337" s="6"/>
       <c r="K337" s="6"/>
     </row>
-    <row r="338" spans="10:11" ht="12.5">
+    <row r="338" spans="10:11" ht="13.2">
       <c r="J338" s="6"/>
       <c r="K338" s="6"/>
     </row>
-    <row r="339" spans="10:11" ht="12.5">
+    <row r="339" spans="10:11" ht="13.2">
       <c r="J339" s="6"/>
       <c r="K339" s="6"/>
     </row>
-    <row r="340" spans="10:11" ht="12.5">
+    <row r="340" spans="10:11" ht="13.2">
       <c r="J340" s="6"/>
       <c r="K340" s="6"/>
     </row>
-    <row r="341" spans="10:11" ht="12.5">
+    <row r="341" spans="10:11" ht="13.2">
       <c r="J341" s="6"/>
       <c r="K341" s="6"/>
     </row>
-    <row r="342" spans="10:11" ht="12.5">
+    <row r="342" spans="10:11" ht="13.2">
       <c r="J342" s="6"/>
       <c r="K342" s="6"/>
     </row>
-    <row r="343" spans="10:11" ht="12.5">
+    <row r="343" spans="10:11" ht="13.2">
       <c r="J343" s="6"/>
       <c r="K343" s="6"/>
     </row>
-    <row r="344" spans="10:11" ht="12.5">
+    <row r="344" spans="10:11" ht="13.2">
       <c r="J344" s="6"/>
       <c r="K344" s="6"/>
     </row>
-    <row r="345" spans="10:11" ht="12.5">
+    <row r="345" spans="10:11" ht="13.2">
       <c r="J345" s="6"/>
       <c r="K345" s="6"/>
     </row>
-    <row r="346" spans="10:11" ht="12.5">
+    <row r="346" spans="10:11" ht="13.2">
       <c r="J346" s="6"/>
       <c r="K346" s="6"/>
     </row>
-    <row r="347" spans="10:11" ht="12.5">
+    <row r="347" spans="10:11" ht="13.2">
       <c r="J347" s="6"/>
       <c r="K347" s="6"/>
     </row>
-    <row r="348" spans="10:11" ht="12.5">
+    <row r="348" spans="10:11" ht="13.2">
       <c r="J348" s="6"/>
       <c r="K348" s="6"/>
     </row>
-    <row r="349" spans="10:11" ht="12.5">
+    <row r="349" spans="10:11" ht="13.2">
       <c r="J349" s="6"/>
       <c r="K349" s="6"/>
     </row>
-    <row r="350" spans="10:11" ht="12.5">
+    <row r="350" spans="10:11" ht="13.2">
       <c r="J350" s="6"/>
       <c r="K350" s="6"/>
     </row>
-    <row r="351" spans="10:11" ht="12.5">
+    <row r="351" spans="10:11" ht="13.2">
       <c r="J351" s="6"/>
       <c r="K351" s="6"/>
     </row>
-    <row r="352" spans="10:11" ht="12.5">
+    <row r="352" spans="10:11" ht="13.2">
       <c r="J352" s="6"/>
       <c r="K352" s="6"/>
     </row>
-    <row r="353" spans="10:11" ht="12.5">
+    <row r="353" spans="10:11" ht="13.2">
       <c r="J353" s="6"/>
       <c r="K353" s="6"/>
     </row>
-    <row r="354" spans="10:11" ht="12.5">
+    <row r="354" spans="10:11" ht="13.2">
       <c r="J354" s="6"/>
       <c r="K354" s="6"/>
     </row>
-    <row r="355" spans="10:11" ht="12.5">
+    <row r="355" spans="10:11" ht="13.2">
       <c r="J355" s="6"/>
       <c r="K355" s="6"/>
     </row>
-    <row r="356" spans="10:11" ht="12.5">
+    <row r="356" spans="10:11" ht="13.2">
       <c r="J356" s="6"/>
       <c r="K356" s="6"/>
     </row>
-    <row r="357" spans="10:11" ht="12.5">
+    <row r="357" spans="10:11" ht="13.2">
       <c r="J357" s="6"/>
       <c r="K357" s="6"/>
     </row>
-    <row r="358" spans="10:11" ht="12.5">
+    <row r="358" spans="10:11" ht="13.2">
       <c r="J358" s="6"/>
       <c r="K358" s="6"/>
     </row>
-    <row r="359" spans="10:11" ht="12.5">
+    <row r="359" spans="10:11" ht="13.2">
       <c r="J359" s="6"/>
       <c r="K359" s="6"/>
     </row>
-    <row r="360" spans="10:11" ht="12.5">
+    <row r="360" spans="10:11" ht="13.2">
       <c r="J360" s="6"/>
       <c r="K360" s="6"/>
     </row>
-    <row r="361" spans="10:11" ht="12.5">
+    <row r="361" spans="10:11" ht="13.2">
       <c r="J361" s="6"/>
       <c r="K361" s="6"/>
     </row>
-    <row r="362" spans="10:11" ht="12.5">
+    <row r="362" spans="10:11" ht="13.2">
       <c r="J362" s="6"/>
       <c r="K362" s="6"/>
     </row>
-    <row r="363" spans="10:11" ht="12.5">
+    <row r="363" spans="10:11" ht="13.2">
       <c r="J363" s="6"/>
       <c r="K363" s="6"/>
     </row>
-    <row r="364" spans="10:11" ht="12.5">
+    <row r="364" spans="10:11" ht="13.2">
       <c r="J364" s="6"/>
       <c r="K364" s="6"/>
     </row>
-    <row r="365" spans="10:11" ht="12.5">
+    <row r="365" spans="10:11" ht="13.2">
       <c r="J365" s="6"/>
       <c r="K365" s="6"/>
     </row>
-    <row r="366" spans="10:11" ht="12.5">
+    <row r="366" spans="10:11" ht="13.2">
       <c r="J366" s="6"/>
       <c r="K366" s="6"/>
     </row>
-    <row r="367" spans="10:11" ht="12.5">
+    <row r="367" spans="10:11" ht="13.2">
       <c r="J367" s="6"/>
       <c r="K367" s="6"/>
     </row>
-    <row r="368" spans="10:11" ht="12.5">
+    <row r="368" spans="10:11" ht="13.2">
       <c r="J368" s="6"/>
       <c r="K368" s="6"/>
     </row>
-    <row r="369" spans="10:11" ht="12.5">
+    <row r="369" spans="10:11" ht="13.2">
       <c r="J369" s="6"/>
       <c r="K369" s="6"/>
     </row>
-    <row r="370" spans="10:11" ht="12.5">
+    <row r="370" spans="10:11" ht="13.2">
       <c r="J370" s="6"/>
       <c r="K370" s="6"/>
     </row>
-    <row r="371" spans="10:11" ht="12.5">
+    <row r="371" spans="10:11" ht="13.2">
       <c r="J371" s="6"/>
       <c r="K371" s="6"/>
     </row>
-    <row r="372" spans="10:11" ht="12.5">
+    <row r="372" spans="10:11" ht="13.2">
       <c r="J372" s="6"/>
       <c r="K372" s="6"/>
     </row>
-    <row r="373" spans="10:11" ht="12.5">
+    <row r="373" spans="10:11" ht="13.2">
       <c r="J373" s="6"/>
       <c r="K373" s="6"/>
     </row>
-    <row r="374" spans="10:11" ht="12.5">
+    <row r="374" spans="10:11" ht="13.2">
       <c r="J374" s="6"/>
       <c r="K374" s="6"/>
     </row>
-    <row r="375" spans="10:11" ht="12.5">
+    <row r="375" spans="10:11" ht="13.2">
       <c r="J375" s="6"/>
       <c r="K375" s="6"/>
     </row>
-    <row r="376" spans="10:11" ht="12.5">
+    <row r="376" spans="10:11" ht="13.2">
       <c r="J376" s="6"/>
       <c r="K376" s="6"/>
     </row>
-    <row r="377" spans="10:11" ht="12.5">
+    <row r="377" spans="10:11" ht="13.2">
       <c r="J377" s="6"/>
       <c r="K377" s="6"/>
     </row>
-    <row r="378" spans="10:11" ht="12.5">
+    <row r="378" spans="10:11" ht="13.2">
       <c r="J378" s="6"/>
       <c r="K378" s="6"/>
     </row>
-    <row r="379" spans="10:11" ht="12.5">
+    <row r="379" spans="10:11" ht="13.2">
       <c r="J379" s="6"/>
       <c r="K379" s="6"/>
     </row>
-    <row r="380" spans="10:11" ht="12.5">
+    <row r="380" spans="10:11" ht="13.2">
       <c r="J380" s="6"/>
       <c r="K380" s="6"/>
     </row>
-    <row r="381" spans="10:11" ht="12.5">
+    <row r="381" spans="10:11" ht="13.2">
       <c r="J381" s="6"/>
       <c r="K381" s="6"/>
     </row>
-    <row r="382" spans="10:11" ht="12.5">
+    <row r="382" spans="10:11" ht="13.2">
       <c r="J382" s="6"/>
       <c r="K382" s="6"/>
     </row>
-    <row r="383" spans="10:11" ht="12.5">
+    <row r="383" spans="10:11" ht="13.2">
       <c r="J383" s="6"/>
       <c r="K383" s="6"/>
     </row>
-    <row r="384" spans="10:11" ht="12.5">
+    <row r="384" spans="10:11" ht="13.2">
       <c r="J384" s="6"/>
       <c r="K384" s="6"/>
     </row>
-    <row r="385" spans="10:11" ht="12.5">
+    <row r="385" spans="10:11" ht="13.2">
       <c r="J385" s="6"/>
       <c r="K385" s="6"/>
     </row>
-    <row r="386" spans="10:11" ht="12.5">
+    <row r="386" spans="10:11" ht="13.2">
       <c r="J386" s="6"/>
       <c r="K386" s="6"/>
     </row>
-    <row r="387" spans="10:11" ht="12.5">
+    <row r="387" spans="10:11" ht="13.2">
       <c r="J387" s="6"/>
       <c r="K387" s="6"/>
     </row>
-    <row r="388" spans="10:11" ht="12.5">
+    <row r="388" spans="10:11" ht="13.2">
       <c r="J388" s="6"/>
       <c r="K388" s="6"/>
     </row>
-    <row r="389" spans="10:11" ht="12.5">
+    <row r="389" spans="10:11" ht="13.2">
       <c r="J389" s="6"/>
       <c r="K389" s="6"/>
     </row>
-    <row r="390" spans="10:11" ht="12.5">
+    <row r="390" spans="10:11" ht="13.2">
       <c r="J390" s="6"/>
       <c r="K390" s="6"/>
     </row>
-    <row r="391" spans="10:11" ht="12.5">
+    <row r="391" spans="10:11" ht="13.2">
       <c r="J391" s="6"/>
       <c r="K391" s="6"/>
     </row>
-    <row r="392" spans="10:11" ht="12.5">
+    <row r="392" spans="10:11" ht="13.2">
       <c r="J392" s="6"/>
       <c r="K392" s="6"/>
     </row>
-    <row r="393" spans="10:11" ht="12.5">
+    <row r="393" spans="10:11" ht="13.2">
       <c r="J393" s="6"/>
       <c r="K393" s="6"/>
     </row>
-    <row r="394" spans="10:11" ht="12.5">
+    <row r="394" spans="10:11" ht="13.2">
       <c r="J394" s="6"/>
       <c r="K394" s="6"/>
     </row>
-    <row r="395" spans="10:11" ht="12.5">
+    <row r="395" spans="10:11" ht="13.2">
       <c r="J395" s="6"/>
       <c r="K395" s="6"/>
     </row>
-    <row r="396" spans="10:11" ht="12.5">
+    <row r="396" spans="10:11" ht="13.2">
       <c r="J396" s="6"/>
       <c r="K396" s="6"/>
     </row>
-    <row r="397" spans="10:11" ht="12.5">
+    <row r="397" spans="10:11" ht="13.2">
       <c r="J397" s="6"/>
       <c r="K397" s="6"/>
     </row>
-    <row r="398" spans="10:11" ht="12.5">
+    <row r="398" spans="10:11" ht="13.2">
       <c r="J398" s="6"/>
       <c r="K398" s="6"/>
     </row>
-    <row r="399" spans="10:11" ht="12.5">
+    <row r="399" spans="10:11" ht="13.2">
       <c r="J399" s="6"/>
       <c r="K399" s="6"/>
     </row>
-    <row r="400" spans="10:11" ht="12.5">
+    <row r="400" spans="10:11" ht="13.2">
       <c r="J400" s="6"/>
       <c r="K400" s="6"/>
     </row>
-    <row r="401" spans="10:11" ht="12.5">
+    <row r="401" spans="10:11" ht="13.2">
       <c r="J401" s="6"/>
       <c r="K401" s="6"/>
     </row>
-    <row r="402" spans="10:11" ht="12.5">
+    <row r="402" spans="10:11" ht="13.2">
       <c r="J402" s="6"/>
       <c r="K402" s="6"/>
     </row>
-    <row r="403" spans="10:11" ht="12.5">
+    <row r="403" spans="10:11" ht="13.2">
       <c r="J403" s="6"/>
       <c r="K403" s="6"/>
     </row>
-    <row r="404" spans="10:11" ht="12.5">
+    <row r="404" spans="10:11" ht="13.2">
       <c r="J404" s="6"/>
       <c r="K404" s="6"/>
     </row>
-    <row r="405" spans="10:11" ht="12.5">
+    <row r="405" spans="10:11" ht="13.2">
       <c r="J405" s="6"/>
       <c r="K405" s="6"/>
     </row>
-    <row r="406" spans="10:11" ht="12.5">
+    <row r="406" spans="10:11" ht="13.2">
       <c r="J406" s="6"/>
       <c r="K406" s="6"/>
     </row>
-    <row r="407" spans="10:11" ht="12.5">
+    <row r="407" spans="10:11" ht="13.2">
       <c r="J407" s="6"/>
       <c r="K407" s="6"/>
     </row>
-    <row r="408" spans="10:11" ht="12.5">
+    <row r="408" spans="10:11" ht="13.2">
       <c r="J408" s="6"/>
       <c r="K408" s="6"/>
     </row>
-    <row r="409" spans="10:11" ht="12.5">
+    <row r="409" spans="10:11" ht="13.2">
       <c r="J409" s="6"/>
       <c r="K409" s="6"/>
     </row>
-    <row r="410" spans="10:11" ht="12.5">
+    <row r="410" spans="10:11" ht="13.2">
       <c r="J410" s="6"/>
       <c r="K410" s="6"/>
     </row>
-    <row r="411" spans="10:11" ht="12.5">
+    <row r="411" spans="10:11" ht="13.2">
       <c r="J411" s="6"/>
       <c r="K411" s="6"/>
     </row>
-    <row r="412" spans="10:11" ht="12.5">
+    <row r="412" spans="10:11" ht="13.2">
       <c r="J412" s="6"/>
       <c r="K412" s="6"/>
     </row>
-    <row r="413" spans="10:11" ht="12.5">
+    <row r="413" spans="10:11" ht="13.2">
       <c r="J413" s="6"/>
       <c r="K413" s="6"/>
     </row>
-    <row r="414" spans="10:11" ht="12.5">
+    <row r="414" spans="10:11" ht="13.2">
       <c r="J414" s="6"/>
       <c r="K414" s="6"/>
     </row>
-    <row r="415" spans="10:11" ht="12.5">
+    <row r="415" spans="10:11" ht="13.2">
       <c r="J415" s="6"/>
       <c r="K415" s="6"/>
     </row>
-    <row r="416" spans="10:11" ht="12.5">
+    <row r="416" spans="10:11" ht="13.2">
       <c r="J416" s="6"/>
       <c r="K416" s="6"/>
     </row>
-    <row r="417" spans="10:11" ht="12.5">
+    <row r="417" spans="10:11" ht="13.2">
       <c r="J417" s="6"/>
       <c r="K417" s="6"/>
     </row>
-    <row r="418" spans="10:11" ht="12.5">
+    <row r="418" spans="10:11" ht="13.2">
       <c r="J418" s="6"/>
       <c r="K418" s="6"/>
     </row>
-    <row r="419" spans="10:11" ht="12.5">
+    <row r="419" spans="10:11" ht="13.2">
       <c r="J419" s="6"/>
       <c r="K419" s="6"/>
     </row>
-    <row r="420" spans="10:11" ht="12.5">
+    <row r="420" spans="10:11" ht="13.2">
       <c r="J420" s="6"/>
       <c r="K420" s="6"/>
     </row>
-    <row r="421" spans="10:11" ht="12.5">
+    <row r="421" spans="10:11" ht="13.2">
       <c r="J421" s="6"/>
       <c r="K421" s="6"/>
     </row>
-    <row r="422" spans="10:11" ht="12.5">
+    <row r="422" spans="10:11" ht="13.2">
       <c r="J422" s="6"/>
       <c r="K422" s="6"/>
     </row>
-    <row r="423" spans="10:11" ht="12.5">
+    <row r="423" spans="10:11" ht="13.2">
       <c r="J423" s="6"/>
       <c r="K423" s="6"/>
     </row>
-    <row r="424" spans="10:11" ht="12.5">
+    <row r="424" spans="10:11" ht="13.2">
       <c r="J424" s="6"/>
       <c r="K424" s="6"/>
     </row>
-    <row r="425" spans="10:11" ht="12.5">
+    <row r="425" spans="10:11" ht="13.2">
       <c r="J425" s="6"/>
       <c r="K425" s="6"/>
     </row>
-    <row r="426" spans="10:11" ht="12.5">
+    <row r="426" spans="10:11" ht="13.2">
       <c r="J426" s="6"/>
       <c r="K426" s="6"/>
     </row>
-    <row r="427" spans="10:11" ht="12.5">
+    <row r="427" spans="10:11" ht="13.2">
       <c r="J427" s="6"/>
       <c r="K427" s="6"/>
     </row>
-    <row r="428" spans="10:11" ht="12.5">
+    <row r="428" spans="10:11" ht="13.2">
       <c r="J428" s="6"/>
       <c r="K428" s="6"/>
     </row>
-    <row r="429" spans="10:11" ht="12.5">
+    <row r="429" spans="10:11" ht="13.2">
       <c r="J429" s="6"/>
       <c r="K429" s="6"/>
     </row>
-    <row r="430" spans="10:11" ht="12.5">
+    <row r="430" spans="10:11" ht="13.2">
       <c r="J430" s="6"/>
       <c r="K430" s="6"/>
     </row>
-    <row r="431" spans="10:11" ht="12.5">
+    <row r="431" spans="10:11" ht="13.2">
       <c r="J431" s="6"/>
       <c r="K431" s="6"/>
     </row>
-    <row r="432" spans="10:11" ht="12.5">
+    <row r="432" spans="10:11" ht="13.2">
       <c r="J432" s="6"/>
       <c r="K432" s="6"/>
     </row>
-    <row r="433" spans="10:11" ht="12.5">
+    <row r="433" spans="10:11" ht="13.2">
       <c r="J433" s="6"/>
       <c r="K433" s="6"/>
     </row>
-    <row r="434" spans="10:11" ht="12.5">
+    <row r="434" spans="10:11" ht="13.2">
       <c r="J434" s="6"/>
       <c r="K434" s="6"/>
     </row>
-    <row r="435" spans="10:11" ht="12.5">
+    <row r="435" spans="10:11" ht="13.2">
       <c r="J435" s="6"/>
       <c r="K435" s="6"/>
     </row>
-    <row r="436" spans="10:11" ht="12.5">
+    <row r="436" spans="10:11" ht="13.2">
       <c r="J436" s="6"/>
       <c r="K436" s="6"/>
     </row>
-    <row r="437" spans="10:11" ht="12.5">
+    <row r="437" spans="10:11" ht="13.2">
       <c r="J437" s="6"/>
       <c r="K437" s="6"/>
     </row>
-    <row r="438" spans="10:11" ht="12.5">
+    <row r="438" spans="10:11" ht="13.2">
       <c r="J438" s="6"/>
       <c r="K438" s="6"/>
     </row>
-    <row r="439" spans="10:11" ht="12.5">
+    <row r="439" spans="10:11" ht="13.2">
       <c r="J439" s="6"/>
       <c r="K439" s="6"/>
     </row>
-    <row r="440" spans="10:11" ht="12.5">
+    <row r="440" spans="10:11" ht="13.2">
       <c r="J440" s="6"/>
       <c r="K440" s="6"/>
     </row>
-    <row r="441" spans="10:11" ht="12.5">
+    <row r="441" spans="10:11" ht="13.2">
       <c r="J441" s="6"/>
       <c r="K441" s="6"/>
     </row>
-    <row r="442" spans="10:11" ht="12.5">
+    <row r="442" spans="10:11" ht="13.2">
       <c r="J442" s="6"/>
       <c r="K442" s="6"/>
     </row>
-    <row r="443" spans="10:11" ht="12.5">
+    <row r="443" spans="10:11" ht="13.2">
       <c r="J443" s="6"/>
       <c r="K443" s="6"/>
     </row>
-    <row r="444" spans="10:11" ht="12.5">
+    <row r="444" spans="10:11" ht="13.2">
       <c r="J444" s="6"/>
       <c r="K444" s="6"/>
     </row>
-    <row r="445" spans="10:11" ht="12.5">
+    <row r="445" spans="10:11" ht="13.2">
       <c r="J445" s="6"/>
       <c r="K445" s="6"/>
     </row>
-    <row r="446" spans="10:11" ht="12.5">
+    <row r="446" spans="10:11" ht="13.2">
       <c r="J446" s="6"/>
       <c r="K446" s="6"/>
     </row>
-    <row r="447" spans="10:11" ht="12.5">
+    <row r="447" spans="10:11" ht="13.2">
       <c r="J447" s="6"/>
       <c r="K447" s="6"/>
     </row>
-    <row r="448" spans="10:11" ht="12.5">
+    <row r="448" spans="10:11" ht="13.2">
       <c r="J448" s="6"/>
       <c r="K448" s="6"/>
     </row>
-    <row r="449" spans="10:11" ht="12.5">
+    <row r="449" spans="10:11" ht="13.2">
       <c r="J449" s="6"/>
       <c r="K449" s="6"/>
     </row>
-    <row r="450" spans="10:11" ht="12.5">
+    <row r="450" spans="10:11" ht="13.2">
       <c r="J450" s="6"/>
       <c r="K450" s="6"/>
     </row>
-    <row r="451" spans="10:11" ht="12.5">
+    <row r="451" spans="10:11" ht="13.2">
       <c r="J451" s="6"/>
       <c r="K451" s="6"/>
     </row>
-    <row r="452" spans="10:11" ht="12.5">
+    <row r="452" spans="10:11" ht="13.2">
       <c r="J452" s="6"/>
       <c r="K452" s="6"/>
     </row>
-    <row r="453" spans="10:11" ht="12.5">
+    <row r="453" spans="10:11" ht="13.2">
       <c r="J453" s="6"/>
       <c r="K453" s="6"/>
     </row>
-    <row r="454" spans="10:11" ht="12.5">
+    <row r="454" spans="10:11" ht="13.2">
       <c r="J454" s="6"/>
       <c r="K454" s="6"/>
     </row>
-    <row r="455" spans="10:11" ht="12.5">
+    <row r="455" spans="10:11" ht="13.2">
       <c r="J455" s="6"/>
       <c r="K455" s="6"/>
     </row>
-    <row r="456" spans="10:11" ht="12.5">
+    <row r="456" spans="10:11" ht="13.2">
       <c r="J456" s="6"/>
       <c r="K456" s="6"/>
     </row>
-    <row r="457" spans="10:11" ht="12.5">
+    <row r="457" spans="10:11" ht="13.2">
       <c r="J457" s="6"/>
       <c r="K457" s="6"/>
     </row>
-    <row r="458" spans="10:11" ht="12.5">
+    <row r="458" spans="10:11" ht="13.2">
       <c r="J458" s="6"/>
       <c r="K458" s="6"/>
     </row>
-    <row r="459" spans="10:11" ht="12.5">
+    <row r="459" spans="10:11" ht="13.2">
       <c r="J459" s="6"/>
       <c r="K459" s="6"/>
     </row>
-    <row r="460" spans="10:11" ht="12.5">
+    <row r="460" spans="10:11" ht="13.2">
       <c r="J460" s="6"/>
       <c r="K460" s="6"/>
     </row>
-    <row r="461" spans="10:11" ht="12.5">
+    <row r="461" spans="10:11" ht="13.2">
       <c r="J461" s="6"/>
       <c r="K461" s="6"/>
     </row>
-    <row r="462" spans="10:11" ht="12.5">
+    <row r="462" spans="10:11" ht="13.2">
       <c r="J462" s="6"/>
       <c r="K462" s="6"/>
     </row>
-    <row r="463" spans="10:11" ht="12.5">
+    <row r="463" spans="10:11" ht="13.2">
       <c r="J463" s="6"/>
       <c r="K463" s="6"/>
     </row>
-    <row r="464" spans="10:11" ht="12.5">
+    <row r="464" spans="10:11" ht="13.2">
       <c r="J464" s="6"/>
       <c r="K464" s="6"/>
     </row>
-    <row r="465" spans="10:11" ht="12.5">
+    <row r="465" spans="10:11" ht="13.2">
       <c r="J465" s="6"/>
       <c r="K465" s="6"/>
     </row>
-    <row r="466" spans="10:11" ht="12.5">
+    <row r="466" spans="10:11" ht="13.2">
       <c r="J466" s="6"/>
       <c r="K466" s="6"/>
     </row>
-    <row r="467" spans="10:11" ht="12.5">
+    <row r="467" spans="10:11" ht="13.2">
       <c r="J467" s="6"/>
       <c r="K467" s="6"/>
     </row>
-    <row r="468" spans="10:11" ht="12.5">
+    <row r="468" spans="10:11" ht="13.2">
       <c r="J468" s="6"/>
       <c r="K468" s="6"/>
     </row>
-    <row r="469" spans="10:11" ht="12.5">
+    <row r="469" spans="10:11" ht="13.2">
       <c r="J469" s="6"/>
       <c r="K469" s="6"/>
     </row>
-    <row r="470" spans="10:11" ht="12.5">
+    <row r="470" spans="10:11" ht="13.2">
       <c r="J470" s="6"/>
       <c r="K470" s="6"/>
     </row>
-    <row r="471" spans="10:11" ht="12.5">
+    <row r="471" spans="10:11" ht="13.2">
       <c r="J471" s="6"/>
       <c r="K471" s="6"/>
     </row>
-    <row r="472" spans="10:11" ht="12.5">
+    <row r="472" spans="10:11" ht="13.2">
       <c r="J472" s="6"/>
       <c r="K472" s="6"/>
     </row>
-    <row r="473" spans="10:11" ht="12.5">
+    <row r="473" spans="10:11" ht="13.2">
       <c r="J473" s="6"/>
       <c r="K473" s="6"/>
     </row>
-    <row r="474" spans="10:11" ht="12.5">
+    <row r="474" spans="10:11" ht="13.2">
       <c r="J474" s="6"/>
       <c r="K474" s="6"/>
     </row>
-    <row r="475" spans="10:11" ht="12.5">
+    <row r="475" spans="10:11" ht="13.2">
       <c r="J475" s="6"/>
       <c r="K475" s="6"/>
     </row>
-    <row r="476" spans="10:11" ht="12.5">
+    <row r="476" spans="10:11" ht="13.2">
       <c r="J476" s="6"/>
       <c r="K476" s="6"/>
     </row>
-    <row r="477" spans="10:11" ht="12.5">
+    <row r="477" spans="10:11" ht="13.2">
       <c r="J477" s="6"/>
       <c r="K477" s="6"/>
     </row>
-    <row r="478" spans="10:11" ht="12.5">
+    <row r="478" spans="10:11" ht="13.2">
       <c r="J478" s="6"/>
       <c r="K478" s="6"/>
     </row>
-    <row r="479" spans="10:11" ht="12.5">
+    <row r="479" spans="10:11" ht="13.2">
       <c r="J479" s="6"/>
       <c r="K479" s="6"/>
     </row>
-    <row r="480" spans="10:11" ht="12.5">
+    <row r="480" spans="10:11" ht="13.2">
       <c r="J480" s="6"/>
       <c r="K480" s="6"/>
     </row>
-    <row r="481" spans="10:11" ht="12.5">
+    <row r="481" spans="10:11" ht="13.2">
       <c r="J481" s="6"/>
       <c r="K481" s="6"/>
     </row>
-    <row r="482" spans="10:11" ht="12.5">
+    <row r="482" spans="10:11" ht="13.2">
       <c r="J482" s="6"/>
       <c r="K482" s="6"/>
     </row>
-    <row r="483" spans="10:11" ht="12.5">
+    <row r="483" spans="10:11" ht="13.2">
       <c r="J483" s="6"/>
       <c r="K483" s="6"/>
     </row>
-    <row r="484" spans="10:11" ht="12.5">
+    <row r="484" spans="10:11" ht="13.2">
       <c r="J484" s="6"/>
       <c r="K484" s="6"/>
     </row>
-    <row r="485" spans="10:11" ht="12.5">
+    <row r="485" spans="10:11" ht="13.2">
       <c r="J485" s="6"/>
       <c r="K485" s="6"/>
     </row>
-    <row r="486" spans="10:11" ht="12.5">
+    <row r="486" spans="10:11" ht="13.2">
       <c r="J486" s="6"/>
       <c r="K486" s="6"/>
     </row>
-    <row r="487" spans="10:11" ht="12.5">
+    <row r="487" spans="10:11" ht="13.2">
       <c r="J487" s="6"/>
       <c r="K487" s="6"/>
     </row>
-    <row r="488" spans="10:11" ht="12.5">
+    <row r="488" spans="10:11" ht="13.2">
       <c r="J488" s="6"/>
       <c r="K488" s="6"/>
     </row>
-    <row r="489" spans="10:11" ht="12.5">
+    <row r="489" spans="10:11" ht="13.2">
       <c r="J489" s="6"/>
       <c r="K489" s="6"/>
     </row>
-    <row r="490" spans="10:11" ht="12.5">
+    <row r="490" spans="10:11" ht="13.2">
       <c r="J490" s="6"/>
       <c r="K490" s="6"/>
     </row>
-    <row r="491" spans="10:11" ht="12.5">
+    <row r="491" spans="10:11" ht="13.2">
       <c r="J491" s="6"/>
       <c r="K491" s="6"/>
     </row>
-    <row r="492" spans="10:11" ht="12.5">
+    <row r="492" spans="10:11" ht="13.2">
       <c r="J492" s="6"/>
       <c r="K492" s="6"/>
     </row>
-    <row r="493" spans="10:11" ht="12.5">
+    <row r="493" spans="10:11" ht="13.2">
       <c r="J493" s="6"/>
       <c r="K493" s="6"/>
     </row>
-    <row r="494" spans="10:11" ht="12.5">
+    <row r="494" spans="10:11" ht="13.2">
       <c r="J494" s="6"/>
       <c r="K494" s="6"/>
     </row>
-    <row r="495" spans="10:11" ht="12.5">
+    <row r="495" spans="10:11" ht="13.2">
       <c r="J495" s="6"/>
       <c r="K495" s="6"/>
     </row>
-    <row r="496" spans="10:11" ht="12.5">
+    <row r="496" spans="10:11" ht="13.2">
       <c r="J496" s="6"/>
       <c r="K496" s="6"/>
     </row>
-    <row r="497" spans="10:11" ht="12.5">
+    <row r="497" spans="10:11" ht="13.2">
       <c r="J497" s="6"/>
       <c r="K497" s="6"/>
     </row>
-    <row r="498" spans="10:11" ht="12.5">
+    <row r="498" spans="10:11" ht="13.2">
       <c r="J498" s="6"/>
       <c r="K498" s="6"/>
     </row>
-    <row r="499" spans="10:11" ht="12.5">
+    <row r="499" spans="10:11" ht="13.2">
       <c r="J499" s="6"/>
       <c r="K499" s="6"/>
     </row>
-    <row r="500" spans="10:11" ht="12.5">
+    <row r="500" spans="10:11" ht="13.2">
       <c r="J500" s="6"/>
       <c r="K500" s="6"/>
     </row>
-    <row r="501" spans="10:11" ht="12.5">
+    <row r="501" spans="10:11" ht="13.2">
       <c r="J501" s="6"/>
       <c r="K501" s="6"/>
     </row>
-    <row r="502" spans="10:11" ht="12.5">
+    <row r="502" spans="10:11" ht="13.2">
       <c r="J502" s="6"/>
       <c r="K502" s="6"/>
     </row>
-    <row r="503" spans="10:11" ht="12.5">
+    <row r="503" spans="10:11" ht="13.2">
       <c r="J503" s="6"/>
       <c r="K503" s="6"/>
     </row>
-    <row r="504" spans="10:11" ht="12.5">
+    <row r="504" spans="10:11" ht="13.2">
       <c r="J504" s="6"/>
       <c r="K504" s="6"/>
     </row>
-    <row r="505" spans="10:11" ht="12.5">
+    <row r="505" spans="10:11" ht="13.2">
       <c r="J505" s="6"/>
       <c r="K505" s="6"/>
     </row>
-    <row r="506" spans="10:11" ht="12.5">
+    <row r="506" spans="10:11" ht="13.2">
       <c r="J506" s="6"/>
       <c r="K506" s="6"/>
     </row>
-    <row r="507" spans="10:11" ht="12.5">
+    <row r="507" spans="10:11" ht="13.2">
       <c r="J507" s="6"/>
       <c r="K507" s="6"/>
     </row>
-    <row r="508" spans="10:11" ht="12.5">
+    <row r="508" spans="10:11" ht="13.2">
       <c r="J508" s="6"/>
       <c r="K508" s="6"/>
     </row>
-    <row r="509" spans="10:11" ht="12.5">
+    <row r="509" spans="10:11" ht="13.2">
       <c r="J509" s="6"/>
       <c r="K509" s="6"/>
     </row>
-    <row r="510" spans="10:11" ht="12.5">
+    <row r="510" spans="10:11" ht="13.2">
       <c r="J510" s="6"/>
       <c r="K510" s="6"/>
     </row>
-    <row r="511" spans="10:11" ht="12.5">
+    <row r="511" spans="10:11" ht="13.2">
       <c r="J511" s="6"/>
       <c r="K511" s="6"/>
     </row>
-    <row r="512" spans="10:11" ht="12.5">
+    <row r="512" spans="10:11" ht="13.2">
       <c r="J512" s="6"/>
       <c r="K512" s="6"/>
     </row>
-    <row r="513" spans="10:11" ht="12.5">
+    <row r="513" spans="10:11" ht="13.2">
       <c r="J513" s="6"/>
       <c r="K513" s="6"/>
     </row>
-    <row r="514" spans="10:11" ht="12.5">
+    <row r="514" spans="10:11" ht="13.2">
       <c r="J514" s="6"/>
       <c r="K514" s="6"/>
     </row>
-    <row r="515" spans="10:11" ht="12.5">
+    <row r="515" spans="10:11" ht="13.2">
       <c r="J515" s="6"/>
       <c r="K515" s="6"/>
     </row>
-    <row r="516" spans="10:11" ht="12.5">
+    <row r="516" spans="10:11" ht="13.2">
       <c r="J516" s="6"/>
       <c r="K516" s="6"/>
     </row>
-    <row r="517" spans="10:11" ht="12.5">
+    <row r="517" spans="10:11" ht="13.2">
       <c r="J517" s="6"/>
       <c r="K517" s="6"/>
     </row>
-    <row r="518" spans="10:11" ht="12.5">
+    <row r="518" spans="10:11" ht="13.2">
       <c r="J518" s="6"/>
       <c r="K518" s="6"/>
     </row>
-    <row r="519" spans="10:11" ht="12.5">
+    <row r="519" spans="10:11" ht="13.2">
       <c r="J519" s="6"/>
       <c r="K519" s="6"/>
     </row>
-    <row r="520" spans="10:11" ht="12.5">
+    <row r="520" spans="10:11" ht="13.2">
       <c r="J520" s="6"/>
       <c r="K520" s="6"/>
     </row>
-    <row r="521" spans="10:11" ht="12.5">
+    <row r="521" spans="10:11" ht="13.2">
       <c r="J521" s="6"/>
       <c r="K521" s="6"/>
     </row>
-    <row r="522" spans="10:11" ht="12.5">
+    <row r="522" spans="10:11" ht="13.2">
       <c r="J522" s="6"/>
       <c r="K522" s="6"/>
     </row>
-    <row r="523" spans="10:11" ht="12.5">
+    <row r="523" spans="10:11" ht="13.2">
       <c r="J523" s="6"/>
       <c r="K523" s="6"/>
     </row>
-    <row r="524" spans="10:11" ht="12.5">
+    <row r="524" spans="10:11" ht="13.2">
       <c r="J524" s="6"/>
       <c r="K524" s="6"/>
     </row>
-    <row r="525" spans="10:11" ht="12.5">
+    <row r="525" spans="10:11" ht="13.2">
       <c r="J525" s="6"/>
       <c r="K525" s="6"/>
     </row>
-    <row r="526" spans="10:11" ht="12.5">
+    <row r="526" spans="10:11" ht="13.2">
       <c r="J526" s="6"/>
       <c r="K526" s="6"/>
     </row>
-    <row r="527" spans="10:11" ht="12.5">
+    <row r="527" spans="10:11" ht="13.2">
       <c r="J527" s="6"/>
       <c r="K527" s="6"/>
     </row>
-    <row r="528" spans="10:11" ht="12.5">
+    <row r="528" spans="10:11" ht="13.2">
       <c r="J528" s="6"/>
       <c r="K528" s="6"/>
     </row>
-    <row r="529" spans="10:11" ht="12.5">
+    <row r="529" spans="10:11" ht="13.2">
       <c r="J529" s="6"/>
       <c r="K529" s="6"/>
     </row>
-    <row r="530" spans="10:11" ht="12.5">
+    <row r="530" spans="10:11" ht="13.2">
       <c r="J530" s="6"/>
       <c r="K530" s="6"/>
     </row>
-    <row r="531" spans="10:11" ht="12.5">
+    <row r="531" spans="10:11" ht="13.2">
       <c r="J531" s="6"/>
       <c r="K531" s="6"/>
     </row>
-    <row r="532" spans="10:11" ht="12.5">
+    <row r="532" spans="10:11" ht="13.2">
       <c r="J532" s="6"/>
       <c r="K532" s="6"/>
     </row>
-    <row r="533" spans="10:11" ht="12.5">
+    <row r="533" spans="10:11" ht="13.2">
       <c r="J533" s="6"/>
       <c r="K533" s="6"/>
     </row>
-    <row r="534" spans="10:11" ht="12.5">
+    <row r="534" spans="10:11" ht="13.2">
       <c r="J534" s="6"/>
       <c r="K534" s="6"/>
     </row>
-    <row r="535" spans="10:11" ht="12.5">
+    <row r="535" spans="10:11" ht="13.2">
       <c r="J535" s="6"/>
       <c r="K535" s="6"/>
     </row>
-    <row r="536" spans="10:11" ht="12.5">
+    <row r="536" spans="10:11" ht="13.2">
       <c r="J536" s="6"/>
       <c r="K536" s="6"/>
     </row>
-    <row r="537" spans="10:11" ht="12.5">
+    <row r="537" spans="10:11" ht="13.2">
       <c r="J537" s="6"/>
       <c r="K537" s="6"/>
     </row>
-    <row r="538" spans="10:11" ht="12.5">
+    <row r="538" spans="10:11" ht="13.2">
       <c r="J538" s="6"/>
       <c r="K538" s="6"/>
     </row>
-    <row r="539" spans="10:11" ht="12.5">
+    <row r="539" spans="10:11" ht="13.2">
       <c r="J539" s="6"/>
       <c r="K539" s="6"/>
     </row>
-    <row r="540" spans="10:11" ht="12.5">
+    <row r="540" spans="10:11" ht="13.2">
       <c r="J540" s="6"/>
       <c r="K540" s="6"/>
     </row>
-    <row r="541" spans="10:11" ht="12.5">
+    <row r="541" spans="10:11" ht="13.2">
       <c r="J541" s="6"/>
       <c r="K541" s="6"/>
     </row>
-    <row r="542" spans="10:11" ht="12.5">
+    <row r="542" spans="10:11" ht="13.2">
       <c r="J542" s="6"/>
       <c r="K542" s="6"/>
     </row>
-    <row r="543" spans="10:11" ht="12.5">
+    <row r="543" spans="10:11" ht="13.2">
       <c r="J543" s="6"/>
       <c r="K543" s="6"/>
     </row>
-    <row r="544" spans="10:11" ht="12.5">
+    <row r="544" spans="10:11" ht="13.2">
       <c r="J544" s="6"/>
       <c r="K544" s="6"/>
     </row>
-    <row r="545" spans="10:11" ht="12.5">
+    <row r="545" spans="10:11" ht="13.2">
       <c r="J545" s="6"/>
       <c r="K545" s="6"/>
     </row>
-    <row r="546" spans="10:11" ht="12.5">
+    <row r="546" spans="10:11" ht="13.2">
       <c r="J546" s="6"/>
       <c r="K546" s="6"/>
     </row>
-    <row r="547" spans="10:11" ht="12.5">
+    <row r="547" spans="10:11" ht="13.2">
       <c r="J547" s="6"/>
       <c r="K547" s="6"/>
     </row>
-    <row r="548" spans="10:11" ht="12.5">
+    <row r="548" spans="10:11" ht="13.2">
       <c r="J548" s="6"/>
       <c r="K548" s="6"/>
     </row>
-    <row r="549" spans="10:11" ht="12.5">
+    <row r="549" spans="10:11" ht="13.2">
       <c r="J549" s="6"/>
       <c r="K549" s="6"/>
     </row>
-    <row r="550" spans="10:11" ht="12.5">
+    <row r="550" spans="10:11" ht="13.2">
       <c r="J550" s="6"/>
       <c r="K550" s="6"/>
     </row>
-    <row r="551" spans="10:11" ht="12.5">
+    <row r="551" spans="10:11" ht="13.2">
       <c r="J551" s="6"/>
       <c r="K551" s="6"/>
     </row>
-    <row r="552" spans="10:11" ht="12.5">
+    <row r="552" spans="10:11" ht="13.2">
       <c r="J552" s="6"/>
       <c r="K552" s="6"/>
     </row>
-    <row r="553" spans="10:11" ht="12.5">
+    <row r="553" spans="10:11" ht="13.2">
       <c r="J553" s="6"/>
       <c r="K553" s="6"/>
     </row>
-    <row r="554" spans="10:11" ht="12.5">
+    <row r="554" spans="10:11" ht="13.2">
       <c r="J554" s="6"/>
       <c r="K554" s="6"/>
     </row>
-    <row r="555" spans="10:11" ht="12.5">
+    <row r="555" spans="10:11" ht="13.2">
       <c r="J555" s="6"/>
       <c r="K555" s="6"/>
     </row>
-    <row r="556" spans="10:11" ht="12.5">
+    <row r="556" spans="10:11" ht="13.2">
       <c r="J556" s="6"/>
       <c r="K556" s="6"/>
     </row>
-    <row r="557" spans="10:11" ht="12.5">
+    <row r="557" spans="10:11" ht="13.2">
       <c r="J557" s="6"/>
       <c r="K557" s="6"/>
     </row>
-    <row r="558" spans="10:11" ht="12.5">
+    <row r="558" spans="10:11" ht="13.2">
       <c r="J558" s="6"/>
       <c r="K558" s="6"/>
     </row>
-    <row r="559" spans="10:11" ht="12.5">
+    <row r="559" spans="10:11" ht="13.2">
       <c r="J559" s="6"/>
       <c r="K559" s="6"/>
     </row>
-    <row r="560" spans="10:11" ht="12.5">
+    <row r="560" spans="10:11" ht="13.2">
       <c r="J560" s="6"/>
       <c r="K560" s="6"/>
     </row>
-    <row r="561" spans="10:11" ht="12.5">
+    <row r="561" spans="10:11" ht="13.2">
       <c r="J561" s="6"/>
       <c r="K561" s="6"/>
     </row>
-    <row r="562" spans="10:11" ht="12.5">
+    <row r="562" spans="10:11" ht="13.2">
       <c r="J562" s="6"/>
       <c r="K562" s="6"/>
     </row>
-    <row r="563" spans="10:11" ht="12.5">
+    <row r="563" spans="10:11" ht="13.2">
       <c r="J563" s="6"/>
       <c r="K563" s="6"/>
     </row>
-    <row r="564" spans="10:11" ht="12.5">
+    <row r="564" spans="10:11" ht="13.2">
       <c r="J564" s="6"/>
       <c r="K564" s="6"/>
     </row>
-    <row r="565" spans="10:11" ht="12.5">
+    <row r="565" spans="10:11" ht="13.2">
       <c r="J565" s="6"/>
       <c r="K565" s="6"/>
     </row>
-    <row r="566" spans="10:11" ht="12.5">
+    <row r="566" spans="10:11" ht="13.2">
       <c r="J566" s="6"/>
       <c r="K566" s="6"/>
     </row>
-    <row r="567" spans="10:11" ht="12.5">
+    <row r="567" spans="10:11" ht="13.2">
       <c r="J567" s="6"/>
       <c r="K567" s="6"/>
     </row>
-    <row r="568" spans="10:11" ht="12.5">
+    <row r="568" spans="10:11" ht="13.2">
       <c r="J568" s="6"/>
       <c r="K568" s="6"/>
     </row>
-    <row r="569" spans="10:11" ht="12.5">
+    <row r="569" spans="10:11" ht="13.2">
       <c r="J569" s="6"/>
       <c r="K569" s="6"/>
     </row>
-    <row r="570" spans="10:11" ht="12.5">
+    <row r="570" spans="10:11" ht="13.2">
       <c r="J570" s="6"/>
       <c r="K570" s="6"/>
     </row>
-    <row r="571" spans="10:11" ht="12.5">
+    <row r="571" spans="10:11" ht="13.2">
       <c r="J571" s="6"/>
       <c r="K571" s="6"/>
     </row>
-    <row r="572" spans="10:11" ht="12.5">
+    <row r="572" spans="10:11" ht="13.2">
       <c r="J572" s="6"/>
       <c r="K572" s="6"/>
     </row>
-    <row r="573" spans="10:11" ht="12.5">
+    <row r="573" spans="10:11" ht="13.2">
       <c r="J573" s="6"/>
       <c r="K573" s="6"/>
     </row>
-    <row r="574" spans="10:11" ht="12.5">
+    <row r="574" spans="10:11" ht="13.2">
       <c r="J574" s="6"/>
       <c r="K574" s="6"/>
     </row>
-    <row r="575" spans="10:11" ht="12.5">
+    <row r="575" spans="10:11" ht="13.2">
       <c r="J575" s="6"/>
       <c r="K575" s="6"/>
     </row>
-    <row r="576" spans="10:11" ht="12.5">
+    <row r="576" spans="10:11" ht="13.2">
       <c r="J576" s="6"/>
       <c r="K576" s="6"/>
     </row>
-    <row r="577" spans="10:11" ht="12.5">
+    <row r="577" spans="10:11" ht="13.2">
       <c r="J577" s="6"/>
       <c r="K577" s="6"/>
     </row>
-    <row r="578" spans="10:11" ht="12.5">
+    <row r="578" spans="10:11" ht="13.2">
       <c r="J578" s="6"/>
       <c r="K578" s="6"/>
     </row>
-    <row r="579" spans="10:11" ht="12.5">
+    <row r="579" spans="10:11" ht="13.2">
       <c r="J579" s="6"/>
       <c r="K579" s="6"/>
     </row>
-    <row r="580" spans="10:11" ht="12.5">
+    <row r="580" spans="10:11" ht="13.2">
       <c r="J580" s="6"/>
       <c r="K580" s="6"/>
     </row>
-    <row r="581" spans="10:11" ht="12.5">
+    <row r="581" spans="10:11" ht="13.2">
       <c r="J581" s="6"/>
       <c r="K581" s="6"/>
     </row>
-    <row r="582" spans="10:11" ht="12.5">
+    <row r="582" spans="10:11" ht="13.2">
       <c r="J582" s="6"/>
       <c r="K582" s="6"/>
     </row>
-    <row r="583" spans="10:11" ht="12.5">
+    <row r="583" spans="10:11" ht="13.2">
       <c r="J583" s="6"/>
       <c r="K583" s="6"/>
     </row>
-    <row r="584" spans="10:11" ht="12.5">
+    <row r="584" spans="10:11" ht="13.2">
       <c r="J584" s="6"/>
       <c r="K584" s="6"/>
     </row>
-    <row r="585" spans="10:11" ht="12.5">
+    <row r="585" spans="10:11" ht="13.2">
       <c r="J585" s="6"/>
       <c r="K585" s="6"/>
     </row>
-    <row r="586" spans="10:11" ht="12.5">
+    <row r="586" spans="10:11" ht="13.2">
       <c r="J586" s="6"/>
       <c r="K586" s="6"/>
     </row>
-    <row r="587" spans="10:11" ht="12.5">
+    <row r="587" spans="10:11" ht="13.2">
       <c r="J587" s="6"/>
       <c r="K587" s="6"/>
     </row>
-    <row r="588" spans="10:11" ht="12.5">
+    <row r="588" spans="10:11" ht="13.2">
       <c r="J588" s="6"/>
       <c r="K588" s="6"/>
     </row>
-    <row r="589" spans="10:11" ht="12.5">
+    <row r="589" spans="10:11" ht="13.2">
       <c r="J589" s="6"/>
       <c r="K589" s="6"/>
     </row>
-    <row r="590" spans="10:11" ht="12.5">
+    <row r="590" spans="10:11" ht="13.2">
       <c r="J590" s="6"/>
       <c r="K590" s="6"/>
     </row>
-    <row r="591" spans="10:11" ht="12.5">
+    <row r="591" spans="10:11" ht="13.2">
       <c r="J591" s="6"/>
       <c r="K591" s="6"/>
     </row>
-    <row r="592" spans="10:11" ht="12.5">
+    <row r="592" spans="10:11" ht="13.2">
       <c r="J592" s="6"/>
       <c r="K592" s="6"/>
     </row>
-    <row r="593" spans="10:11" ht="12.5">
+    <row r="593" spans="10:11" ht="13.2">
       <c r="J593" s="6"/>
       <c r="K593" s="6"/>
     </row>
-    <row r="594" spans="10:11" ht="12.5">
+    <row r="594" spans="10:11" ht="13.2">
       <c r="J594" s="6"/>
       <c r="K594" s="6"/>
     </row>
-    <row r="595" spans="10:11" ht="12.5">
+    <row r="595" spans="10:11" ht="13.2">
       <c r="J595" s="6"/>
       <c r="K595" s="6"/>
     </row>
-    <row r="596" spans="10:11" ht="12.5">
+    <row r="596" spans="10:11" ht="13.2">
       <c r="J596" s="6"/>
       <c r="K596" s="6"/>
     </row>
-    <row r="597" spans="10:11" ht="12.5">
+    <row r="597" spans="10:11" ht="13.2">
       <c r="J597" s="6"/>
       <c r="K597" s="6"/>
     </row>
-    <row r="598" spans="10:11" ht="12.5">
+    <row r="598" spans="10:11" ht="13.2">
       <c r="J598" s="6"/>
       <c r="K598" s="6"/>
     </row>
-    <row r="599" spans="10:11" ht="12.5">
+    <row r="599" spans="10:11" ht="13.2">
       <c r="J599" s="6"/>
       <c r="K599" s="6"/>
     </row>
-    <row r="600" spans="10:11" ht="12.5">
+    <row r="600" spans="10:11" ht="13.2">
       <c r="J600" s="6"/>
       <c r="K600" s="6"/>
     </row>
-    <row r="601" spans="10:11" ht="12.5">
+    <row r="601" spans="10:11" ht="13.2">
       <c r="J601" s="6"/>
       <c r="K601" s="6"/>
     </row>
-    <row r="602" spans="10:11" ht="12.5">
+    <row r="602" spans="10:11" ht="13.2">
       <c r="J602" s="6"/>
       <c r="K602" s="6"/>
     </row>
-    <row r="603" spans="10:11" ht="12.5">
+    <row r="603" spans="10:11" ht="13.2">
       <c r="J603" s="6"/>
       <c r="K603" s="6"/>
     </row>
-    <row r="604" spans="10:11" ht="12.5">
+    <row r="604" spans="10:11" ht="13.2">
       <c r="J604" s="6"/>
       <c r="K604" s="6"/>
     </row>
-    <row r="605" spans="10:11" ht="12.5">
+    <row r="605" spans="10:11" ht="13.2">
       <c r="J605" s="6"/>
       <c r="K605" s="6"/>
     </row>
-    <row r="606" spans="10:11" ht="12.5">
+    <row r="606" spans="10:11" ht="13.2">
       <c r="J606" s="6"/>
       <c r="K606" s="6"/>
     </row>
-    <row r="607" spans="10:11" ht="12.5">
+    <row r="607" spans="10:11" ht="13.2">
       <c r="J607" s="6"/>
       <c r="K607" s="6"/>
     </row>
-    <row r="608" spans="10:11" ht="12.5">
+    <row r="608" spans="10:11" ht="13.2">
       <c r="J608" s="6"/>
       <c r="K608" s="6"/>
     </row>
-    <row r="609" spans="10:11" ht="12.5">
+    <row r="609" spans="10:11" ht="13.2">
       <c r="J609" s="6"/>
       <c r="K609" s="6"/>
     </row>
-    <row r="610" spans="10:11" ht="12.5">
+    <row r="610" spans="10:11" ht="13.2">
       <c r="J610" s="6"/>
       <c r="K610" s="6"/>
     </row>
-    <row r="611" spans="10:11" ht="12.5">
+    <row r="611" spans="10:11" ht="13.2">
       <c r="J611" s="6"/>
       <c r="K611" s="6"/>
     </row>
-    <row r="612" spans="10:11" ht="12.5">
+    <row r="612" spans="10:11" ht="13.2">
       <c r="J612" s="6"/>
       <c r="K612" s="6"/>
     </row>
-    <row r="613" spans="10:11" ht="12.5">
+    <row r="613" spans="10:11" ht="13.2">
       <c r="J613" s="6"/>
       <c r="K613" s="6"/>
     </row>
-    <row r="614" spans="10:11" ht="12.5">
+    <row r="614" spans="10:11" ht="13.2">
       <c r="J614" s="6"/>
       <c r="K614" s="6"/>
     </row>
-    <row r="615" spans="10:11" ht="12.5">
+    <row r="615" spans="10:11" ht="13.2">
       <c r="J615" s="6"/>
       <c r="K615" s="6"/>
     </row>
-    <row r="616" spans="10:11" ht="12.5">
+    <row r="616" spans="10:11" ht="13.2">
       <c r="J616" s="6"/>
       <c r="K616" s="6"/>
     </row>
-    <row r="617" spans="10:11" ht="12.5">
+    <row r="617" spans="10:11" ht="13.2">
       <c r="J617" s="6"/>
       <c r="K617" s="6"/>
     </row>
-    <row r="618" spans="10:11" ht="12.5">
+    <row r="618" spans="10:11" ht="13.2">
       <c r="J618" s="6"/>
       <c r="K618" s="6"/>
     </row>
-    <row r="619" spans="10:11" ht="12.5">
+    <row r="619" spans="10:11" ht="13.2">
       <c r="J619" s="6"/>
       <c r="K619" s="6"/>
     </row>
-    <row r="620" spans="10:11" ht="12.5">
+    <row r="620" spans="10:11" ht="13.2">
       <c r="J620" s="6"/>
       <c r="K620" s="6"/>
     </row>
-    <row r="621" spans="10:11" ht="12.5">
+    <row r="621" spans="10:11" ht="13.2">
       <c r="J621" s="6"/>
       <c r="K621" s="6"/>
     </row>
-    <row r="622" spans="10:11" ht="12.5">
+    <row r="622" spans="10:11" ht="13.2">
       <c r="J622" s="6"/>
       <c r="K622" s="6"/>
     </row>
-    <row r="623" spans="10:11" ht="12.5">
+    <row r="623" spans="10:11" ht="13.2">
       <c r="J623" s="6"/>
       <c r="K623" s="6"/>
     </row>
-    <row r="624" spans="10:11" ht="12.5">
+    <row r="624" spans="10:11" ht="13.2">
       <c r="J624" s="6"/>
       <c r="K624" s="6"/>
     </row>
-    <row r="625" spans="10:11" ht="12.5">
+    <row r="625" spans="10:11" ht="13.2">
       <c r="J625" s="6"/>
       <c r="K625" s="6"/>
     </row>
-    <row r="626" spans="10:11" ht="12.5">
+    <row r="626" spans="10:11" ht="13.2">
       <c r="J626" s="6"/>
       <c r="K626" s="6"/>
     </row>
-    <row r="627" spans="10:11" ht="12.5">
+    <row r="627" spans="10:11" ht="13.2">
       <c r="J627" s="6"/>
       <c r="K627" s="6"/>
     </row>
-    <row r="628" spans="10:11" ht="12.5">
+    <row r="628" spans="10:11" ht="13.2">
       <c r="J628" s="6"/>
       <c r="K628" s="6"/>
     </row>
-    <row r="629" spans="10:11" ht="12.5">
+    <row r="629" spans="10:11" ht="13.2">
       <c r="J629" s="6"/>
       <c r="K629" s="6"/>
     </row>
-    <row r="630" spans="10:11" ht="12.5">
+    <row r="630" spans="10:11" ht="13.2">
       <c r="J630" s="6"/>
       <c r="K630" s="6"/>
     </row>
-    <row r="631" spans="10:11" ht="12.5">
+    <row r="631" spans="10:11" ht="13.2">
       <c r="J631" s="6"/>
       <c r="K631" s="6"/>
     </row>
-    <row r="632" spans="10:11" ht="12.5">
+    <row r="632" spans="10:11" ht="13.2">
       <c r="J632" s="6"/>
       <c r="K632" s="6"/>
     </row>
-    <row r="633" spans="10:11" ht="12.5">
+    <row r="633" spans="10:11" ht="13.2">
       <c r="J633" s="6"/>
       <c r="K633" s="6"/>
     </row>
-    <row r="634" spans="10:11" ht="12.5">
+    <row r="634" spans="10:11" ht="13.2">
       <c r="J634" s="6"/>
       <c r="K634" s="6"/>
     </row>
-    <row r="635" spans="10:11" ht="12.5">
+    <row r="635" spans="10:11" ht="13.2">
       <c r="J635" s="6"/>
       <c r="K635" s="6"/>
     </row>
-    <row r="636" spans="10:11" ht="12.5">
+    <row r="636" spans="10:11" ht="13.2">
       <c r="J636" s="6"/>
       <c r="K636" s="6"/>
     </row>
-    <row r="637" spans="10:11" ht="12.5">
+    <row r="637" spans="10:11" ht="13.2">
       <c r="J637" s="6"/>
       <c r="K637" s="6"/>
     </row>
-    <row r="638" spans="10:11" ht="12.5">
+    <row r="638" spans="10:11" ht="13.2">
       <c r="J638" s="6"/>
       <c r="K638" s="6"/>
     </row>
-    <row r="639" spans="10:11" ht="12.5">
+    <row r="639" spans="10:11" ht="13.2">
       <c r="J639" s="6"/>
       <c r="K639" s="6"/>
     </row>
-    <row r="640" spans="10:11" ht="12.5">
+    <row r="640" spans="10:11" ht="13.2">
       <c r="J640" s="6"/>
       <c r="K640" s="6"/>
     </row>
-    <row r="641" spans="10:11" ht="12.5">
+    <row r="641" spans="10:11" ht="13.2">
       <c r="J641" s="6"/>
       <c r="K641" s="6"/>
     </row>
-    <row r="642" spans="10:11" ht="12.5">
+    <row r="642" spans="10:11" ht="13.2">
       <c r="J642" s="6"/>
       <c r="K642" s="6"/>
     </row>
-    <row r="643" spans="10:11" ht="12.5">
+    <row r="643" spans="10:11" ht="13.2">
       <c r="J643" s="6"/>
       <c r="K643" s="6"/>
     </row>
-    <row r="644" spans="10:11" ht="12.5">
+    <row r="644" spans="10:11" ht="13.2">
       <c r="J644" s="6"/>
       <c r="K644" s="6"/>
     </row>
-    <row r="645" spans="10:11" ht="12.5">
+    <row r="645" spans="10:11" ht="13.2">
       <c r="J645" s="6"/>
       <c r="K645" s="6"/>
     </row>
-    <row r="646" spans="10:11" ht="12.5">
+    <row r="646" spans="10:11" ht="13.2">
       <c r="J646" s="6"/>
       <c r="K646" s="6"/>
     </row>
-    <row r="647" spans="10:11" ht="12.5">
+    <row r="647" spans="10:11" ht="13.2">
       <c r="J647" s="6"/>
       <c r="K647" s="6"/>
     </row>
-    <row r="648" spans="10:11" ht="12.5">
+    <row r="648" spans="10:11" ht="13.2">
       <c r="J648" s="6"/>
       <c r="K648" s="6"/>
     </row>
-    <row r="649" spans="10:11" ht="12.5">
+    <row r="649" spans="10:11" ht="13.2">
       <c r="J649" s="6"/>
       <c r="K649" s="6"/>
     </row>
-    <row r="650" spans="10:11" ht="12.5">
+    <row r="650" spans="10:11" ht="13.2">
       <c r="J650" s="6"/>
       <c r="K650" s="6"/>
     </row>
-    <row r="651" spans="10:11" ht="12.5">
+    <row r="651" spans="10:11" ht="13.2">
       <c r="J651" s="6"/>
       <c r="K651" s="6"/>
     </row>
-    <row r="652" spans="10:11" ht="12.5">
+    <row r="652" spans="10:11" ht="13.2">
       <c r="J652" s="6"/>
       <c r="K652" s="6"/>
     </row>
-    <row r="653" spans="10:11" ht="12.5">
+    <row r="653" spans="10:11" ht="13.2">
       <c r="J653" s="6"/>
       <c r="K653" s="6"/>
     </row>
-    <row r="654" spans="10:11" ht="12.5">
+    <row r="654" spans="10:11" ht="13.2">
       <c r="J654" s="6"/>
       <c r="K654" s="6"/>
     </row>
-    <row r="655" spans="10:11" ht="12.5">
+    <row r="655" spans="10:11" ht="13.2">
       <c r="J655" s="6"/>
       <c r="K655" s="6"/>
     </row>
-    <row r="656" spans="10:11" ht="12.5">
+    <row r="656" spans="10:11" ht="13.2">
       <c r="J656" s="6"/>
       <c r="K656" s="6"/>
     </row>
-    <row r="657" spans="10:11" ht="12.5">
+    <row r="657" spans="10:11" ht="13.2">
       <c r="J657" s="6"/>
       <c r="K657" s="6"/>
     </row>
-    <row r="658" spans="10:11" ht="12.5">
+    <row r="658" spans="10:11" ht="13.2">
       <c r="J658" s="6"/>
       <c r="K658" s="6"/>
     </row>
-    <row r="659" spans="10:11" ht="12.5">
+    <row r="659" spans="10:11" ht="13.2">
       <c r="J659" s="6"/>
       <c r="K659" s="6"/>
     </row>
-    <row r="660" spans="10:11" ht="12.5">
+    <row r="660" spans="10:11" ht="13.2">
       <c r="J660" s="6"/>
       <c r="K660" s="6"/>
     </row>
-    <row r="661" spans="10:11" ht="12.5">
+    <row r="661" spans="10:11" ht="13.2">
       <c r="J661" s="6"/>
       <c r="K661" s="6"/>
     </row>
-    <row r="662" spans="10:11" ht="12.5">
+    <row r="662" spans="10:11" ht="13.2">
       <c r="J662" s="6"/>
       <c r="K662" s="6"/>
     </row>
-    <row r="663" spans="10:11" ht="12.5">
+    <row r="663" spans="10:11" ht="13.2">
       <c r="J663" s="6"/>
       <c r="K663" s="6"/>
     </row>
-    <row r="664" spans="10:11" ht="12.5">
+    <row r="664" spans="10:11" ht="13.2">
       <c r="J664" s="6"/>
       <c r="K664" s="6"/>
     </row>
-    <row r="665" spans="10:11" ht="12.5">
+    <row r="665" spans="10:11" ht="13.2">
       <c r="J665" s="6"/>
       <c r="K665" s="6"/>
     </row>
-    <row r="666" spans="10:11" ht="12.5">
+    <row r="666" spans="10:11" ht="13.2">
       <c r="J666" s="6"/>
       <c r="K666" s="6"/>
     </row>
-    <row r="667" spans="10:11" ht="12.5">
+    <row r="667" spans="10:11" ht="13.2">
       <c r="J667" s="6"/>
       <c r="K667" s="6"/>
     </row>
-    <row r="668" spans="10:11" ht="12.5">
+    <row r="668" spans="10:11" ht="13.2">
       <c r="J668" s="6"/>
       <c r="K668" s="6"/>
     </row>
-    <row r="669" spans="10:11" ht="12.5">
+    <row r="669" spans="10:11" ht="13.2">
       <c r="J669" s="6"/>
       <c r="K669" s="6"/>
     </row>
-    <row r="670" spans="10:11" ht="12.5">
+    <row r="670" spans="10:11" ht="13.2">
       <c r="J670" s="6"/>
       <c r="K670" s="6"/>
     </row>
-    <row r="671" spans="10:11" ht="12.5">
+    <row r="671" spans="10:11" ht="13.2">
       <c r="J671" s="6"/>
       <c r="K671" s="6"/>
     </row>
-    <row r="672" spans="10:11" ht="12.5">
+    <row r="672" spans="10:11" ht="13.2">
       <c r="J672" s="6"/>
       <c r="K672" s="6"/>
     </row>
-    <row r="673" spans="10:11" ht="12.5">
+    <row r="673" spans="10:11" ht="13.2">
       <c r="J673" s="6"/>
       <c r="K673" s="6"/>
     </row>
-    <row r="674" spans="10:11" ht="12.5">
+    <row r="674" spans="10:11" ht="13.2">
       <c r="J674" s="6"/>
       <c r="K674" s="6"/>
     </row>
-    <row r="675" spans="10:11" ht="12.5">
+    <row r="675" spans="10:11" ht="13.2">
       <c r="J675" s="6"/>
       <c r="K675" s="6"/>
     </row>
-    <row r="676" spans="10:11" ht="12.5">
+    <row r="676" spans="10:11" ht="13.2">
       <c r="J676" s="6"/>
       <c r="K676" s="6"/>
     </row>
-    <row r="677" spans="10:11" ht="12.5">
+    <row r="677" spans="10:11" ht="13.2">
       <c r="J677" s="6"/>
       <c r="K677" s="6"/>
     </row>
-    <row r="678" spans="10:11" ht="12.5">
+    <row r="678" spans="10:11" ht="13.2">
       <c r="J678" s="6"/>
       <c r="K678" s="6"/>
     </row>
-    <row r="679" spans="10:11" ht="12.5">
+    <row r="679" spans="10:11" ht="13.2">
       <c r="J679" s="6"/>
       <c r="K679" s="6"/>
     </row>
-    <row r="680" spans="10:11" ht="12.5">
+    <row r="680" spans="10:11" ht="13.2">
       <c r="J680" s="6"/>
       <c r="K680" s="6"/>
     </row>
-    <row r="681" spans="10:11" ht="12.5">
+    <row r="681" spans="10:11" ht="13.2">
       <c r="J681" s="6"/>
       <c r="K681" s="6"/>
     </row>
-    <row r="682" spans="10:11" ht="12.5">
+    <row r="682" spans="10:11" ht="13.2">
       <c r="J682" s="6"/>
       <c r="K682" s="6"/>
     </row>
-    <row r="683" spans="10:11" ht="12.5">
+    <row r="683" spans="10:11" ht="13.2">
       <c r="J683" s="6"/>
       <c r="K683" s="6"/>
     </row>
-    <row r="684" spans="10:11" ht="12.5">
+    <row r="684" spans="10:11" ht="13.2">
       <c r="J684" s="6"/>
       <c r="K684" s="6"/>
     </row>
-    <row r="685" spans="10:11" ht="12.5">
+    <row r="685" spans="10:11" ht="13.2">
       <c r="J685" s="6"/>
       <c r="K685" s="6"/>
     </row>
-    <row r="686" spans="10:11" ht="12.5">
+    <row r="686" spans="10:11" ht="13.2">
       <c r="J686" s="6"/>
       <c r="K686" s="6"/>
     </row>
-    <row r="687" spans="10:11" ht="12.5">
+    <row r="687" spans="10:11" ht="13.2">
       <c r="J687" s="6"/>
       <c r="K687" s="6"/>
     </row>
-    <row r="688" spans="10:11" ht="12.5">
+    <row r="688" spans="10:11" ht="13.2">
       <c r="J688" s="6"/>
       <c r="K688" s="6"/>
     </row>
-    <row r="689" spans="10:11" ht="12.5">
+    <row r="689" spans="10:11" ht="13.2">
       <c r="J689" s="6"/>
       <c r="K689" s="6"/>
     </row>
-    <row r="690" spans="10:11" ht="12.5">
+    <row r="690" spans="10:11" ht="13.2">
       <c r="J690" s="6"/>
       <c r="K690" s="6"/>
     </row>
-    <row r="691" spans="10:11" ht="12.5">
+    <row r="691" spans="10:11" ht="13.2">
       <c r="J691" s="6"/>
       <c r="K691" s="6"/>
     </row>
-    <row r="692" spans="10:11" ht="12.5">
+    <row r="692" spans="10:11" ht="13.2">
       <c r="J692" s="6"/>
       <c r="K692" s="6"/>
     </row>
-    <row r="693" spans="10:11" ht="12.5">
+    <row r="693" spans="10:11" ht="13.2">
       <c r="J693" s="6"/>
       <c r="K693" s="6"/>
     </row>
-    <row r="694" spans="10:11" ht="12.5">
+    <row r="694" spans="10:11" ht="13.2">
       <c r="J694" s="6"/>
       <c r="K694" s="6"/>
     </row>
-    <row r="695" spans="10:11" ht="12.5">
+    <row r="695" spans="10:11" ht="13.2">
       <c r="J695" s="6"/>
       <c r="K695" s="6"/>
     </row>
-    <row r="696" spans="10:11" ht="12.5">
+    <row r="696" spans="10:11" ht="13.2">
       <c r="J696" s="6"/>
       <c r="K696" s="6"/>
     </row>
-    <row r="697" spans="10:11" ht="12.5">
+    <row r="697" spans="10:11" ht="13.2">
       <c r="J697" s="6"/>
       <c r="K697" s="6"/>
     </row>
-    <row r="698" spans="10:11" ht="12.5">
+    <row r="698" spans="10:11" ht="13.2">
       <c r="J698" s="6"/>
       <c r="K698" s="6"/>
     </row>
-    <row r="699" spans="10:11" ht="12.5">
+    <row r="699" spans="10:11" ht="13.2">
       <c r="J699" s="6"/>
       <c r="K699" s="6"/>
     </row>
-    <row r="700" spans="10:11" ht="12.5">
+    <row r="700" spans="10:11" ht="13.2">
       <c r="J700" s="6"/>
       <c r="K700" s="6"/>
     </row>
-    <row r="701" spans="10:11" ht="12.5">
+    <row r="701" spans="10:11" ht="13.2">
       <c r="J701" s="6"/>
       <c r="K701" s="6"/>
     </row>
-    <row r="702" spans="10:11" ht="12.5">
+    <row r="702" spans="10:11" ht="13.2">
       <c r="J702" s="6"/>
       <c r="K702" s="6"/>
     </row>
-    <row r="703" spans="10:11" ht="12.5">
+    <row r="703" spans="10:11" ht="13.2">
       <c r="J703" s="6"/>
       <c r="K703" s="6"/>
     </row>
-    <row r="704" spans="10:11" ht="12.5">
+    <row r="704" spans="10:11" ht="13.2">
       <c r="J704" s="6"/>
       <c r="K704" s="6"/>
     </row>
-    <row r="705" spans="10:11" ht="12.5">
+    <row r="705" spans="10:11" ht="13.2">
       <c r="J705" s="6"/>
       <c r="K705" s="6"/>
     </row>
-    <row r="706" spans="10:11" ht="12.5">
+    <row r="706" spans="10:11" ht="13.2">
       <c r="J706" s="6"/>
       <c r="K706" s="6"/>
     </row>
-    <row r="707" spans="10:11" ht="12.5">
+    <row r="707" spans="10:11" ht="13.2">
       <c r="J707" s="6"/>
       <c r="K707" s="6"/>
     </row>
-    <row r="708" spans="10:11" ht="12.5">
+    <row r="708" spans="10:11" ht="13.2">
       <c r="J708" s="6"/>
       <c r="K708" s="6"/>
     </row>
-    <row r="709" spans="10:11" ht="12.5">
+    <row r="709" spans="10:11" ht="13.2">
       <c r="J709" s="6"/>
       <c r="K709" s="6"/>
     </row>
-    <row r="710" spans="10:11" ht="12.5">
+    <row r="710" spans="10:11" ht="13.2">
       <c r="J710" s="6"/>
       <c r="K710" s="6"/>
     </row>
-    <row r="711" spans="10:11" ht="12.5">
+    <row r="711" spans="10:11" ht="13.2">
       <c r="J711" s="6"/>
       <c r="K711" s="6"/>
     </row>
-    <row r="712" spans="10:11" ht="12.5">
+    <row r="712" spans="10:11" ht="13.2">
       <c r="J712" s="6"/>
       <c r="K712" s="6"/>
     </row>
-    <row r="713" spans="10:11" ht="12.5">
+    <row r="713" spans="10:11" ht="13.2">
       <c r="J713" s="6"/>
       <c r="K713" s="6"/>
     </row>
-    <row r="714" spans="10:11" ht="12.5">
+    <row r="714" spans="10:11" ht="13.2">
       <c r="J714" s="6"/>
       <c r="K714" s="6"/>
     </row>
-    <row r="715" spans="10:11" ht="12.5">
+    <row r="715" spans="10:11" ht="13.2">
       <c r="J715" s="6"/>
       <c r="K715" s="6"/>
     </row>
-    <row r="716" spans="10:11" ht="12.5">
+    <row r="716" spans="10:11" ht="13.2">
       <c r="J716" s="6"/>
       <c r="K716" s="6"/>
     </row>
-    <row r="717" spans="10:11" ht="12.5">
+    <row r="717" spans="10:11" ht="13.2">
       <c r="J717" s="6"/>
       <c r="K717" s="6"/>
     </row>
-    <row r="718" spans="10:11" ht="12.5">
+    <row r="718" spans="10:11" ht="13.2">
       <c r="J718" s="6"/>
       <c r="K718" s="6"/>
     </row>
-    <row r="719" spans="10:11" ht="12.5">
+    <row r="719" spans="10:11" ht="13.2">
       <c r="J719" s="6"/>
       <c r="K719" s="6"/>
     </row>
-    <row r="720" spans="10:11" ht="12.5">
+    <row r="720" spans="10:11" ht="13.2">
       <c r="J720" s="6"/>
       <c r="K720" s="6"/>
     </row>
-    <row r="721" spans="10:11" ht="12.5">
+    <row r="721" spans="10:11" ht="13.2">
       <c r="J721" s="6"/>
       <c r="K721" s="6"/>
     </row>
-    <row r="722" spans="10:11" ht="12.5">
+    <row r="722" spans="10:11" ht="13.2">
       <c r="J722" s="6"/>
       <c r="K722" s="6"/>
     </row>
-    <row r="723" spans="10:11" ht="12.5">
+    <row r="723" spans="10:11" ht="13.2">
       <c r="J723" s="6"/>
       <c r="K723" s="6"/>
     </row>
-    <row r="724" spans="10:11" ht="12.5">
+    <row r="724" spans="10:11" ht="13.2">
       <c r="J724" s="6"/>
       <c r="K724" s="6"/>
     </row>
-    <row r="725" spans="10:11" ht="12.5">
+    <row r="725" spans="10:11" ht="13.2">
       <c r="J725" s="6"/>
       <c r="K725" s="6"/>
     </row>
-    <row r="726" spans="10:11" ht="12.5">
+    <row r="726" spans="10:11" ht="13.2">
       <c r="J726" s="6"/>
       <c r="K726" s="6"/>
     </row>
-    <row r="727" spans="10:11" ht="12.5">
+    <row r="727" spans="10:11" ht="13.2">
       <c r="J727" s="6"/>
       <c r="K727" s="6"/>
     </row>
-    <row r="728" spans="10:11" ht="12.5">
+    <row r="728" spans="10:11" ht="13.2">
       <c r="J728" s="6"/>
       <c r="K728" s="6"/>
     </row>
-    <row r="729" spans="10:11" ht="12.5">
+    <row r="729" spans="10:11" ht="13.2">
       <c r="J729" s="6"/>
       <c r="K729" s="6"/>
     </row>
-    <row r="730" spans="10:11" ht="12.5">
+    <row r="730" spans="10:11" ht="13.2">
       <c r="J730" s="6"/>
       <c r="K730" s="6"/>
     </row>
-    <row r="731" spans="10:11" ht="12.5">
+    <row r="731" spans="10:11" ht="13.2">
       <c r="J731" s="6"/>
       <c r="K731" s="6"/>
     </row>
-    <row r="732" spans="10:11" ht="12.5">
+    <row r="732" spans="10:11" ht="13.2">
       <c r="J732" s="6"/>
       <c r="K732" s="6"/>
     </row>
-    <row r="733" spans="10:11" ht="12.5">
+    <row r="733" spans="10:11" ht="13.2">
       <c r="J733" s="6"/>
       <c r="K733" s="6"/>
     </row>
-    <row r="734" spans="10:11" ht="12.5">
+    <row r="734" spans="10:11" ht="13.2">
       <c r="J734" s="6"/>
       <c r="K734" s="6"/>
     </row>
-    <row r="735" spans="10:11" ht="12.5">
+    <row r="735" spans="10:11" ht="13.2">
       <c r="J735" s="6"/>
       <c r="K735" s="6"/>
     </row>
-    <row r="736" spans="10:11" ht="12.5">
+    <row r="736" spans="10:11" ht="13.2">
       <c r="J736" s="6"/>
       <c r="K736" s="6"/>
     </row>
-    <row r="737" spans="10:11" ht="12.5">
+    <row r="737" spans="10:11" ht="13.2">
       <c r="J737" s="6"/>
       <c r="K737" s="6"/>
     </row>
-    <row r="738" spans="10:11" ht="12.5">
+    <row r="738" spans="10:11" ht="13.2">
       <c r="J738" s="6"/>
       <c r="K738" s="6"/>
     </row>
-    <row r="739" spans="10:11" ht="12.5">
+    <row r="739" spans="10:11" ht="13.2">
       <c r="J739" s="6"/>
       <c r="K739" s="6"/>
     </row>
-    <row r="740" spans="10:11" ht="12.5">
+    <row r="740" spans="10:11" ht="13.2">
       <c r="J740" s="6"/>
       <c r="K740" s="6"/>
     </row>
-    <row r="741" spans="10:11" ht="12.5">
+    <row r="741" spans="10:11" ht="13.2">
       <c r="J741" s="6"/>
       <c r="K741" s="6"/>
     </row>
-    <row r="742" spans="10:11" ht="12.5">
+    <row r="742" spans="10:11" ht="13.2">
       <c r="J742" s="6"/>
       <c r="K742" s="6"/>
     </row>
-    <row r="743" spans="10:11" ht="12.5">
+    <row r="743" spans="10:11" ht="13.2">
       <c r="J743" s="6"/>
       <c r="K743" s="6"/>
     </row>
-    <row r="744" spans="10:11" ht="12.5">
+    <row r="744" spans="10:11" ht="13.2">
       <c r="J744" s="6"/>
       <c r="K744" s="6"/>
     </row>
-    <row r="745" spans="10:11" ht="12.5">
+    <row r="745" spans="10:11" ht="13.2">
       <c r="J745" s="6"/>
       <c r="K745" s="6"/>
     </row>
-    <row r="746" spans="10:11" ht="12.5">
+    <row r="746" spans="10:11" ht="13.2">
       <c r="J746" s="6"/>
       <c r="K746" s="6"/>
     </row>
-    <row r="747" spans="10:11" ht="12.5">
+    <row r="747" spans="10:11" ht="13.2">
       <c r="J747" s="6"/>
       <c r="K747" s="6"/>
     </row>
-    <row r="748" spans="10:11" ht="12.5">
+    <row r="748" spans="10:11" ht="13.2">
       <c r="J748" s="6"/>
       <c r="K748" s="6"/>
     </row>
-    <row r="749" spans="10:11" ht="12.5">
+    <row r="749" spans="10:11" ht="13.2">
       <c r="J749" s="6"/>
       <c r="K749" s="6"/>
     </row>
-    <row r="750" spans="10:11" ht="12.5">
+    <row r="750" spans="10:11" ht="13.2">
       <c r="J750" s="6"/>
       <c r="K750" s="6"/>
     </row>
-    <row r="751" spans="10:11" ht="12.5">
+    <row r="751" spans="10:11" ht="13.2">
       <c r="J751" s="6"/>
       <c r="K751" s="6"/>
     </row>
-    <row r="752" spans="10:11" ht="12.5">
+    <row r="752" spans="10:11" ht="13.2">
       <c r="J752" s="6"/>
       <c r="K752" s="6"/>
     </row>
-    <row r="753" spans="10:11" ht="12.5">
+    <row r="753" spans="10:11" ht="13.2">
       <c r="J753" s="6"/>
       <c r="K753" s="6"/>
     </row>
-    <row r="754" spans="10:11" ht="12.5">
+    <row r="754" spans="10:11" ht="13.2">
       <c r="J754" s="6"/>
       <c r="K754" s="6"/>
     </row>
-    <row r="755" spans="10:11" ht="12.5">
+    <row r="755" spans="10:11" ht="13.2">
       <c r="J755" s="6"/>
       <c r="K755" s="6"/>
     </row>
-    <row r="756" spans="10:11" ht="12.5">
+    <row r="756" spans="10:11" ht="13.2">
       <c r="J756" s="6"/>
       <c r="K756" s="6"/>
     </row>
-    <row r="757" spans="10:11" ht="12.5">
+    <row r="757" spans="10:11" ht="13.2">
       <c r="J757" s="6"/>
       <c r="K757" s="6"/>
     </row>
-    <row r="758" spans="10:11" ht="12.5">
+    <row r="758" spans="10:11" ht="13.2">
       <c r="J758" s="6"/>
       <c r="K758" s="6"/>
     </row>
-    <row r="759" spans="10:11" ht="12.5">
+    <row r="759" spans="10:11" ht="13.2">
       <c r="J759" s="6"/>
       <c r="K759" s="6"/>
     </row>
-    <row r="760" spans="10:11" ht="12.5">
+    <row r="760" spans="10:11" ht="13.2">
       <c r="J760" s="6"/>
       <c r="K760" s="6"/>
     </row>
-    <row r="761" spans="10:11" ht="12.5">
+    <row r="761" spans="10:11" ht="13.2">
       <c r="J761" s="6"/>
       <c r="K761" s="6"/>
     </row>
-    <row r="762" spans="10:11" ht="12.5">
+    <row r="762" spans="10:11" ht="13.2">
       <c r="J762" s="6"/>
       <c r="K762" s="6"/>
     </row>
-    <row r="763" spans="10:11" ht="12.5">
+    <row r="763" spans="10:11" ht="13.2">
       <c r="J763" s="6"/>
       <c r="K763" s="6"/>
     </row>
-    <row r="764" spans="10:11" ht="12.5">
+    <row r="764" spans="10:11" ht="13.2">
       <c r="J764" s="6"/>
       <c r="K764" s="6"/>
     </row>
-    <row r="765" spans="10:11" ht="12.5">
+    <row r="765" spans="10:11" ht="13.2">
       <c r="J765" s="6"/>
       <c r="K765" s="6"/>
     </row>
-    <row r="766" spans="10:11" ht="12.5">
+    <row r="766" spans="10:11" ht="13.2">
       <c r="J766" s="6"/>
       <c r="K766" s="6"/>
     </row>
-    <row r="767" spans="10:11" ht="12.5">
+    <row r="767" spans="10:11" ht="13.2">
       <c r="J767" s="6"/>
       <c r="K767" s="6"/>
     </row>
-    <row r="768" spans="10:11" ht="12.5">
+    <row r="768" spans="10:11" ht="13.2">
       <c r="J768" s="6"/>
       <c r="K768" s="6"/>
     </row>
-    <row r="769" spans="10:11" ht="12.5">
+    <row r="769" spans="10:11" ht="13.2">
       <c r="J769" s="6"/>
       <c r="K769" s="6"/>
     </row>
-    <row r="770" spans="10:11" ht="12.5">
+    <row r="770" spans="10:11" ht="13.2">
       <c r="J770" s="6"/>
       <c r="K770" s="6"/>
     </row>
-    <row r="771" spans="10:11" ht="12.5">
+    <row r="771" spans="10:11" ht="13.2">
       <c r="J771" s="6"/>
       <c r="K771" s="6"/>
     </row>
-    <row r="772" spans="10:11" ht="12.5">
+    <row r="772" spans="10:11" ht="13.2">
       <c r="J772" s="6"/>
       <c r="K772" s="6"/>
     </row>
-    <row r="773" spans="10:11" ht="12.5">
+    <row r="773" spans="10:11" ht="13.2">
       <c r="J773" s="6"/>
       <c r="K773" s="6"/>
     </row>
-    <row r="774" spans="10:11" ht="12.5">
+    <row r="774" spans="10:11" ht="13.2">
       <c r="J774" s="6"/>
       <c r="K774" s="6"/>
     </row>
-    <row r="775" spans="10:11" ht="12.5">
+    <row r="775" spans="10:11" ht="13.2">
       <c r="J775" s="6"/>
       <c r="K775" s="6"/>
     </row>
-    <row r="776" spans="10:11" ht="12.5">
+    <row r="776" spans="10:11" ht="13.2">
       <c r="J776" s="6"/>
       <c r="K776" s="6"/>
     </row>
-    <row r="777" spans="10:11" ht="12.5">
+    <row r="777" spans="10:11" ht="13.2">
       <c r="J777" s="6"/>
       <c r="K777" s="6"/>
     </row>
-    <row r="778" spans="10:11" ht="12.5">
+    <row r="778" spans="10:11" ht="13.2">
       <c r="J778" s="6"/>
       <c r="K778" s="6"/>
     </row>
-    <row r="779" spans="10:11" ht="12.5">
+    <row r="779" spans="10:11" ht="13.2">
       <c r="J779" s="6"/>
       <c r="K779" s="6"/>
     </row>
-    <row r="780" spans="10:11" ht="12.5">
+    <row r="780" spans="10:11" ht="13.2">
       <c r="J780" s="6"/>
       <c r="K780" s="6"/>
     </row>
-    <row r="781" spans="10:11" ht="12.5">
+    <row r="781" spans="10:11" ht="13.2">
       <c r="J781" s="6"/>
       <c r="K781" s="6"/>
     </row>
-    <row r="782" spans="10:11" ht="12.5">
+    <row r="782" spans="10:11" ht="13.2">
       <c r="J782" s="6"/>
       <c r="K782" s="6"/>
     </row>
-    <row r="783" spans="10:11" ht="12.5">
+    <row r="783" spans="10:11" ht="13.2">
       <c r="J783" s="6"/>
       <c r="K783" s="6"/>
     </row>
-    <row r="784" spans="10:11" ht="12.5">
+    <row r="784" spans="10:11" ht="13.2">
       <c r="J784" s="6"/>
       <c r="K784" s="6"/>
     </row>
-    <row r="785" spans="10:11" ht="12.5">
+    <row r="785" spans="10:11" ht="13.2">
       <c r="J785" s="6"/>
       <c r="K785" s="6"/>
     </row>
-    <row r="786" spans="10:11" ht="12.5">
+    <row r="786" spans="10:11" ht="13.2">
       <c r="J786" s="6"/>
       <c r="K786" s="6"/>
     </row>
-    <row r="787" spans="10:11" ht="12.5">
+    <row r="787" spans="10:11" ht="13.2">
       <c r="J787" s="6"/>
       <c r="K787" s="6"/>
     </row>
-    <row r="788" spans="10:11" ht="12.5">
+    <row r="788" spans="10:11" ht="13.2">
       <c r="J788" s="6"/>
       <c r="K788" s="6"/>
     </row>
-    <row r="789" spans="10:11" ht="12.5">
+    <row r="789" spans="10:11" ht="13.2">
       <c r="J789" s="6"/>
       <c r="K789" s="6"/>
     </row>
-    <row r="790" spans="10:11" ht="12.5">
+    <row r="790" spans="10:11" ht="13.2">
       <c r="J790" s="6"/>
       <c r="K790" s="6"/>
     </row>
-    <row r="791" spans="10:11" ht="12.5">
+    <row r="791" spans="10:11" ht="13.2">
       <c r="J791" s="6"/>
       <c r="K791" s="6"/>
     </row>
-    <row r="792" spans="10:11" ht="12.5">
+    <row r="792" spans="10:11" ht="13.2">
       <c r="J792" s="6"/>
       <c r="K792" s="6"/>
     </row>
-    <row r="793" spans="10:11" ht="12.5">
+    <row r="793" spans="10:11" ht="13.2">
       <c r="J793" s="6"/>
       <c r="K793" s="6"/>
     </row>
-    <row r="794" spans="10:11" ht="12.5">
+    <row r="794" spans="10:11" ht="13.2">
       <c r="J794" s="6"/>
       <c r="K794" s="6"/>
     </row>
-    <row r="795" spans="10:11" ht="12.5">
+    <row r="795" spans="10:11" ht="13.2">
       <c r="J795" s="6"/>
       <c r="K795" s="6"/>
     </row>
-    <row r="796" spans="10:11" ht="12.5">
+    <row r="796" spans="10:11" ht="13.2">
       <c r="J796" s="6"/>
       <c r="K796" s="6"/>
     </row>
-    <row r="797" spans="10:11" ht="12.5">
+    <row r="797" spans="10:11" ht="13.2">
       <c r="J797" s="6"/>
       <c r="K797" s="6"/>
     </row>
-    <row r="798" spans="10:11" ht="12.5">
+    <row r="798" spans="10:11" ht="13.2">
       <c r="J798" s="6"/>
       <c r="K798" s="6"/>
     </row>
-    <row r="799" spans="10:11" ht="12.5">
+    <row r="799" spans="10:11" ht="13.2">
       <c r="J799" s="6"/>
       <c r="K799" s="6"/>
     </row>
-    <row r="800" spans="10:11" ht="12.5">
+    <row r="800" spans="10:11" ht="13.2">
       <c r="J800" s="6"/>
       <c r="K800" s="6"/>
     </row>
-    <row r="801" spans="10:11" ht="12.5">
+    <row r="801" spans="10:11" ht="13.2">
       <c r="J801" s="6"/>
       <c r="K801" s="6"/>
     </row>
-    <row r="802" spans="10:11" ht="12.5">
+    <row r="802" spans="10:11" ht="13.2">
       <c r="J802" s="6"/>
       <c r="K802" s="6"/>
     </row>
-    <row r="803" spans="10:11" ht="12.5">
+    <row r="803" spans="10:11" ht="13.2">
       <c r="J803" s="6"/>
       <c r="K803" s="6"/>
     </row>
-    <row r="804" spans="10:11" ht="12.5">
+    <row r="804" spans="10:11" ht="13.2">
       <c r="J804" s="6"/>
       <c r="K804" s="6"/>
     </row>
-    <row r="805" spans="10:11" ht="12.5">
+    <row r="805" spans="10:11" ht="13.2">
       <c r="J805" s="6"/>
       <c r="K805" s="6"/>
     </row>
-    <row r="806" spans="10:11" ht="12.5">
+    <row r="806" spans="10:11" ht="13.2">
       <c r="J806" s="6"/>
       <c r="K806" s="6"/>
     </row>
-    <row r="807" spans="10:11" ht="12.5">
+    <row r="807" spans="10:11" ht="13.2">
       <c r="J807" s="6"/>
       <c r="K807" s="6"/>
     </row>
-    <row r="808" spans="10:11" ht="12.5">
+    <row r="808" spans="10:11" ht="13.2">
       <c r="J808" s="6"/>
       <c r="K808" s="6"/>
     </row>
-    <row r="809" spans="10:11" ht="12.5">
+    <row r="809" spans="10:11" ht="13.2">
       <c r="J809" s="6"/>
       <c r="K809" s="6"/>
     </row>
-    <row r="810" spans="10:11" ht="12.5">
+    <row r="810" spans="10:11" ht="13.2">
       <c r="J810" s="6"/>
       <c r="K810" s="6"/>
     </row>
-    <row r="811" spans="10:11" ht="12.5">
+    <row r="811" spans="10:11" ht="13.2">
       <c r="J811" s="6"/>
       <c r="K811" s="6"/>
     </row>
-    <row r="812" spans="10:11" ht="12.5">
+    <row r="812" spans="10:11" ht="13.2">
       <c r="J812" s="6"/>
       <c r="K812" s="6"/>
     </row>
-    <row r="813" spans="10:11" ht="12.5">
+    <row r="813" spans="10:11" ht="13.2">
       <c r="J813" s="6"/>
       <c r="K813" s="6"/>
     </row>
-    <row r="814" spans="10:11" ht="12.5">
+    <row r="814" spans="10:11" ht="13.2">
       <c r="J814" s="6"/>
       <c r="K814" s="6"/>
     </row>
-    <row r="815" spans="10:11" ht="12.5">
+    <row r="815" spans="10:11" ht="13.2">
       <c r="J815" s="6"/>
       <c r="K815" s="6"/>
     </row>
-    <row r="816" spans="10:11" ht="12.5">
+    <row r="816" spans="10:11" ht="13.2">
       <c r="J816" s="6"/>
       <c r="K816" s="6"/>
     </row>
-    <row r="817" spans="10:11" ht="12.5">
+    <row r="817" spans="10:11" ht="13.2">
       <c r="J817" s="6"/>
       <c r="K817" s="6"/>
     </row>
-    <row r="818" spans="10:11" ht="12.5">
+    <row r="818" spans="10:11" ht="13.2">
       <c r="J818" s="6"/>
       <c r="K818" s="6"/>
     </row>
-    <row r="819" spans="10:11" ht="12.5">
+    <row r="819" spans="10:11" ht="13.2">
       <c r="J819" s="6"/>
       <c r="K819" s="6"/>
     </row>
-    <row r="820" spans="10:11" ht="12.5">
+    <row r="820" spans="10:11" ht="13.2">
       <c r="J820" s="6"/>
       <c r="K820" s="6"/>
     </row>
-    <row r="821" spans="10:11" ht="12.5">
+    <row r="821" spans="10:11" ht="13.2">
       <c r="J821" s="6"/>
       <c r="K821" s="6"/>
     </row>
-    <row r="822" spans="10:11" ht="12.5">
+    <row r="822" spans="10:11" ht="13.2">
       <c r="J822" s="6"/>
       <c r="K822" s="6"/>
     </row>
-    <row r="823" spans="10:11" ht="12.5">
+    <row r="823" spans="10:11" ht="13.2">
       <c r="J823" s="6"/>
       <c r="K823" s="6"/>
     </row>
-    <row r="824" spans="10:11" ht="12.5">
+    <row r="824" spans="10:11" ht="13.2">
       <c r="J824" s="6"/>
       <c r="K824" s="6"/>
     </row>
-    <row r="825" spans="10:11" ht="12.5">
+    <row r="825" spans="10:11" ht="13.2">
       <c r="J825" s="6"/>
       <c r="K825" s="6"/>
     </row>
-    <row r="826" spans="10:11" ht="12.5">
+    <row r="826" spans="10:11" ht="13.2">
       <c r="J826" s="6"/>
       <c r="K826" s="6"/>
     </row>
-    <row r="827" spans="10:11" ht="12.5">
+    <row r="827" spans="10:11" ht="13.2">
       <c r="J827" s="6"/>
       <c r="K827" s="6"/>
     </row>
-    <row r="828" spans="10:11" ht="12.5">
+    <row r="828" spans="10:11" ht="13.2">
       <c r="J828" s="6"/>
       <c r="K828" s="6"/>
     </row>
-    <row r="829" spans="10:11" ht="12.5">
+    <row r="829" spans="10:11" ht="13.2">
       <c r="J829" s="6"/>
       <c r="K829" s="6"/>
     </row>
-    <row r="830" spans="10:11" ht="12.5">
+    <row r="830" spans="10:11" ht="13.2">
       <c r="J830" s="6"/>
       <c r="K830" s="6"/>
     </row>
-    <row r="831" spans="10:11" ht="12.5">
+    <row r="831" spans="10:11" ht="13.2">
       <c r="J831" s="6"/>
       <c r="K831" s="6"/>
     </row>
-    <row r="832" spans="10:11" ht="12.5">
+    <row r="832" spans="10:11" ht="13.2">
       <c r="J832" s="6"/>
       <c r="K832" s="6"/>
     </row>
-    <row r="833" spans="10:11" ht="12.5">
+    <row r="833" spans="10:11" ht="13.2">
       <c r="J833" s="6"/>
       <c r="K833" s="6"/>
     </row>
-    <row r="834" spans="10:11" ht="12.5">
+    <row r="834" spans="10:11" ht="13.2">
       <c r="J834" s="6"/>
       <c r="K834" s="6"/>
     </row>
-    <row r="835" spans="10:11" ht="12.5">
+    <row r="835" spans="10:11" ht="13.2">
       <c r="J835" s="6"/>
       <c r="K835" s="6"/>
     </row>
-    <row r="836" spans="10:11" ht="12.5">
+    <row r="836" spans="10:11" ht="13.2">
       <c r="J836" s="6"/>
       <c r="K836" s="6"/>
     </row>
-    <row r="837" spans="10:11" ht="12.5">
+    <row r="837" spans="10:11" ht="13.2">
       <c r="J837" s="6"/>
       <c r="K837" s="6"/>
     </row>
-    <row r="838" spans="10:11" ht="12.5">
+    <row r="838" spans="10:11" ht="13.2">
       <c r="J838" s="6"/>
       <c r="K838" s="6"/>
     </row>
-    <row r="839" spans="10:11" ht="12.5">
+    <row r="839" spans="10:11" ht="13.2">
       <c r="J839" s="6"/>
       <c r="K839" s="6"/>
     </row>
-    <row r="840" spans="10:11" ht="12.5">
+    <row r="840" spans="10:11" ht="13.2">
       <c r="J840" s="6"/>
       <c r="K840" s="6"/>
     </row>
-    <row r="841" spans="10:11" ht="12.5">
+    <row r="841" spans="10:11" ht="13.2">
       <c r="J841" s="6"/>
       <c r="K841" s="6"/>
     </row>
-    <row r="842" spans="10:11" ht="12.5">
+    <row r="842" spans="10:11" ht="13.2">
       <c r="J842" s="6"/>
       <c r="K842" s="6"/>
     </row>
-    <row r="843" spans="10:11" ht="12.5">
+    <row r="843" spans="10:11" ht="13.2">
       <c r="J843" s="6"/>
       <c r="K843" s="6"/>
     </row>
-    <row r="844" spans="10:11" ht="12.5">
+    <row r="844" spans="10:11" ht="13.2">
       <c r="J844" s="6"/>
       <c r="K844" s="6"/>
     </row>
-    <row r="845" spans="10:11" ht="12.5">
+    <row r="845" spans="10:11" ht="13.2">
       <c r="J845" s="6"/>
       <c r="K845" s="6"/>
     </row>
-    <row r="846" spans="10:11" ht="12.5">
+    <row r="846" spans="10:11" ht="13.2">
       <c r="J846" s="6"/>
       <c r="K846" s="6"/>
     </row>
-    <row r="847" spans="10:11" ht="12.5">
+    <row r="847" spans="10:11" ht="13.2">
       <c r="J847" s="6"/>
       <c r="K847" s="6"/>
     </row>
-    <row r="848" spans="10:11" ht="12.5">
+    <row r="848" spans="10:11" ht="13.2">
       <c r="J848" s="6"/>
       <c r="K848" s="6"/>
     </row>
-    <row r="849" spans="10:11" ht="12.5">
+    <row r="849" spans="10:11" ht="13.2">
       <c r="J849" s="6"/>
       <c r="K849" s="6"/>
     </row>
-    <row r="850" spans="10:11" ht="12.5">
+    <row r="850" spans="10:11" ht="13.2">
       <c r="J850" s="6"/>
       <c r="K850" s="6"/>
     </row>
-    <row r="851" spans="10:11" ht="12.5">
+    <row r="851" spans="10:11" ht="13.2">
       <c r="J851" s="6"/>
       <c r="K851" s="6"/>
     </row>
-    <row r="852" spans="10:11" ht="12.5">
+    <row r="852" spans="10:11" ht="13.2">
       <c r="J852" s="6"/>
       <c r="K852" s="6"/>
     </row>
-    <row r="853" spans="10:11" ht="12.5">
+    <row r="853" spans="10:11" ht="13.2">
       <c r="J853" s="6"/>
       <c r="K853" s="6"/>
     </row>
-    <row r="854" spans="10:11" ht="12.5">
+    <row r="854" spans="10:11" ht="13.2">
       <c r="J854" s="6"/>
       <c r="K854" s="6"/>
     </row>
-    <row r="855" spans="10:11" ht="12.5">
+    <row r="855" spans="10:11" ht="13.2">
       <c r="J855" s="6"/>
       <c r="K855" s="6"/>
     </row>
-    <row r="856" spans="10:11" ht="12.5">
+    <row r="856" spans="10:11" ht="13.2">
       <c r="J856" s="6"/>
       <c r="K856" s="6"/>
     </row>
-    <row r="857" spans="10:11" ht="12.5">
+    <row r="857" spans="10:11" ht="13.2">
       <c r="J857" s="6"/>
       <c r="K857" s="6"/>
     </row>
-    <row r="858" spans="10:11" ht="12.5">
+    <row r="858" spans="10:11" ht="13.2">
       <c r="J858" s="6"/>
       <c r="K858" s="6"/>
     </row>
-    <row r="859" spans="10:11" ht="12.5">
+    <row r="859" spans="10:11" ht="13.2">
       <c r="J859" s="6"/>
       <c r="K859" s="6"/>
     </row>
-    <row r="860" spans="10:11" ht="12.5">
+    <row r="860" spans="10:11" ht="13.2">
       <c r="J860" s="6"/>
       <c r="K860" s="6"/>
     </row>
-    <row r="861" spans="10:11" ht="12.5">
+    <row r="861" spans="10:11" ht="13.2">
       <c r="J861" s="6"/>
       <c r="K861" s="6"/>
     </row>
-    <row r="862" spans="10:11" ht="12.5">
+    <row r="862" spans="10:11" ht="13.2">
       <c r="J862" s="6"/>
       <c r="K862" s="6"/>
     </row>
-    <row r="863" spans="10:11" ht="12.5">
+    <row r="863" spans="10:11" ht="13.2">
       <c r="J863" s="6"/>
       <c r="K863" s="6"/>
     </row>
-    <row r="864" spans="10:11" ht="12.5">
+    <row r="864" spans="10:11" ht="13.2">
       <c r="J864" s="6"/>
       <c r="K864" s="6"/>
     </row>
-    <row r="865" spans="10:11" ht="12.5">
+    <row r="865" spans="10:11" ht="13.2">
       <c r="J865" s="6"/>
       <c r="K865" s="6"/>
     </row>
-    <row r="866" spans="10:11" ht="12.5">
+    <row r="866" spans="10:11" ht="13.2">
       <c r="J866" s="6"/>
       <c r="K866" s="6"/>
     </row>
-    <row r="867" spans="10:11" ht="12.5">
+    <row r="867" spans="10:11" ht="13.2">
       <c r="J867" s="6"/>
       <c r="K867" s="6"/>
     </row>
-    <row r="868" spans="10:11" ht="12.5">
+    <row r="868" spans="10:11" ht="13.2">
       <c r="J868" s="6"/>
       <c r="K868" s="6"/>
     </row>
-    <row r="869" spans="10:11" ht="12.5">
+    <row r="869" spans="10:11" ht="13.2">
       <c r="J869" s="6"/>
       <c r="K869" s="6"/>
     </row>
-    <row r="870" spans="10:11" ht="12.5">
+    <row r="870" spans="10:11" ht="13.2">
       <c r="J870" s="6"/>
       <c r="K870" s="6"/>
     </row>
-    <row r="871" spans="10:11" ht="12.5">
+    <row r="871" spans="10:11" ht="13.2">
       <c r="J871" s="6"/>
       <c r="K871" s="6"/>
     </row>
-    <row r="872" spans="10:11" ht="12.5">
+    <row r="872" spans="10:11" ht="13.2">
       <c r="J872" s="6"/>
       <c r="K872" s="6"/>
     </row>
-    <row r="873" spans="10:11" ht="12.5">
+    <row r="873" spans="10:11" ht="13.2">
       <c r="J873" s="6"/>
       <c r="K873" s="6"/>
     </row>
-    <row r="874" spans="10:11" ht="12.5">
+    <row r="874" spans="10:11" ht="13.2">
       <c r="J874" s="6"/>
       <c r="K874" s="6"/>
     </row>
-    <row r="875" spans="10:11" ht="12.5">
+    <row r="875" spans="10:11" ht="13.2">
       <c r="J875" s="6"/>
       <c r="K875" s="6"/>
     </row>
-    <row r="876" spans="10:11" ht="12.5">
+    <row r="876" spans="10:11" ht="13.2">
       <c r="J876" s="6"/>
       <c r="K876" s="6"/>
     </row>
-    <row r="877" spans="10:11" ht="12.5">
+    <row r="877" spans="10:11" ht="13.2">
       <c r="J877" s="6"/>
       <c r="K877" s="6"/>
     </row>
-    <row r="878" spans="10:11" ht="12.5">
+    <row r="878" spans="10:11" ht="13.2">
       <c r="J878" s="6"/>
       <c r="K878" s="6"/>
     </row>
-    <row r="879" spans="10:11" ht="12.5">
+    <row r="879" spans="10:11" ht="13.2">
       <c r="J879" s="6"/>
       <c r="K879" s="6"/>
     </row>
-    <row r="880" spans="10:11" ht="12.5">
+    <row r="880" spans="10:11" ht="13.2">
       <c r="J880" s="6"/>
       <c r="K880" s="6"/>
     </row>
-    <row r="881" spans="10:11" ht="12.5">
+    <row r="881" spans="10:11" ht="13.2">
       <c r="J881" s="6"/>
       <c r="K881" s="6"/>
     </row>
-    <row r="882" spans="10:11" ht="12.5">
+    <row r="882" spans="10:11" ht="13.2">
       <c r="J882" s="6"/>
       <c r="K882" s="6"/>
     </row>
-    <row r="883" spans="10:11" ht="12.5">
+    <row r="883" spans="10:11" ht="13.2">
       <c r="J883" s="6"/>
       <c r="K883" s="6"/>
     </row>
-    <row r="884" spans="10:11" ht="12.5">
+    <row r="884" spans="10:11" ht="13.2">
       <c r="J884" s="6"/>
       <c r="K884" s="6"/>
     </row>
-    <row r="885" spans="10:11" ht="12.5">
+    <row r="885" spans="10:11" ht="13.2">
       <c r="J885" s="6"/>
       <c r="K885" s="6"/>
     </row>
-    <row r="886" spans="10:11" ht="12.5">
+    <row r="886" spans="10:11" ht="13.2">
       <c r="J886" s="6"/>
       <c r="K886" s="6"/>
     </row>
-    <row r="887" spans="10:11" ht="12.5">
+    <row r="887" spans="10:11" ht="13.2">
       <c r="J887" s="6"/>
       <c r="K887" s="6"/>
     </row>
-    <row r="888" spans="10:11" ht="12.5">
+    <row r="888" spans="10:11" ht="13.2">
       <c r="J888" s="6"/>
       <c r="K888" s="6"/>
     </row>
-    <row r="889" spans="10:11" ht="12.5">
+    <row r="889" spans="10:11" ht="13.2">
       <c r="J889" s="6"/>
       <c r="K889" s="6"/>
     </row>
-    <row r="890" spans="10:11" ht="12.5">
+    <row r="890" spans="10:11" ht="13.2">
       <c r="J890" s="6"/>
       <c r="K890" s="6"/>
     </row>
-    <row r="891" spans="10:11" ht="12.5">
+    <row r="891" spans="10:11" ht="13.2">
       <c r="J891" s="6"/>
       <c r="K891" s="6"/>
     </row>
-    <row r="892" spans="10:11" ht="12.5">
+    <row r="892" spans="10:11" ht="13.2">
       <c r="J892" s="6"/>
       <c r="K892" s="6"/>
     </row>
-    <row r="893" spans="10:11" ht="12.5">
+    <row r="893" spans="10:11" ht="13.2">
       <c r="J893" s="6"/>
       <c r="K893" s="6"/>
     </row>
-    <row r="894" spans="10:11" ht="12.5">
+    <row r="894" spans="10:11" ht="13.2">
       <c r="J894" s="6"/>
       <c r="K894" s="6"/>
     </row>
-    <row r="895" spans="10:11" ht="12.5">
+    <row r="895" spans="10:11" ht="13.2">
       <c r="J895" s="6"/>
       <c r="K895" s="6"/>
     </row>
-    <row r="896" spans="10:11" ht="12.5">
+    <row r="896" spans="10:11" ht="13.2">
       <c r="J896" s="6"/>
       <c r="K896" s="6"/>
     </row>
-    <row r="897" spans="10:11" ht="12.5">
+    <row r="897" spans="10:11" ht="13.2">
       <c r="J897" s="6"/>
       <c r="K897" s="6"/>
     </row>
-    <row r="898" spans="10:11" ht="12.5">
+    <row r="898" spans="10:11" ht="13.2">
       <c r="J898" s="6"/>
       <c r="K898" s="6"/>
     </row>
-    <row r="899" spans="10:11" ht="12.5">
+    <row r="899" spans="10:11" ht="13.2">
       <c r="J899" s="6"/>
       <c r="K899" s="6"/>
     </row>
-    <row r="900" spans="10:11" ht="12.5">
+    <row r="900" spans="10:11" ht="13.2">
       <c r="J900" s="6"/>
       <c r="K900" s="6"/>
     </row>
-    <row r="901" spans="10:11" ht="12.5">
+    <row r="901" spans="10:11" ht="13.2">
       <c r="J901" s="6"/>
       <c r="K901" s="6"/>
     </row>
-    <row r="902" spans="10:11" ht="12.5">
+    <row r="902" spans="10:11" ht="13.2">
       <c r="J902" s="6"/>
       <c r="K902" s="6"/>
     </row>
-    <row r="903" spans="10:11" ht="12.5">
+    <row r="903" spans="10:11" ht="13.2">
       <c r="J903" s="6"/>
       <c r="K903" s="6"/>
     </row>
-    <row r="904" spans="10:11" ht="12.5">
+    <row r="904" spans="10:11" ht="13.2">
       <c r="J904" s="6"/>
       <c r="K904" s="6"/>
     </row>
-    <row r="905" spans="10:11" ht="12.5">
+    <row r="905" spans="10:11" ht="13.2">
       <c r="J905" s="6"/>
       <c r="K905" s="6"/>
     </row>
-    <row r="906" spans="10:11" ht="12.5">
+    <row r="906" spans="10:11" ht="13.2">
       <c r="J906" s="6"/>
       <c r="K906" s="6"/>
     </row>
-    <row r="907" spans="10:11" ht="12.5">
+    <row r="907" spans="10:11" ht="13.2">
       <c r="J907" s="6"/>
       <c r="K907" s="6"/>
     </row>
-    <row r="908" spans="10:11" ht="12.5">
+    <row r="908" spans="10:11" ht="13.2">
       <c r="J908" s="6"/>
       <c r="K908" s="6"/>
     </row>
-    <row r="909" spans="10:11" ht="12.5">
+    <row r="909" spans="10:11" ht="13.2">
       <c r="J909" s="6"/>
       <c r="K909" s="6"/>
     </row>
-    <row r="910" spans="10:11" ht="12.5">
+    <row r="910" spans="10:11" ht="13.2">
       <c r="J910" s="6"/>
       <c r="K910" s="6"/>
     </row>
-    <row r="911" spans="10:11" ht="12.5">
+    <row r="911" spans="10:11" ht="13.2">
       <c r="J911" s="6"/>
       <c r="K911" s="6"/>
     </row>
-    <row r="912" spans="10:11" ht="12.5">
+    <row r="912" spans="10:11" ht="13.2">
       <c r="J912" s="6"/>
       <c r="K912" s="6"/>
     </row>
-    <row r="913" spans="10:11" ht="12.5">
+    <row r="913" spans="10:11" ht="13.2">
       <c r="J913" s="6"/>
       <c r="K913" s="6"/>
     </row>
-    <row r="914" spans="10:11" ht="12.5">
+    <row r="914" spans="10:11" ht="13.2">
       <c r="J914" s="6"/>
       <c r="K914" s="6"/>
     </row>
-    <row r="915" spans="10:11" ht="12.5">
+    <row r="915" spans="10:11" ht="13.2">
       <c r="J915" s="6"/>
       <c r="K915" s="6"/>
     </row>
-    <row r="916" spans="10:11" ht="12.5">
+    <row r="916" spans="10:11" ht="13.2">
       <c r="J916" s="6"/>
       <c r="K916" s="6"/>
     </row>
-    <row r="917" spans="10:11" ht="12.5">
+    <row r="917" spans="10:11" ht="13.2">
       <c r="J917" s="6"/>
       <c r="K917" s="6"/>
     </row>
-    <row r="918" spans="10:11" ht="12.5">
+    <row r="918" spans="10:11" ht="13.2">
       <c r="J918" s="6"/>
       <c r="K918" s="6"/>
     </row>
-    <row r="919" spans="10:11" ht="12.5">
+    <row r="919" spans="10:11" ht="13.2">
       <c r="J919" s="6"/>
       <c r="K919" s="6"/>
     </row>
-    <row r="920" spans="10:11" ht="12.5">
+    <row r="920" spans="10:11" ht="13.2">
       <c r="J920" s="6"/>
       <c r="K920" s="6"/>
     </row>
-    <row r="921" spans="10:11" ht="12.5">
+    <row r="921" spans="10:11" ht="13.2">
       <c r="J921" s="6"/>
       <c r="K921" s="6"/>
     </row>
-    <row r="922" spans="10:11" ht="12.5">
+    <row r="922" spans="10:11" ht="13.2">
       <c r="J922" s="6"/>
       <c r="K922" s="6"/>
     </row>
-    <row r="923" spans="10:11" ht="12.5">
+    <row r="923" spans="10:11" ht="13.2">
       <c r="J923" s="6"/>
       <c r="K923" s="6"/>
     </row>
-    <row r="924" spans="10:11" ht="12.5">
+    <row r="924" spans="10:11" ht="13.2">
       <c r="J924" s="6"/>
       <c r="K924" s="6"/>
     </row>
-    <row r="925" spans="10:11" ht="12.5">
+    <row r="925" spans="10:11" ht="13.2">
       <c r="J925" s="6"/>
       <c r="K925" s="6"/>
     </row>
-    <row r="926" spans="10:11" ht="12.5">
+    <row r="926" spans="10:11" ht="13.2">
       <c r="J926" s="6"/>
       <c r="K926" s="6"/>
     </row>
-    <row r="927" spans="10:11" ht="12.5">
+    <row r="927" spans="10:11" ht="13.2">
       <c r="J927" s="6"/>
       <c r="K927" s="6"/>
     </row>
-    <row r="928" spans="10:11" ht="12.5">
+    <row r="928" spans="10:11" ht="13.2">
       <c r="J928" s="6"/>
       <c r="K928" s="6"/>
     </row>
-    <row r="929" spans="10:11" ht="12.5">
+    <row r="929" spans="10:11" ht="13.2">
       <c r="J929" s="6"/>
       <c r="K929" s="6"/>
     </row>
-    <row r="930" spans="10:11" ht="12.5">
+    <row r="930" spans="10:11" ht="13.2">
       <c r="J930" s="6"/>
       <c r="K930" s="6"/>
     </row>
-    <row r="931" spans="10:11" ht="12.5">
+    <row r="931" spans="10:11" ht="13.2">
       <c r="J931" s="6"/>
       <c r="K931" s="6"/>
     </row>
-    <row r="932" spans="10:11" ht="12.5">
+    <row r="932" spans="10:11" ht="13.2">
       <c r="J932" s="6"/>
       <c r="K932" s="6"/>
     </row>
-    <row r="933" spans="10:11" ht="12.5">
+    <row r="933" spans="10:11" ht="13.2">
       <c r="J933" s="6"/>
       <c r="K933" s="6"/>
     </row>
-    <row r="934" spans="10:11" ht="12.5">
+    <row r="934" spans="10:11" ht="13.2">
       <c r="J934" s="6"/>
       <c r="K934" s="6"/>
     </row>
-    <row r="935" spans="10:11" ht="12.5">
+    <row r="935" spans="10:11" ht="13.2">
       <c r="J935" s="6"/>
       <c r="K935" s="6"/>
     </row>
-    <row r="936" spans="10:11" ht="12.5">
+    <row r="936" spans="10:11" ht="13.2">
       <c r="J936" s="6"/>
       <c r="K936" s="6"/>
     </row>
-    <row r="937" spans="10:11" ht="12.5">
+    <row r="937" spans="10:11" ht="13.2">
       <c r="J937" s="6"/>
       <c r="K937" s="6"/>
     </row>
-    <row r="938" spans="10:11" ht="12.5">
+    <row r="938" spans="10:11" ht="13.2">
       <c r="J938" s="6"/>
       <c r="K938" s="6"/>
     </row>
-    <row r="939" spans="10:11" ht="12.5">
+    <row r="939" spans="10:11" ht="13.2">
       <c r="J939" s="6"/>
       <c r="K939" s="6"/>
     </row>
-    <row r="940" spans="10:11" ht="12.5">
+    <row r="940" spans="10:11" ht="13.2">
       <c r="J940" s="6"/>
       <c r="K940" s="6"/>
     </row>
-    <row r="941" spans="10:11" ht="12.5">
+    <row r="941" spans="10:11" ht="13.2">
       <c r="J941" s="6"/>
       <c r="K941" s="6"/>
     </row>
-    <row r="942" spans="10:11" ht="12.5">
+    <row r="942" spans="10:11" ht="13.2">
       <c r="J942" s="6"/>
       <c r="K942" s="6"/>
     </row>
-    <row r="943" spans="10:11" ht="12.5">
+    <row r="943" spans="10:11" ht="13.2">
       <c r="J943" s="6"/>
       <c r="K943" s="6"/>
     </row>
-    <row r="944" spans="10:11" ht="12.5">
+    <row r="944" spans="10:11" ht="13.2">
       <c r="J944" s="6"/>
       <c r="K944" s="6"/>
     </row>
-    <row r="945" spans="10:11" ht="12.5">
+    <row r="945" spans="10:11" ht="13.2">
       <c r="J945" s="6"/>
       <c r="K945" s="6"/>
     </row>
-    <row r="946" spans="10:11" ht="12.5">
+    <row r="946" spans="10:11" ht="13.2">
       <c r="J946" s="6"/>
       <c r="K946" s="6"/>
     </row>
-    <row r="947" spans="10:11" ht="12.5">
+    <row r="947" spans="10:11" ht="13.2">
       <c r="J947" s="6"/>
       <c r="K947" s="6"/>
     </row>
-    <row r="948" spans="10:11" ht="12.5">
+    <row r="948" spans="10:11" ht="13.2">
       <c r="J948" s="6"/>
       <c r="K948" s="6"/>
     </row>
-    <row r="949" spans="10:11" ht="12.5">
+    <row r="949" spans="10:11" ht="13.2">
       <c r="J949" s="6"/>
       <c r="K949" s="6"/>
     </row>
-    <row r="950" spans="10:11" ht="12.5">
+    <row r="950" spans="10:11" ht="13.2">
       <c r="J950" s="6"/>
       <c r="K950" s="6"/>
     </row>
-    <row r="951" spans="10:11" ht="12.5">
+    <row r="951" spans="10:11" ht="13.2">
       <c r="J951" s="6"/>
       <c r="K951" s="6"/>
     </row>
-    <row r="952" spans="10:11" ht="12.5">
+    <row r="952" spans="10:11" ht="13.2">
       <c r="J952" s="6"/>
       <c r="K952" s="6"/>
     </row>
-    <row r="953" spans="10:11" ht="12.5">
+    <row r="953" spans="10:11" ht="13.2">
       <c r="J953" s="6"/>
       <c r="K953" s="6"/>
     </row>
-    <row r="954" spans="10:11" ht="12.5">
+    <row r="954" spans="10:11" ht="13.2">
       <c r="J954" s="6"/>
       <c r="K954" s="6"/>
     </row>
-    <row r="955" spans="10:11" ht="12.5">
+    <row r="955" spans="10:11" ht="13.2">
       <c r="J955" s="6"/>
       <c r="K955" s="6"/>
     </row>
-    <row r="956" spans="10:11" ht="12.5">
+    <row r="956" spans="10:11" ht="13.2">
       <c r="J956" s="6"/>
       <c r="K956" s="6"/>
     </row>
-    <row r="957" spans="10:11" ht="12.5">
+    <row r="957" spans="10:11" ht="13.2">
       <c r="J957" s="6"/>
       <c r="K957" s="6"/>
     </row>
-    <row r="958" spans="10:11" ht="12.5">
+    <row r="958" spans="10:11" ht="13.2">
       <c r="J958" s="6"/>
       <c r="K958" s="6"/>
     </row>
-    <row r="959" spans="10:11" ht="12.5">
+    <row r="959" spans="10:11" ht="13.2">
       <c r="J959" s="6"/>
       <c r="K959" s="6"/>
     </row>
-    <row r="960" spans="10:11" ht="12.5">
+    <row r="960" spans="10:11" ht="13.2">
       <c r="J960" s="6"/>
       <c r="K960" s="6"/>
     </row>
-    <row r="961" spans="10:11" ht="12.5">
+    <row r="961" spans="10:11" ht="13.2">
       <c r="J961" s="6"/>
       <c r="K961" s="6"/>
     </row>
-    <row r="962" spans="10:11" ht="12.5">
+    <row r="962" spans="10:11" ht="13.2">
       <c r="J962" s="6"/>
       <c r="K962" s="6"/>
     </row>
-    <row r="963" spans="10:11" ht="12.5">
+    <row r="963" spans="10:11" ht="13.2">
       <c r="J963" s="6"/>
       <c r="K963" s="6"/>
     </row>
-    <row r="964" spans="10:11" ht="12.5">
+    <row r="964" spans="10:11" ht="13.2">
       <c r="J964" s="6"/>
       <c r="K964" s="6"/>
     </row>
-    <row r="965" spans="10:11" ht="12.5">
+    <row r="965" spans="10:11" ht="13.2">
       <c r="J965" s="6"/>
       <c r="K965" s="6"/>
     </row>
-    <row r="966" spans="10:11" ht="12.5">
+    <row r="966" spans="10:11" ht="13.2">
       <c r="J966" s="6"/>
       <c r="K966" s="6"/>
     </row>
-    <row r="967" spans="10:11" ht="12.5">
+    <row r="967" spans="10:11" ht="13.2">
       <c r="J967" s="6"/>
       <c r="K967" s="6"/>
     </row>
-    <row r="968" spans="10:11" ht="12.5">
+    <row r="968" spans="10:11" ht="13.2">
       <c r="J968" s="6"/>
       <c r="K968" s="6"/>
     </row>
-    <row r="969" spans="10:11" ht="12.5">
+    <row r="969" spans="10:11" ht="13.2">
       <c r="J969" s="6"/>
       <c r="K969" s="6"/>
     </row>
-    <row r="970" spans="10:11" ht="12.5">
+    <row r="970" spans="10:11" ht="13.2">
       <c r="J970" s="6"/>
       <c r="K970" s="6"/>
     </row>
-    <row r="971" spans="10:11" ht="12.5">
+    <row r="971" spans="10:11" ht="13.2">
       <c r="J971" s="6"/>
       <c r="K971" s="6"/>
     </row>
-    <row r="972" spans="10:11" ht="12.5">
+    <row r="972" spans="10:11" ht="13.2">
       <c r="J972" s="6"/>
       <c r="K972" s="6"/>
     </row>
-    <row r="973" spans="10:11" ht="12.5">
+    <row r="973" spans="10:11" ht="13.2">
       <c r="J973" s="6"/>
       <c r="K973" s="6"/>
     </row>
-    <row r="974" spans="10:11" ht="12.5">
+    <row r="974" spans="10:11" ht="13.2">
       <c r="J974" s="6"/>
       <c r="K974" s="6"/>
     </row>
-    <row r="975" spans="10:11" ht="12.5">
+    <row r="975" spans="10:11" ht="13.2">
       <c r="J975" s="6"/>
       <c r="K975" s="6"/>
     </row>
-    <row r="976" spans="10:11" ht="12.5">
+    <row r="976" spans="10:11" ht="13.2">
       <c r="J976" s="6"/>
       <c r="K976" s="6"/>
     </row>
-    <row r="977" spans="10:11" ht="12.5">
+    <row r="977" spans="10:11" ht="13.2">
       <c r="J977" s="6"/>
       <c r="K977" s="6"/>
     </row>
-    <row r="978" spans="10:11" ht="12.5">
+    <row r="978" spans="10:11" ht="13.2">
       <c r="J978" s="6"/>
       <c r="K978" s="6"/>
     </row>
-    <row r="979" spans="10:11" ht="12.5">
+    <row r="979" spans="10:11" ht="13.2">
       <c r="J979" s="6"/>
       <c r="K979" s="6"/>
     </row>
-    <row r="980" spans="10:11" ht="12.5">
+    <row r="980" spans="10:11" ht="13.2">
       <c r="J980" s="6"/>
       <c r="K980" s="6"/>
     </row>
-    <row r="981" spans="10:11" ht="12.5">
+    <row r="981" spans="10:11" ht="13.2">
       <c r="J981" s="6"/>
       <c r="K981" s="6"/>
     </row>
-    <row r="982" spans="10:11" ht="12.5">
+    <row r="982" spans="10:11" ht="13.2">
       <c r="J982" s="6"/>
       <c r="K982" s="6"/>
     </row>
-    <row r="983" spans="10:11" ht="12.5">
+    <row r="983" spans="10:11" ht="13.2">
       <c r="J983" s="6"/>
       <c r="K983" s="6"/>
     </row>
-    <row r="984" spans="10:11" ht="12.5">
+    <row r="984" spans="10:11" ht="13.2">
       <c r="J984" s="6"/>
       <c r="K984" s="6"/>
     </row>
-    <row r="985" spans="10:11" ht="12.5">
+    <row r="985" spans="10:11" ht="13.2">
       <c r="J985" s="6"/>
       <c r="K985" s="6"/>
     </row>
-    <row r="986" spans="10:11" ht="12.5">
+    <row r="986" spans="10:11" ht="13.2">
       <c r="J986" s="6"/>
       <c r="K986" s="6"/>
     </row>
-    <row r="987" spans="10:11" ht="12.5">
+    <row r="987" spans="10:11" ht="13.2">
       <c r="J987" s="6"/>
       <c r="K987" s="6"/>
     </row>
-    <row r="988" spans="10:11" ht="12.5">
+    <row r="988" spans="10:11" ht="13.2">
       <c r="J988" s="6"/>
       <c r="K988" s="6"/>
     </row>
-    <row r="989" spans="10:11" ht="12.5">
+    <row r="989" spans="10:11" ht="13.2">
       <c r="J989" s="6"/>
       <c r="K989" s="6"/>
     </row>
-    <row r="990" spans="10:11" ht="12.5">
+    <row r="990" spans="10:11" ht="13.2">
       <c r="J990" s="6"/>
       <c r="K990" s="6"/>
     </row>
-    <row r="991" spans="10:11" ht="12.5">
+    <row r="991" spans="10:11" ht="13.2">
       <c r="J991" s="6"/>
       <c r="K991" s="6"/>
     </row>
-    <row r="992" spans="10:11" ht="12.5">
+    <row r="992" spans="10:11" ht="13.2">
       <c r="J992" s="6"/>
       <c r="K992" s="6"/>
     </row>
-    <row r="993" spans="10:11" ht="12.5">
+    <row r="993" spans="10:11" ht="13.2">
       <c r="J993" s="6"/>
       <c r="K993" s="6"/>
     </row>
-    <row r="994" spans="10:11" ht="12.5">
+    <row r="994" spans="10:11" ht="13.2">
       <c r="J994" s="6"/>
       <c r="K994" s="6"/>
     </row>
-    <row r="995" spans="10:11" ht="12.5">
+    <row r="995" spans="10:11" ht="13.2">
       <c r="J995" s="6"/>
       <c r="K995" s="6"/>
     </row>
-    <row r="996" spans="10:11" ht="12.5">
+    <row r="996" spans="10:11" ht="13.2">
       <c r="J996" s="6"/>
       <c r="K996" s="6"/>
     </row>
-    <row r="997" spans="10:11" ht="12.5">
+    <row r="997" spans="10:11" ht="13.2">
       <c r="J997" s="6"/>
       <c r="K997" s="6"/>
     </row>
-    <row r="998" spans="10:11" ht="12.5">
+    <row r="998" spans="10:11" ht="13.2">
       <c r="J998" s="6"/>
       <c r="K998" s="6"/>
     </row>
-    <row r="999" spans="10:11" ht="12.5">
+    <row r="999" spans="10:11" ht="13.2">
       <c r="J999" s="6"/>
       <c r="K999" s="6"/>
     </row>
-    <row r="1000" spans="10:11" ht="12.5">
+    <row r="1000" spans="10:11" ht="13.2">
       <c r="J1000" s="6"/>
       <c r="K1000" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AJ15" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048572 N2:N1048572" xr:uid="{FED67D7D-1B44-45AF-99B3-FB1BD002C7BE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048572 T2:T1048572" xr:uid="{FED67D7D-1B44-45AF-99B3-FB1BD002C7BE}">
       <formula1>"15,30,45,60,90,120,180"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048572 M2:M1048572" xr:uid="{288FE9CB-530E-4C71-9260-55E725322ECE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048572 S2:S1048572" xr:uid="{288FE9CB-530E-4C71-9260-55E725322ECE}">
       <formula1>"Juan Manuel,Santiago,Manuela"</formula1>
     </dataValidation>
   </dataValidations>
